--- a/output/Fiyat-Listesi-Yonetim.xlsx
+++ b/output/Fiyat-Listesi-Yonetim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALS\Documents\26-27 Fiyat Listeleri\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62F9FCF-936D-40DC-A331-29AB861D61EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDCFB12-6446-4849-9699-1DBEB15D93EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2979" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3008" uniqueCount="698">
   <si>
     <t>Barkod</t>
   </si>
@@ -2041,6 +2041,93 @@
   </si>
   <si>
     <t>MÖF</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/eahn/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/gitx/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/ykgk/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/wtkw/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/bilu/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/uclz/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/wxxz/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/nfsd/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/xztx/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/ifyh/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/pqrm/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/rwrl/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/kbscf/uste/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/tjur/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/wobl/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/myzu/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/ssrj/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/byqm/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/arvp/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/mpgu/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/peka/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/mdvp/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/atkt/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/xwsi/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/nxnv/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/ehfc/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/lixu/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/hbis/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/yntn/</t>
   </si>
 </sst>
 </file>
@@ -2050,7 +2137,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\₺#,##0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -2082,6 +2169,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF173F5F"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -2193,10 +2286,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2279,12 +2373,16 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Köprü" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -2306,7 +2404,11 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UrunlerTablosu" displayName="UrunlerTablosu" ref="A1:K488" totalsRowShown="0">
-  <autoFilter ref="A1:K488" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <autoFilter ref="A1:K488" xr:uid="{00000000-0009-0000-0100-000002000000}">
+    <filterColumn colId="4">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Barkod"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Yayın"/>
@@ -2579,7 +2681,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="21.95" customHeight="1">
+    <row r="2" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A2" s="14" t="s">
         <v>10</v>
       </c>
@@ -2610,7 +2712,7 @@
         <v>356.3</v>
       </c>
       <c r="J2" s="11"/>
-      <c r="K2" s="31"/>
+      <c r="K2" s="30"/>
     </row>
     <row r="3" spans="1:11" ht="21.95" customHeight="1">
       <c r="A3" s="15" t="s">
@@ -2641,9 +2743,9 @@
         <v>377.3</v>
       </c>
       <c r="J3" s="12"/>
-      <c r="K3" s="31"/>
-    </row>
-    <row r="4" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K3" s="30"/>
+    </row>
+    <row r="4" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A4" s="15" t="s">
         <v>18</v>
       </c>
@@ -2674,7 +2776,7 @@
         <v>258.3</v>
       </c>
       <c r="J4" s="12"/>
-      <c r="K4" s="31"/>
+      <c r="K4" s="30"/>
     </row>
     <row r="5" spans="1:11" ht="21.95" customHeight="1">
       <c r="A5" s="15" t="s">
@@ -2705,9 +2807,9 @@
         <v>336</v>
       </c>
       <c r="J5" s="12"/>
-      <c r="K5" s="31"/>
-    </row>
-    <row r="6" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K5" s="30"/>
+    </row>
+    <row r="6" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>22</v>
       </c>
@@ -2736,9 +2838,9 @@
         <v>0</v>
       </c>
       <c r="J6" s="12"/>
-      <c r="K6" s="31"/>
-    </row>
-    <row r="7" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K6" s="30"/>
+    </row>
+    <row r="7" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A7" s="15" t="s">
         <v>25</v>
       </c>
@@ -2767,9 +2869,9 @@
         <v>0</v>
       </c>
       <c r="J7" s="12"/>
-      <c r="K7" s="31"/>
-    </row>
-    <row r="8" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K7" s="30"/>
+    </row>
+    <row r="8" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>27</v>
       </c>
@@ -2800,7 +2902,7 @@
         <v>153.30000000000001</v>
       </c>
       <c r="J8" s="12"/>
-      <c r="K8" s="31"/>
+      <c r="K8" s="30"/>
     </row>
     <row r="9" spans="1:11" ht="21.95" customHeight="1">
       <c r="A9" s="15" t="s">
@@ -2830,8 +2932,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B9,İndirimler!$B$2:$B$110,C9)&gt;0,ROUND(G9*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B9,İndirimler!$B$2:$B$110,C9)),2),"")</f>
         <v>384.3</v>
       </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="31"/>
+      <c r="J9" s="32" t="s">
+        <v>669</v>
+      </c>
+      <c r="K9" s="30"/>
     </row>
     <row r="10" spans="1:11" ht="21.95" customHeight="1">
       <c r="A10" s="15" t="s">
@@ -2862,9 +2966,9 @@
         <v>395.5</v>
       </c>
       <c r="J10" s="12"/>
-      <c r="K10" s="31"/>
-    </row>
-    <row r="11" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K10" s="30"/>
+    </row>
+    <row r="11" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A11" s="15" t="s">
         <v>36</v>
       </c>
@@ -2893,9 +2997,9 @@
         <v>0</v>
       </c>
       <c r="J11" s="12"/>
-      <c r="K11" s="31"/>
-    </row>
-    <row r="12" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K11" s="30"/>
+    </row>
+    <row r="12" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>39</v>
       </c>
@@ -2928,7 +3032,7 @@
       <c r="J12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K12" s="31"/>
+      <c r="K12" s="30"/>
     </row>
     <row r="13" spans="1:11" ht="21.95" customHeight="1">
       <c r="A13" s="15" t="s">
@@ -2959,9 +3063,9 @@
         <v>468.3</v>
       </c>
       <c r="J13" s="12"/>
-      <c r="K13" s="31"/>
-    </row>
-    <row r="14" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K13" s="30"/>
+    </row>
+    <row r="14" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A14" s="15" t="s">
         <v>44</v>
       </c>
@@ -2992,7 +3096,7 @@
         <v>560</v>
       </c>
       <c r="J14" s="12"/>
-      <c r="K14" s="31"/>
+      <c r="K14" s="30"/>
     </row>
     <row r="15" spans="1:11" ht="21.95" customHeight="1">
       <c r="A15" s="15" t="s">
@@ -3023,7 +3127,7 @@
         <v>377.3</v>
       </c>
       <c r="J15" s="12"/>
-      <c r="K15" s="31"/>
+      <c r="K15" s="30"/>
     </row>
     <row r="16" spans="1:11" ht="21.95" customHeight="1">
       <c r="A16" s="15" t="s">
@@ -3056,7 +3160,7 @@
       <c r="J16" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="K16" s="31"/>
+      <c r="K16" s="30"/>
     </row>
     <row r="17" spans="1:11" ht="21.95" customHeight="1">
       <c r="A17" s="15" t="s">
@@ -3086,10 +3190,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B17,İndirimler!$B$2:$B$110,C17)&gt;0,ROUND(G17*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B17,İndirimler!$B$2:$B$110,C17)),2),"")</f>
         <v>230.3</v>
       </c>
-      <c r="J17" s="12"/>
-      <c r="K17" s="31"/>
-    </row>
-    <row r="18" spans="1:11" ht="21.95" customHeight="1">
+      <c r="J17" s="32" t="s">
+        <v>682</v>
+      </c>
+      <c r="K17" s="30"/>
+    </row>
+    <row r="18" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A18" s="15" t="s">
         <v>53</v>
       </c>
@@ -3122,9 +3228,9 @@
       <c r="J18" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K18" s="31"/>
-    </row>
-    <row r="19" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K18" s="30"/>
+    </row>
+    <row r="19" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A19" s="15" t="s">
         <v>56</v>
       </c>
@@ -3155,7 +3261,7 @@
         <v>332.5</v>
       </c>
       <c r="J19" s="12"/>
-      <c r="K19" s="31"/>
+      <c r="K19" s="30"/>
     </row>
     <row r="20" spans="1:11" ht="21.95" customHeight="1">
       <c r="A20" s="15" t="s">
@@ -3186,9 +3292,9 @@
         <v>438.2</v>
       </c>
       <c r="J20" s="12"/>
-      <c r="K20" s="31"/>
-    </row>
-    <row r="21" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K20" s="30"/>
+    </row>
+    <row r="21" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A21" s="15" t="s">
         <v>60</v>
       </c>
@@ -3219,9 +3325,9 @@
         <v>345.1</v>
       </c>
       <c r="J21" s="12"/>
-      <c r="K21" s="31"/>
-    </row>
-    <row r="22" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K21" s="30"/>
+    </row>
+    <row r="22" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A22" s="15" t="s">
         <v>62</v>
       </c>
@@ -3252,7 +3358,7 @@
         <v>363.3</v>
       </c>
       <c r="J22" s="12"/>
-      <c r="K22" s="31"/>
+      <c r="K22" s="30"/>
     </row>
     <row r="23" spans="1:11" ht="21.95" customHeight="1">
       <c r="A23" s="15" t="s">
@@ -3283,7 +3389,7 @@
         <v>230.3</v>
       </c>
       <c r="J23" s="12"/>
-      <c r="K23" s="31"/>
+      <c r="K23" s="30"/>
     </row>
     <row r="24" spans="1:11" ht="21.95" customHeight="1">
       <c r="A24" s="15" t="s">
@@ -3314,7 +3420,7 @@
         <v>300.3</v>
       </c>
       <c r="J24" s="12"/>
-      <c r="K24" s="31"/>
+      <c r="K24" s="30"/>
     </row>
     <row r="25" spans="1:11" ht="21.95" customHeight="1">
       <c r="A25" s="15" t="s">
@@ -3344,8 +3450,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B25,İndirimler!$B$2:$B$110,C25)&gt;0,ROUND(G25*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B25,İndirimler!$B$2:$B$110,C25)),2),"")</f>
         <v>370.3</v>
       </c>
-      <c r="J25" s="12"/>
-      <c r="K25" s="31"/>
+      <c r="J25" s="32" t="s">
+        <v>676</v>
+      </c>
+      <c r="K25" s="30"/>
     </row>
     <row r="26" spans="1:11" ht="21.95" customHeight="1">
       <c r="A26" s="15" t="s">
@@ -3376,9 +3484,9 @@
         <v>412.3</v>
       </c>
       <c r="J26" s="12"/>
-      <c r="K26" s="31"/>
-    </row>
-    <row r="27" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K26" s="30"/>
+    </row>
+    <row r="27" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A27" s="15" t="s">
         <v>70</v>
       </c>
@@ -3407,9 +3515,9 @@
         <v>0</v>
       </c>
       <c r="J27" s="12"/>
-      <c r="K27" s="31"/>
-    </row>
-    <row r="28" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K27" s="30"/>
+    </row>
+    <row r="28" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A28" s="15" t="s">
         <v>71</v>
       </c>
@@ -3442,7 +3550,7 @@
       <c r="J28" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="K28" s="31"/>
+      <c r="K28" s="30"/>
     </row>
     <row r="29" spans="1:11" ht="21.95" customHeight="1">
       <c r="A29" s="15" t="s">
@@ -3473,9 +3581,9 @@
         <v>478.8</v>
       </c>
       <c r="J29" s="12"/>
-      <c r="K29" s="31"/>
-    </row>
-    <row r="30" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K29" s="30"/>
+    </row>
+    <row r="30" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A30" s="15" t="s">
         <v>74</v>
       </c>
@@ -3506,7 +3614,7 @@
         <v>574</v>
       </c>
       <c r="J30" s="12"/>
-      <c r="K30" s="31"/>
+      <c r="K30" s="30"/>
     </row>
     <row r="31" spans="1:11" ht="21.95" customHeight="1">
       <c r="A31" s="15" t="s">
@@ -3539,7 +3647,7 @@
       <c r="J31" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K31" s="31"/>
+      <c r="K31" s="30"/>
     </row>
     <row r="32" spans="1:11" ht="21.95" customHeight="1">
       <c r="A32" s="15" t="s">
@@ -3569,10 +3677,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B32,İndirimler!$B$2:$B$110,C32)&gt;0,ROUND(G32*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B32,İndirimler!$B$2:$B$110,C32)),2),"")</f>
         <v>335.3</v>
       </c>
-      <c r="J32" s="12"/>
-      <c r="K32" s="31"/>
-    </row>
-    <row r="33" spans="1:11" ht="21.95" customHeight="1">
+      <c r="J32" s="32" t="s">
+        <v>689</v>
+      </c>
+      <c r="K32" s="30"/>
+    </row>
+    <row r="33" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A33" s="15" t="s">
         <v>78</v>
       </c>
@@ -3605,9 +3715,9 @@
       <c r="J33" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="K33" s="31"/>
-    </row>
-    <row r="34" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K33" s="30"/>
+    </row>
+    <row r="34" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A34" s="15" t="s">
         <v>80</v>
       </c>
@@ -3638,7 +3748,7 @@
         <v>283.5</v>
       </c>
       <c r="J34" s="12"/>
-      <c r="K34" s="31"/>
+      <c r="K34" s="30"/>
     </row>
     <row r="35" spans="1:11" ht="21.95" customHeight="1">
       <c r="A35" s="15" t="s">
@@ -3669,9 +3779,9 @@
         <v>435.4</v>
       </c>
       <c r="J35" s="12"/>
-      <c r="K35" s="31"/>
-    </row>
-    <row r="36" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K35" s="30"/>
+    </row>
+    <row r="36" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A36" s="15" t="s">
         <v>82</v>
       </c>
@@ -3702,7 +3812,7 @@
         <v>418.6</v>
       </c>
       <c r="J36" s="12"/>
-      <c r="K36" s="31"/>
+      <c r="K36" s="30"/>
     </row>
     <row r="37" spans="1:11" ht="21.95" customHeight="1">
       <c r="A37" s="15" t="s">
@@ -3733,9 +3843,9 @@
         <v>377.3</v>
       </c>
       <c r="J37" s="12"/>
-      <c r="K37" s="31"/>
-    </row>
-    <row r="38" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K37" s="30"/>
+    </row>
+    <row r="38" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A38" s="15" t="s">
         <v>84</v>
       </c>
@@ -3766,7 +3876,7 @@
         <v>353.5</v>
       </c>
       <c r="J38" s="12"/>
-      <c r="K38" s="31"/>
+      <c r="K38" s="30"/>
     </row>
     <row r="39" spans="1:11" ht="21.95" customHeight="1">
       <c r="A39" s="15" t="s">
@@ -3797,7 +3907,7 @@
         <v>286.3</v>
       </c>
       <c r="J39" s="12"/>
-      <c r="K39" s="31"/>
+      <c r="K39" s="30"/>
     </row>
     <row r="40" spans="1:11" ht="21.95" customHeight="1">
       <c r="A40" s="15" t="s">
@@ -3826,9 +3936,9 @@
         <v>0</v>
       </c>
       <c r="J40" s="12"/>
-      <c r="K40" s="31"/>
-    </row>
-    <row r="41" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K40" s="30"/>
+    </row>
+    <row r="41" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A41" s="15" t="s">
         <v>88</v>
       </c>
@@ -3857,9 +3967,9 @@
         <v>0</v>
       </c>
       <c r="J41" s="12"/>
-      <c r="K41" s="31"/>
-    </row>
-    <row r="42" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K41" s="30"/>
+    </row>
+    <row r="42" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A42" s="15" t="s">
         <v>89</v>
       </c>
@@ -3888,7 +3998,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="12"/>
-      <c r="K42" s="31"/>
+      <c r="K42" s="30"/>
     </row>
     <row r="43" spans="1:11" ht="21.95" customHeight="1">
       <c r="A43" s="15" t="s">
@@ -3919,9 +4029,9 @@
         <v>382.2</v>
       </c>
       <c r="J43" s="12"/>
-      <c r="K43" s="31"/>
-    </row>
-    <row r="44" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K43" s="30"/>
+    </row>
+    <row r="44" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A44" s="15" t="s">
         <v>92</v>
       </c>
@@ -3952,7 +4062,7 @@
         <v>588</v>
       </c>
       <c r="J44" s="12"/>
-      <c r="K44" s="31"/>
+      <c r="K44" s="30"/>
     </row>
     <row r="45" spans="1:11" ht="21.95" customHeight="1">
       <c r="A45" s="15" t="s">
@@ -3983,7 +4093,7 @@
         <v>281.39999999999998</v>
       </c>
       <c r="J45" s="12"/>
-      <c r="K45" s="31"/>
+      <c r="K45" s="30"/>
     </row>
     <row r="46" spans="1:11" ht="21.95" customHeight="1">
       <c r="A46" s="15" t="s">
@@ -4012,9 +4122,9 @@
         <v>0</v>
       </c>
       <c r="J46" s="12"/>
-      <c r="K46" s="31"/>
-    </row>
-    <row r="47" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K46" s="30"/>
+    </row>
+    <row r="47" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A47" s="15" t="s">
         <v>95</v>
       </c>
@@ -4043,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="12"/>
-      <c r="K47" s="31"/>
+      <c r="K47" s="30"/>
     </row>
     <row r="48" spans="1:11" ht="21.95" customHeight="1">
       <c r="A48" s="15" t="s">
@@ -4074,9 +4184,9 @@
         <v>343</v>
       </c>
       <c r="J48" s="12"/>
-      <c r="K48" s="31"/>
-    </row>
-    <row r="49" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K48" s="30"/>
+    </row>
+    <row r="49" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A49" s="15" t="s">
         <v>97</v>
       </c>
@@ -4107,7 +4217,7 @@
         <v>431.2</v>
       </c>
       <c r="J49" s="12"/>
-      <c r="K49" s="31"/>
+      <c r="K49" s="30"/>
     </row>
     <row r="50" spans="1:11" ht="21.95" customHeight="1">
       <c r="A50" s="15" t="s">
@@ -4136,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="12"/>
-      <c r="K50" s="31"/>
+      <c r="K50" s="30"/>
     </row>
     <row r="51" spans="1:11" ht="21.95" customHeight="1">
       <c r="A51" s="15" t="s">
@@ -4165,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="12"/>
-      <c r="K51" s="31"/>
+      <c r="K51" s="30"/>
     </row>
     <row r="52" spans="1:11" ht="21.95" customHeight="1">
       <c r="A52" s="15" t="s">
@@ -4194,9 +4304,9 @@
         <v>0</v>
       </c>
       <c r="J52" s="12"/>
-      <c r="K52" s="31"/>
-    </row>
-    <row r="53" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K52" s="30"/>
+    </row>
+    <row r="53" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A53" s="15" t="s">
         <v>101</v>
       </c>
@@ -4227,9 +4337,9 @@
         <v>255.5</v>
       </c>
       <c r="J53" s="12"/>
-      <c r="K53" s="31"/>
-    </row>
-    <row r="54" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K53" s="30"/>
+    </row>
+    <row r="54" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A54" s="15" t="s">
         <v>102</v>
       </c>
@@ -4260,9 +4370,9 @@
         <v>461.3</v>
       </c>
       <c r="J54" s="12"/>
-      <c r="K54" s="31"/>
-    </row>
-    <row r="55" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K54" s="30"/>
+    </row>
+    <row r="55" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A55" s="15" t="s">
         <v>105</v>
       </c>
@@ -4293,9 +4403,9 @@
         <v>461.3</v>
       </c>
       <c r="J55" s="12"/>
-      <c r="K55" s="31"/>
-    </row>
-    <row r="56" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K55" s="30"/>
+    </row>
+    <row r="56" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A56" s="15" t="s">
         <v>106</v>
       </c>
@@ -4324,9 +4434,9 @@
         <v>0</v>
       </c>
       <c r="J56" s="12"/>
-      <c r="K56" s="31"/>
-    </row>
-    <row r="57" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K56" s="30"/>
+    </row>
+    <row r="57" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A57" s="15" t="s">
         <v>109</v>
       </c>
@@ -4357,9 +4467,9 @@
         <v>461.3</v>
       </c>
       <c r="J57" s="12"/>
-      <c r="K57" s="31"/>
-    </row>
-    <row r="58" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K57" s="30"/>
+    </row>
+    <row r="58" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A58" s="15" t="s">
         <v>110</v>
       </c>
@@ -4390,7 +4500,7 @@
         <v>461.3</v>
       </c>
       <c r="J58" s="12"/>
-      <c r="K58" s="31" t="s">
+      <c r="K58" s="30" t="s">
         <v>113</v>
       </c>
     </row>
@@ -4422,8 +4532,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B59,İndirimler!$B$2:$B$110,C59)&gt;0,ROUND(G59*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B59,İndirimler!$B$2:$B$110,C59)),2),"")</f>
         <v>489.3</v>
       </c>
-      <c r="J59" s="12"/>
-      <c r="K59" s="31"/>
+      <c r="J59" s="32" t="s">
+        <v>672</v>
+      </c>
+      <c r="K59" s="30"/>
     </row>
     <row r="60" spans="1:11" ht="21.95" customHeight="1">
       <c r="A60" s="15" t="s">
@@ -4454,7 +4566,7 @@
         <v>699.3</v>
       </c>
       <c r="J60" s="12"/>
-      <c r="K60" s="31"/>
+      <c r="K60" s="30"/>
     </row>
     <row r="61" spans="1:11" ht="21.95" customHeight="1">
       <c r="A61" s="15" t="s">
@@ -4485,9 +4597,9 @@
         <v>629.29999999999995</v>
       </c>
       <c r="J61" s="12"/>
-      <c r="K61" s="31"/>
-    </row>
-    <row r="62" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K61" s="30"/>
+    </row>
+    <row r="62" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A62" s="15" t="s">
         <v>118</v>
       </c>
@@ -4518,9 +4630,9 @@
         <v>450.8</v>
       </c>
       <c r="J62" s="12"/>
-      <c r="K62" s="31"/>
-    </row>
-    <row r="63" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K62" s="30"/>
+    </row>
+    <row r="63" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A63" s="15" t="s">
         <v>121</v>
       </c>
@@ -4553,9 +4665,9 @@
       <c r="J63" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="K63" s="31"/>
-    </row>
-    <row r="64" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K63" s="30"/>
+    </row>
+    <row r="64" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A64" s="15" t="s">
         <v>124</v>
       </c>
@@ -4586,9 +4698,9 @@
         <v>403.2</v>
       </c>
       <c r="J64" s="12"/>
-      <c r="K64" s="31"/>
-    </row>
-    <row r="65" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K64" s="30"/>
+    </row>
+    <row r="65" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A65" s="15" t="s">
         <v>125</v>
       </c>
@@ -4619,9 +4731,9 @@
         <v>403.2</v>
       </c>
       <c r="J65" s="12"/>
-      <c r="K65" s="31"/>
-    </row>
-    <row r="66" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K65" s="30"/>
+    </row>
+    <row r="66" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A66" s="15" t="s">
         <v>126</v>
       </c>
@@ -4652,9 +4764,9 @@
         <v>588</v>
       </c>
       <c r="J66" s="12"/>
-      <c r="K66" s="31"/>
-    </row>
-    <row r="67" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K66" s="30"/>
+    </row>
+    <row r="67" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A67" s="15" t="s">
         <v>128</v>
       </c>
@@ -4687,7 +4799,7 @@
       <c r="J67" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="K67" s="31"/>
+      <c r="K67" s="30"/>
     </row>
     <row r="68" spans="1:11" ht="21.95" customHeight="1">
       <c r="A68" s="15" t="s">
@@ -4718,9 +4830,9 @@
         <v>335.3</v>
       </c>
       <c r="J68" s="12"/>
-      <c r="K68" s="31"/>
-    </row>
-    <row r="69" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K68" s="30"/>
+    </row>
+    <row r="69" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A69" s="15" t="s">
         <v>131</v>
       </c>
@@ -4751,9 +4863,9 @@
         <v>353.5</v>
       </c>
       <c r="J69" s="12"/>
-      <c r="K69" s="31"/>
-    </row>
-    <row r="70" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K69" s="30"/>
+    </row>
+    <row r="70" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A70" s="15" t="s">
         <v>133</v>
       </c>
@@ -4784,7 +4896,7 @@
         <v>425.6</v>
       </c>
       <c r="J70" s="12"/>
-      <c r="K70" s="31"/>
+      <c r="K70" s="30"/>
     </row>
     <row r="71" spans="1:11" ht="21.95" customHeight="1">
       <c r="A71" s="15" t="s">
@@ -4814,10 +4926,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B71,İndirimler!$B$2:$B$110,C71)&gt;0,ROUND(G71*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B71,İndirimler!$B$2:$B$110,C71)),2),"")</f>
         <v>433.3</v>
       </c>
-      <c r="J71" s="12"/>
-      <c r="K71" s="31"/>
-    </row>
-    <row r="72" spans="1:11" ht="21.95" customHeight="1">
+      <c r="J71" s="32" t="s">
+        <v>683</v>
+      </c>
+      <c r="K71" s="30"/>
+    </row>
+    <row r="72" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A72" s="15" t="s">
         <v>135</v>
       </c>
@@ -4848,9 +4962,9 @@
         <v>559.29999999999995</v>
       </c>
       <c r="J72" s="12"/>
-      <c r="K72" s="31"/>
-    </row>
-    <row r="73" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K72" s="30"/>
+    </row>
+    <row r="73" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A73" s="15" t="s">
         <v>136</v>
       </c>
@@ -4883,9 +4997,9 @@
       <c r="J73" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="K73" s="31"/>
-    </row>
-    <row r="74" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K73" s="30"/>
+    </row>
+    <row r="74" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A74" s="15" t="s">
         <v>139</v>
       </c>
@@ -4916,9 +5030,9 @@
         <v>318.5</v>
       </c>
       <c r="J74" s="12"/>
-      <c r="K74" s="31"/>
-    </row>
-    <row r="75" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K74" s="30"/>
+    </row>
+    <row r="75" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A75" s="15" t="s">
         <v>141</v>
       </c>
@@ -4949,9 +5063,9 @@
         <v>381.5</v>
       </c>
       <c r="J75" s="12"/>
-      <c r="K75" s="31"/>
-    </row>
-    <row r="76" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K75" s="30"/>
+    </row>
+    <row r="76" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A76" s="15" t="s">
         <v>142</v>
       </c>
@@ -4982,9 +5096,9 @@
         <v>473.2</v>
       </c>
       <c r="J76" s="12"/>
-      <c r="K76" s="31"/>
-    </row>
-    <row r="77" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K76" s="30"/>
+    </row>
+    <row r="77" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A77" s="15" t="s">
         <v>143</v>
       </c>
@@ -5013,9 +5127,9 @@
         <v>0</v>
       </c>
       <c r="J77" s="12"/>
-      <c r="K77" s="31"/>
-    </row>
-    <row r="78" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K77" s="30"/>
+    </row>
+    <row r="78" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A78" s="15" t="s">
         <v>144</v>
       </c>
@@ -5046,7 +5160,7 @@
         <v>480.2</v>
       </c>
       <c r="J78" s="12"/>
-      <c r="K78" s="31"/>
+      <c r="K78" s="30"/>
     </row>
     <row r="79" spans="1:11" ht="21.95" customHeight="1">
       <c r="A79" s="15" t="s">
@@ -5077,7 +5191,7 @@
         <v>405.3</v>
       </c>
       <c r="J79" s="12"/>
-      <c r="K79" s="31"/>
+      <c r="K79" s="30"/>
     </row>
     <row r="80" spans="1:11" ht="21.95" customHeight="1">
       <c r="A80" s="15" t="s">
@@ -5108,9 +5222,9 @@
         <v>269.5</v>
       </c>
       <c r="J80" s="12"/>
-      <c r="K80" s="31"/>
-    </row>
-    <row r="81" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K80" s="30"/>
+    </row>
+    <row r="81" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A81" s="15" t="s">
         <v>147</v>
       </c>
@@ -5141,7 +5255,7 @@
         <v>350</v>
       </c>
       <c r="J81" s="12"/>
-      <c r="K81" s="31"/>
+      <c r="K81" s="30"/>
     </row>
     <row r="82" spans="1:11" ht="21.95" customHeight="1">
       <c r="A82" s="15" t="s">
@@ -5172,9 +5286,9 @@
         <v>318.5</v>
       </c>
       <c r="J82" s="12"/>
-      <c r="K82" s="31"/>
-    </row>
-    <row r="83" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K82" s="30"/>
+    </row>
+    <row r="83" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A83" s="15" t="s">
         <v>149</v>
       </c>
@@ -5205,9 +5319,9 @@
         <v>482.3</v>
       </c>
       <c r="J83" s="12"/>
-      <c r="K83" s="31"/>
-    </row>
-    <row r="84" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K83" s="30"/>
+    </row>
+    <row r="84" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A84" s="15" t="s">
         <v>150</v>
       </c>
@@ -5236,9 +5350,9 @@
         <v>0</v>
       </c>
       <c r="J84" s="12"/>
-      <c r="K84" s="31"/>
-    </row>
-    <row r="85" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K84" s="30"/>
+    </row>
+    <row r="85" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A85" s="15" t="s">
         <v>151</v>
       </c>
@@ -5269,9 +5383,9 @@
         <v>615.29999999999995</v>
       </c>
       <c r="J85" s="12"/>
-      <c r="K85" s="31"/>
-    </row>
-    <row r="86" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K85" s="30"/>
+    </row>
+    <row r="86" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A86" s="15" t="s">
         <v>152</v>
       </c>
@@ -5302,7 +5416,7 @@
         <v>594.29999999999995</v>
       </c>
       <c r="J86" s="12"/>
-      <c r="K86" s="31"/>
+      <c r="K86" s="30"/>
     </row>
     <row r="87" spans="1:11" ht="21.95" customHeight="1">
       <c r="A87" s="15" t="s">
@@ -5332,8 +5446,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B87,İndirimler!$B$2:$B$110,C87)&gt;0,ROUND(G87*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B87,İndirimler!$B$2:$B$110,C87)),2),"")</f>
         <v>517.29999999999995</v>
       </c>
-      <c r="J87" s="12"/>
-      <c r="K87" s="31"/>
+      <c r="J87" s="32" t="s">
+        <v>678</v>
+      </c>
+      <c r="K87" s="30"/>
     </row>
     <row r="88" spans="1:11" ht="21.95" customHeight="1">
       <c r="A88" s="15" t="s">
@@ -5364,7 +5480,7 @@
         <v>528.5</v>
       </c>
       <c r="J88" s="12"/>
-      <c r="K88" s="31"/>
+      <c r="K88" s="30"/>
     </row>
     <row r="89" spans="1:11" ht="21.95" customHeight="1">
       <c r="A89" s="15" t="s">
@@ -5395,9 +5511,9 @@
         <v>545.29999999999995</v>
       </c>
       <c r="J89" s="12"/>
-      <c r="K89" s="31"/>
-    </row>
-    <row r="90" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K89" s="30"/>
+    </row>
+    <row r="90" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A90" s="15" t="s">
         <v>156</v>
       </c>
@@ -5428,9 +5544,9 @@
         <v>414.4</v>
       </c>
       <c r="J90" s="12"/>
-      <c r="K90" s="31"/>
-    </row>
-    <row r="91" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K90" s="30"/>
+    </row>
+    <row r="91" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A91" s="15" t="s">
         <v>157</v>
       </c>
@@ -5463,9 +5579,9 @@
       <c r="J91" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="K91" s="31"/>
-    </row>
-    <row r="92" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K91" s="30"/>
+    </row>
+    <row r="92" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A92" s="15" t="s">
         <v>159</v>
       </c>
@@ -5496,9 +5612,9 @@
         <v>474.6</v>
       </c>
       <c r="J92" s="12"/>
-      <c r="K92" s="31"/>
-    </row>
-    <row r="93" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K92" s="30"/>
+    </row>
+    <row r="93" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A93" s="15" t="s">
         <v>160</v>
       </c>
@@ -5529,9 +5645,9 @@
         <v>588</v>
       </c>
       <c r="J93" s="12"/>
-      <c r="K93" s="31"/>
-    </row>
-    <row r="94" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K93" s="30"/>
+    </row>
+    <row r="94" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A94" s="15" t="s">
         <v>161</v>
       </c>
@@ -5564,7 +5680,7 @@
       <c r="J94" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="K94" s="31"/>
+      <c r="K94" s="30"/>
     </row>
     <row r="95" spans="1:11" ht="21.95" customHeight="1">
       <c r="A95" s="15" t="s">
@@ -5595,9 +5711,9 @@
         <v>325.5</v>
       </c>
       <c r="J95" s="12"/>
-      <c r="K95" s="31"/>
-    </row>
-    <row r="96" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K95" s="30"/>
+    </row>
+    <row r="96" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A96" s="15" t="s">
         <v>164</v>
       </c>
@@ -5628,9 +5744,9 @@
         <v>325.5</v>
       </c>
       <c r="J96" s="12"/>
-      <c r="K96" s="31"/>
-    </row>
-    <row r="97" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K96" s="30"/>
+    </row>
+    <row r="97" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A97" s="15" t="s">
         <v>165</v>
       </c>
@@ -5661,7 +5777,7 @@
         <v>358.4</v>
       </c>
       <c r="J97" s="12"/>
-      <c r="K97" s="31"/>
+      <c r="K97" s="30"/>
     </row>
     <row r="98" spans="1:11" ht="21.95" customHeight="1">
       <c r="A98" s="15" t="s">
@@ -5691,10 +5807,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B98,İndirimler!$B$2:$B$110,C98)&gt;0,ROUND(G98*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B98,İndirimler!$B$2:$B$110,C98)),2),"")</f>
         <v>479.5</v>
       </c>
-      <c r="J98" s="12"/>
-      <c r="K98" s="31"/>
-    </row>
-    <row r="99" spans="1:11" ht="21.95" customHeight="1">
+      <c r="J98" s="32" t="s">
+        <v>690</v>
+      </c>
+      <c r="K98" s="30"/>
+    </row>
+    <row r="99" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A99" s="15" t="s">
         <v>167</v>
       </c>
@@ -5725,9 +5843,9 @@
         <v>573.29999999999995</v>
       </c>
       <c r="J99" s="12"/>
-      <c r="K99" s="31"/>
-    </row>
-    <row r="100" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K99" s="30"/>
+    </row>
+    <row r="100" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A100" s="15" t="s">
         <v>168</v>
       </c>
@@ -5760,7 +5878,7 @@
       <c r="J100" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="K100" s="31"/>
+      <c r="K100" s="30"/>
     </row>
     <row r="101" spans="1:11" ht="21.95" customHeight="1">
       <c r="A101" s="15" t="s">
@@ -5791,9 +5909,9 @@
         <v>349.3</v>
       </c>
       <c r="J101" s="12"/>
-      <c r="K101" s="31"/>
-    </row>
-    <row r="102" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K101" s="30"/>
+    </row>
+    <row r="102" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A102" s="15" t="s">
         <v>171</v>
       </c>
@@ -5824,9 +5942,9 @@
         <v>398.3</v>
       </c>
       <c r="J102" s="12"/>
-      <c r="K102" s="31"/>
-    </row>
-    <row r="103" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K102" s="30"/>
+    </row>
+    <row r="103" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A103" s="15" t="s">
         <v>172</v>
       </c>
@@ -5857,9 +5975,9 @@
         <v>469</v>
       </c>
       <c r="J103" s="12"/>
-      <c r="K103" s="31"/>
-    </row>
-    <row r="104" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K103" s="30"/>
+    </row>
+    <row r="104" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A104" s="15" t="s">
         <v>173</v>
       </c>
@@ -5888,9 +6006,9 @@
         <v>0</v>
       </c>
       <c r="J104" s="12"/>
-      <c r="K104" s="31"/>
-    </row>
-    <row r="105" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K104" s="30"/>
+    </row>
+    <row r="105" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A105" s="15" t="s">
         <v>174</v>
       </c>
@@ -5921,7 +6039,7 @@
         <v>431.2</v>
       </c>
       <c r="J105" s="12"/>
-      <c r="K105" s="31"/>
+      <c r="K105" s="30"/>
     </row>
     <row r="106" spans="1:11" ht="21.95" customHeight="1">
       <c r="A106" s="15" t="s">
@@ -5952,7 +6070,7 @@
         <v>468.3</v>
       </c>
       <c r="J106" s="12"/>
-      <c r="K106" s="31"/>
+      <c r="K106" s="30"/>
     </row>
     <row r="107" spans="1:11" ht="21.95" customHeight="1">
       <c r="A107" s="15" t="s">
@@ -5983,9 +6101,9 @@
         <v>269.5</v>
       </c>
       <c r="J107" s="12"/>
-      <c r="K107" s="31"/>
-    </row>
-    <row r="108" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K107" s="30"/>
+    </row>
+    <row r="108" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A108" s="15" t="s">
         <v>177</v>
       </c>
@@ -6016,7 +6134,7 @@
         <v>363.3</v>
       </c>
       <c r="J108" s="12"/>
-      <c r="K108" s="31"/>
+      <c r="K108" s="30"/>
     </row>
     <row r="109" spans="1:11" ht="21.95" customHeight="1">
       <c r="A109" s="15" t="s">
@@ -6047,7 +6165,7 @@
         <v>269.5</v>
       </c>
       <c r="J109" s="12"/>
-      <c r="K109" s="31"/>
+      <c r="K109" s="30"/>
     </row>
     <row r="110" spans="1:11" ht="21.95" customHeight="1">
       <c r="A110" s="15" t="s">
@@ -6076,9 +6194,9 @@
         <v>0</v>
       </c>
       <c r="J110" s="12"/>
-      <c r="K110" s="31"/>
-    </row>
-    <row r="111" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K110" s="30"/>
+    </row>
+    <row r="111" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A111" s="15" t="s">
         <v>180</v>
       </c>
@@ -6107,9 +6225,9 @@
         <v>0</v>
       </c>
       <c r="J111" s="12"/>
-      <c r="K111" s="31"/>
-    </row>
-    <row r="112" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K111" s="30"/>
+    </row>
+    <row r="112" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A112" s="15" t="s">
         <v>181</v>
       </c>
@@ -6138,9 +6256,9 @@
         <v>0</v>
       </c>
       <c r="J112" s="12"/>
-      <c r="K112" s="31"/>
-    </row>
-    <row r="113" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K112" s="30"/>
+    </row>
+    <row r="113" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A113" s="15" t="s">
         <v>182</v>
       </c>
@@ -6169,7 +6287,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="12"/>
-      <c r="K113" s="31"/>
+      <c r="K113" s="30"/>
     </row>
     <row r="114" spans="1:11" ht="21.95" customHeight="1">
       <c r="A114" s="15" t="s">
@@ -6200,7 +6318,7 @@
         <v>461.3</v>
       </c>
       <c r="J114" s="12"/>
-      <c r="K114" s="31"/>
+      <c r="K114" s="30"/>
     </row>
     <row r="115" spans="1:11" ht="21.95" customHeight="1">
       <c r="A115" s="15" t="s">
@@ -6229,9 +6347,9 @@
         <v>0</v>
       </c>
       <c r="J115" s="12"/>
-      <c r="K115" s="31"/>
-    </row>
-    <row r="116" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K115" s="30"/>
+    </row>
+    <row r="116" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A116" s="15" t="s">
         <v>187</v>
       </c>
@@ -6262,9 +6380,9 @@
         <v>450.8</v>
       </c>
       <c r="J116" s="12"/>
-      <c r="K116" s="31"/>
-    </row>
-    <row r="117" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K116" s="30"/>
+    </row>
+    <row r="117" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A117" s="15" t="s">
         <v>188</v>
       </c>
@@ -6293,9 +6411,9 @@
         <v>0</v>
       </c>
       <c r="J117" s="12"/>
-      <c r="K117" s="31"/>
-    </row>
-    <row r="118" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K117" s="30"/>
+    </row>
+    <row r="118" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A118" s="15" t="s">
         <v>189</v>
       </c>
@@ -6324,7 +6442,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="12"/>
-      <c r="K118" s="31"/>
+      <c r="K118" s="30"/>
     </row>
     <row r="119" spans="1:11" ht="21.95" customHeight="1">
       <c r="A119" s="15" t="s">
@@ -6355,9 +6473,9 @@
         <v>430.5</v>
       </c>
       <c r="J119" s="12"/>
-      <c r="K119" s="31"/>
-    </row>
-    <row r="120" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K119" s="30"/>
+    </row>
+    <row r="120" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A120" s="15" t="s">
         <v>192</v>
       </c>
@@ -6388,9 +6506,9 @@
         <v>382.2</v>
       </c>
       <c r="J120" s="12"/>
-      <c r="K120" s="31"/>
-    </row>
-    <row r="121" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K120" s="30"/>
+    </row>
+    <row r="121" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A121" s="15" t="s">
         <v>193</v>
       </c>
@@ -6421,9 +6539,9 @@
         <v>490</v>
       </c>
       <c r="J121" s="12"/>
-      <c r="K121" s="31"/>
-    </row>
-    <row r="122" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K121" s="30"/>
+    </row>
+    <row r="122" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A122" s="15" t="s">
         <v>194</v>
       </c>
@@ -6454,7 +6572,7 @@
         <v>334.6</v>
       </c>
       <c r="J122" s="12"/>
-      <c r="K122" s="31"/>
+      <c r="K122" s="30"/>
     </row>
     <row r="123" spans="1:11" ht="21.95" customHeight="1">
       <c r="A123" s="15" t="s">
@@ -6483,9 +6601,9 @@
         <v>0</v>
       </c>
       <c r="J123" s="12"/>
-      <c r="K123" s="31"/>
-    </row>
-    <row r="124" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K123" s="30"/>
+    </row>
+    <row r="124" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A124" s="15" t="s">
         <v>196</v>
       </c>
@@ -6514,9 +6632,9 @@
         <v>0</v>
       </c>
       <c r="J124" s="12"/>
-      <c r="K124" s="31"/>
-    </row>
-    <row r="125" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K124" s="30"/>
+    </row>
+    <row r="125" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A125" s="15" t="s">
         <v>197</v>
       </c>
@@ -6547,7 +6665,7 @@
         <v>336</v>
       </c>
       <c r="J125" s="12"/>
-      <c r="K125" s="31"/>
+      <c r="K125" s="30"/>
     </row>
     <row r="126" spans="1:11" ht="21.95" customHeight="1">
       <c r="A126" s="15" t="s">
@@ -6576,7 +6694,7 @@
         <v>0</v>
       </c>
       <c r="J126" s="12"/>
-      <c r="K126" s="31"/>
+      <c r="K126" s="30"/>
     </row>
     <row r="127" spans="1:11" ht="21.95" customHeight="1">
       <c r="A127" s="15" t="s">
@@ -6605,9 +6723,9 @@
         <v>0</v>
       </c>
       <c r="J127" s="12"/>
-      <c r="K127" s="31"/>
-    </row>
-    <row r="128" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K127" s="30"/>
+    </row>
+    <row r="128" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A128" s="15" t="s">
         <v>200</v>
       </c>
@@ -6636,9 +6754,9 @@
         <v>0</v>
       </c>
       <c r="J128" s="12"/>
-      <c r="K128" s="31"/>
-    </row>
-    <row r="129" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K128" s="30"/>
+    </row>
+    <row r="129" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A129" s="15" t="s">
         <v>201</v>
       </c>
@@ -6669,9 +6787,9 @@
         <v>348.6</v>
       </c>
       <c r="J129" s="12"/>
-      <c r="K129" s="31"/>
-    </row>
-    <row r="130" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K129" s="30"/>
+    </row>
+    <row r="130" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A130" s="15" t="s">
         <v>202</v>
       </c>
@@ -6700,9 +6818,9 @@
         <v>0</v>
       </c>
       <c r="J130" s="12"/>
-      <c r="K130" s="31"/>
-    </row>
-    <row r="131" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K130" s="30"/>
+    </row>
+    <row r="131" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A131" s="15" t="s">
         <v>203</v>
       </c>
@@ -6733,7 +6851,7 @@
         <v>345.1</v>
       </c>
       <c r="J131" s="12"/>
-      <c r="K131" s="31"/>
+      <c r="K131" s="30"/>
     </row>
     <row r="132" spans="1:11" ht="21.95" customHeight="1">
       <c r="A132" s="15" t="s">
@@ -6762,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="12"/>
-      <c r="K132" s="31"/>
+      <c r="K132" s="30"/>
     </row>
     <row r="133" spans="1:11" ht="21.95" customHeight="1">
       <c r="A133" s="15" t="s">
@@ -6791,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="12"/>
-      <c r="K133" s="31"/>
+      <c r="K133" s="30"/>
     </row>
     <row r="134" spans="1:11" ht="21.95" customHeight="1">
       <c r="A134" s="15" t="s">
@@ -6820,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="12"/>
-      <c r="K134" s="31"/>
+      <c r="K134" s="30"/>
     </row>
     <row r="135" spans="1:11" ht="21.95" customHeight="1">
       <c r="A135" s="15" t="s">
@@ -6849,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="12"/>
-      <c r="K135" s="31"/>
+      <c r="K135" s="30"/>
     </row>
     <row r="136" spans="1:11" ht="21.95" customHeight="1">
       <c r="A136" s="15" t="s">
@@ -6880,9 +6998,9 @@
         <v>437.5</v>
       </c>
       <c r="J136" s="12"/>
-      <c r="K136" s="31"/>
-    </row>
-    <row r="137" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K136" s="30"/>
+    </row>
+    <row r="137" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A137" s="15" t="s">
         <v>210</v>
       </c>
@@ -6913,9 +7031,9 @@
         <v>503.3</v>
       </c>
       <c r="J137" s="12"/>
-      <c r="K137" s="31"/>
-    </row>
-    <row r="138" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K137" s="30"/>
+    </row>
+    <row r="138" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A138" s="15" t="s">
         <v>211</v>
       </c>
@@ -6946,7 +7064,7 @@
         <v>545.29999999999995</v>
       </c>
       <c r="J138" s="12"/>
-      <c r="K138" s="31"/>
+      <c r="K138" s="30"/>
     </row>
     <row r="139" spans="1:11" ht="21.95" customHeight="1">
       <c r="A139" s="15" t="s">
@@ -6977,9 +7095,9 @@
         <v>377.3</v>
       </c>
       <c r="J139" s="12"/>
-      <c r="K139" s="31"/>
-    </row>
-    <row r="140" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K139" s="30"/>
+    </row>
+    <row r="140" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A140" s="15" t="s">
         <v>213</v>
       </c>
@@ -7010,9 +7128,9 @@
         <v>545.29999999999995</v>
       </c>
       <c r="J140" s="12"/>
-      <c r="K140" s="31"/>
-    </row>
-    <row r="141" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K140" s="30"/>
+    </row>
+    <row r="141" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A141" s="15" t="s">
         <v>214</v>
       </c>
@@ -7043,9 +7161,9 @@
         <v>629.29999999999995</v>
       </c>
       <c r="J141" s="12"/>
-      <c r="K141" s="31"/>
-    </row>
-    <row r="142" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K141" s="30"/>
+    </row>
+    <row r="142" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A142" s="15" t="s">
         <v>215</v>
       </c>
@@ -7076,9 +7194,9 @@
         <v>385</v>
       </c>
       <c r="J142" s="12"/>
-      <c r="K142" s="31"/>
-    </row>
-    <row r="143" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K142" s="30"/>
+    </row>
+    <row r="143" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A143" s="15" t="s">
         <v>216</v>
       </c>
@@ -7109,9 +7227,9 @@
         <v>476.7</v>
       </c>
       <c r="J143" s="12"/>
-      <c r="K143" s="31"/>
-    </row>
-    <row r="144" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K143" s="30"/>
+    </row>
+    <row r="144" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A144" s="15" t="s">
         <v>217</v>
       </c>
@@ -7142,9 +7260,9 @@
         <v>699.3</v>
       </c>
       <c r="J144" s="12"/>
-      <c r="K144" s="31"/>
-    </row>
-    <row r="145" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K144" s="30"/>
+    </row>
+    <row r="145" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A145" s="15" t="s">
         <v>218</v>
       </c>
@@ -7173,9 +7291,9 @@
         <v>0</v>
       </c>
       <c r="J145" s="12"/>
-      <c r="K145" s="31"/>
-    </row>
-    <row r="146" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K145" s="30"/>
+    </row>
+    <row r="146" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A146" s="15" t="s">
         <v>219</v>
       </c>
@@ -7206,9 +7324,9 @@
         <v>433.3</v>
       </c>
       <c r="J146" s="12"/>
-      <c r="K146" s="31"/>
-    </row>
-    <row r="147" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K146" s="30"/>
+    </row>
+    <row r="147" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A147" s="15" t="s">
         <v>221</v>
       </c>
@@ -7237,9 +7355,9 @@
         <v>0</v>
       </c>
       <c r="J147" s="12"/>
-      <c r="K147" s="31"/>
-    </row>
-    <row r="148" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K147" s="30"/>
+    </row>
+    <row r="148" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A148" s="15" t="s">
         <v>223</v>
       </c>
@@ -7270,9 +7388,9 @@
         <v>328.3</v>
       </c>
       <c r="J148" s="12"/>
-      <c r="K148" s="31"/>
-    </row>
-    <row r="149" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K148" s="30"/>
+    </row>
+    <row r="149" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A149" s="15" t="s">
         <v>224</v>
       </c>
@@ -7303,7 +7421,7 @@
         <v>446.6</v>
       </c>
       <c r="J149" s="12"/>
-      <c r="K149" s="31"/>
+      <c r="K149" s="30"/>
     </row>
     <row r="150" spans="1:11" ht="21.95" customHeight="1">
       <c r="A150" s="15" t="s">
@@ -7334,9 +7452,9 @@
         <v>384.3</v>
       </c>
       <c r="J150" s="12"/>
-      <c r="K150" s="31"/>
-    </row>
-    <row r="151" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K150" s="30"/>
+    </row>
+    <row r="151" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A151" s="15" t="s">
         <v>226</v>
       </c>
@@ -7365,9 +7483,9 @@
         <v>0</v>
       </c>
       <c r="J151" s="12"/>
-      <c r="K151" s="31"/>
-    </row>
-    <row r="152" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K151" s="30"/>
+    </row>
+    <row r="152" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A152" s="15" t="s">
         <v>228</v>
       </c>
@@ -7396,9 +7514,9 @@
         <v>0</v>
       </c>
       <c r="J152" s="12"/>
-      <c r="K152" s="31"/>
-    </row>
-    <row r="153" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K152" s="30"/>
+    </row>
+    <row r="153" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A153" s="15" t="s">
         <v>230</v>
       </c>
@@ -7429,7 +7547,7 @@
         <v>346.5</v>
       </c>
       <c r="J153" s="12"/>
-      <c r="K153" s="31"/>
+      <c r="K153" s="30"/>
     </row>
     <row r="154" spans="1:11" ht="21.95" customHeight="1">
       <c r="A154" s="15" t="s">
@@ -7458,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="J154" s="12"/>
-      <c r="K154" s="31"/>
+      <c r="K154" s="30"/>
     </row>
     <row r="155" spans="1:11" ht="21.95" customHeight="1">
       <c r="A155" s="15" t="s">
@@ -7489,9 +7607,9 @@
         <v>419.3</v>
       </c>
       <c r="J155" s="12"/>
-      <c r="K155" s="31"/>
-    </row>
-    <row r="156" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K155" s="30"/>
+    </row>
+    <row r="156" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A156" s="15" t="s">
         <v>233</v>
       </c>
@@ -7520,9 +7638,9 @@
         <v>0</v>
       </c>
       <c r="J156" s="12"/>
-      <c r="K156" s="31"/>
-    </row>
-    <row r="157" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K156" s="30"/>
+    </row>
+    <row r="157" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A157" s="15" t="s">
         <v>234</v>
       </c>
@@ -7553,7 +7671,7 @@
         <v>435.4</v>
       </c>
       <c r="J157" s="12"/>
-      <c r="K157" s="31"/>
+      <c r="K157" s="30"/>
     </row>
     <row r="158" spans="1:11" ht="21.95" customHeight="1">
       <c r="A158" s="15" t="s">
@@ -7584,7 +7702,7 @@
         <v>419.3</v>
       </c>
       <c r="J158" s="12"/>
-      <c r="K158" s="31"/>
+      <c r="K158" s="30"/>
     </row>
     <row r="159" spans="1:11" ht="21.95" customHeight="1">
       <c r="A159" s="15" t="s">
@@ -7613,7 +7731,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="12"/>
-      <c r="K159" s="31"/>
+      <c r="K159" s="30"/>
     </row>
     <row r="160" spans="1:11" ht="21.95" customHeight="1">
       <c r="A160" s="15" t="s">
@@ -7644,9 +7762,9 @@
         <v>349.3</v>
       </c>
       <c r="J160" s="12"/>
-      <c r="K160" s="31"/>
-    </row>
-    <row r="161" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K160" s="30"/>
+    </row>
+    <row r="161" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A161" s="15" t="s">
         <v>239</v>
       </c>
@@ -7677,9 +7795,9 @@
         <v>188.3</v>
       </c>
       <c r="J161" s="12"/>
-      <c r="K161" s="31"/>
-    </row>
-    <row r="162" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K161" s="30"/>
+    </row>
+    <row r="162" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A162" s="15" t="s">
         <v>240</v>
       </c>
@@ -7710,7 +7828,7 @@
         <v>293.3</v>
       </c>
       <c r="J162" s="12"/>
-      <c r="K162" s="31"/>
+      <c r="K162" s="30"/>
     </row>
     <row r="163" spans="1:11" ht="21.95" customHeight="1">
       <c r="A163" s="15" t="s">
@@ -7741,9 +7859,9 @@
         <v/>
       </c>
       <c r="J163" s="12"/>
-      <c r="K163" s="31"/>
-    </row>
-    <row r="164" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K163" s="30"/>
+    </row>
+    <row r="164" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A164" s="15" t="s">
         <v>244</v>
       </c>
@@ -7774,7 +7892,7 @@
         <v>419.3</v>
       </c>
       <c r="J164" s="12"/>
-      <c r="K164" s="31"/>
+      <c r="K164" s="30"/>
     </row>
     <row r="165" spans="1:11" ht="21.95" customHeight="1">
       <c r="A165" s="15" t="s">
@@ -7805,9 +7923,9 @@
         <v>269.5</v>
       </c>
       <c r="J165" s="12"/>
-      <c r="K165" s="31"/>
-    </row>
-    <row r="166" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K165" s="30"/>
+    </row>
+    <row r="166" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A166" s="15" t="s">
         <v>247</v>
       </c>
@@ -7836,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="J166" s="12"/>
-      <c r="K166" s="31"/>
+      <c r="K166" s="30"/>
     </row>
     <row r="167" spans="1:11" ht="21.95" customHeight="1">
       <c r="A167" s="15" t="s">
@@ -7865,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="J167" s="12"/>
-      <c r="K167" s="31"/>
+      <c r="K167" s="30"/>
     </row>
     <row r="168" spans="1:11" ht="21.95" customHeight="1">
       <c r="A168" s="15" t="s">
@@ -7896,9 +8014,9 @@
         <v>300.3</v>
       </c>
       <c r="J168" s="12"/>
-      <c r="K168" s="31"/>
-    </row>
-    <row r="169" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K168" s="30"/>
+    </row>
+    <row r="169" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A169" s="15" t="s">
         <v>250</v>
       </c>
@@ -7927,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="J169" s="12"/>
-      <c r="K169" s="31"/>
+      <c r="K169" s="30"/>
     </row>
     <row r="170" spans="1:11" ht="21.95" customHeight="1">
       <c r="A170" s="15" t="s">
@@ -7958,7 +8076,7 @@
         <v>332.5</v>
       </c>
       <c r="J170" s="12"/>
-      <c r="K170" s="31"/>
+      <c r="K170" s="30"/>
     </row>
     <row r="171" spans="1:11" ht="21.95" customHeight="1">
       <c r="A171" s="15" t="s">
@@ -7987,9 +8105,9 @@
         <v>0</v>
       </c>
       <c r="J171" s="12"/>
-      <c r="K171" s="31"/>
-    </row>
-    <row r="172" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K171" s="30"/>
+    </row>
+    <row r="172" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A172" s="15" t="s">
         <v>254</v>
       </c>
@@ -8020,9 +8138,9 @@
         <v>391.3</v>
       </c>
       <c r="J172" s="12"/>
-      <c r="K172" s="31"/>
-    </row>
-    <row r="173" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K172" s="30"/>
+    </row>
+    <row r="173" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A173" s="15" t="s">
         <v>255</v>
       </c>
@@ -8051,7 +8169,7 @@
         <v>0</v>
       </c>
       <c r="J173" s="12"/>
-      <c r="K173" s="31"/>
+      <c r="K173" s="30"/>
     </row>
     <row r="174" spans="1:11" ht="21.95" customHeight="1">
       <c r="A174" s="15" t="s">
@@ -8082,7 +8200,7 @@
         <v>494.2</v>
       </c>
       <c r="J174" s="12"/>
-      <c r="K174" s="31"/>
+      <c r="K174" s="30"/>
     </row>
     <row r="175" spans="1:11" ht="21.95" customHeight="1">
       <c r="A175" s="15" t="s">
@@ -8111,9 +8229,9 @@
         <v>0</v>
       </c>
       <c r="J175" s="12"/>
-      <c r="K175" s="31"/>
-    </row>
-    <row r="176" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K175" s="30"/>
+    </row>
+    <row r="176" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A176" s="15" t="s">
         <v>258</v>
       </c>
@@ -8144,9 +8262,9 @@
         <v>395.5</v>
       </c>
       <c r="J176" s="12"/>
-      <c r="K176" s="31"/>
-    </row>
-    <row r="177" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K176" s="30"/>
+    </row>
+    <row r="177" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A177" s="15" t="s">
         <v>262</v>
       </c>
@@ -8177,9 +8295,9 @@
         <v>139.30000000000001</v>
       </c>
       <c r="J177" s="12"/>
-      <c r="K177" s="31"/>
-    </row>
-    <row r="178" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K177" s="30"/>
+    </row>
+    <row r="178" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A178" s="15" t="s">
         <v>263</v>
       </c>
@@ -8210,7 +8328,7 @@
         <v>265.3</v>
       </c>
       <c r="J178" s="12"/>
-      <c r="K178" s="31"/>
+      <c r="K178" s="30"/>
     </row>
     <row r="179" spans="1:11" ht="21.95" customHeight="1">
       <c r="A179" s="15" t="s">
@@ -8240,8 +8358,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B179,İndirimler!$B$2:$B$110,C179)&gt;0,ROUND(G179*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B179,İndirimler!$B$2:$B$110,C179)),2),"")</f>
         <v>377.3</v>
       </c>
-      <c r="J179" s="12"/>
-      <c r="K179" s="31"/>
+      <c r="J179" s="32" t="s">
+        <v>673</v>
+      </c>
+      <c r="K179" s="30"/>
     </row>
     <row r="180" spans="1:11" ht="21.95" customHeight="1">
       <c r="A180" s="15" t="s">
@@ -8272,9 +8392,9 @@
         <v>479.5</v>
       </c>
       <c r="J180" s="12"/>
-      <c r="K180" s="31"/>
-    </row>
-    <row r="181" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K180" s="30"/>
+    </row>
+    <row r="181" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A181" s="15" t="s">
         <v>266</v>
       </c>
@@ -8305,9 +8425,9 @@
         <v>334.6</v>
       </c>
       <c r="J181" s="12"/>
-      <c r="K181" s="31"/>
-    </row>
-    <row r="182" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K181" s="30"/>
+    </row>
+    <row r="182" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A182" s="15" t="s">
         <v>268</v>
       </c>
@@ -8336,9 +8456,9 @@
         <v>0</v>
       </c>
       <c r="J182" s="12"/>
-      <c r="K182" s="31"/>
-    </row>
-    <row r="183" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K182" s="30"/>
+    </row>
+    <row r="183" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A183" s="15" t="s">
         <v>269</v>
       </c>
@@ -8371,7 +8491,7 @@
       <c r="J183" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="K183" s="31"/>
+      <c r="K183" s="30"/>
     </row>
     <row r="184" spans="1:11" ht="21.95" customHeight="1">
       <c r="A184" s="15" t="s">
@@ -8402,9 +8522,9 @@
         <v>403.2</v>
       </c>
       <c r="J184" s="12"/>
-      <c r="K184" s="31"/>
-    </row>
-    <row r="185" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K184" s="30"/>
+    </row>
+    <row r="185" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A185" s="15" t="s">
         <v>272</v>
       </c>
@@ -8435,7 +8555,7 @@
         <v>462</v>
       </c>
       <c r="J185" s="12"/>
-      <c r="K185" s="31"/>
+      <c r="K185" s="30"/>
     </row>
     <row r="186" spans="1:11" ht="21.95" customHeight="1">
       <c r="A186" s="15" t="s">
@@ -8466,7 +8586,7 @@
         <v>367.5</v>
       </c>
       <c r="J186" s="12"/>
-      <c r="K186" s="31"/>
+      <c r="K186" s="30"/>
     </row>
     <row r="187" spans="1:11" ht="21.95" customHeight="1">
       <c r="A187" s="15" t="s">
@@ -8499,7 +8619,7 @@
       <c r="J187" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="K187" s="31"/>
+      <c r="K187" s="30"/>
     </row>
     <row r="188" spans="1:11" ht="21.95" customHeight="1">
       <c r="A188" s="15" t="s">
@@ -8530,7 +8650,7 @@
         <v>291.2</v>
       </c>
       <c r="J188" s="12"/>
-      <c r="K188" s="31"/>
+      <c r="K188" s="30"/>
     </row>
     <row r="189" spans="1:11" ht="21.95" customHeight="1">
       <c r="A189" s="15" t="s">
@@ -8560,8 +8680,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B189,İndirimler!$B$2:$B$110,C189)&gt;0,ROUND(G189*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B189,İndirimler!$B$2:$B$110,C189)),2),"")</f>
         <v>335.3</v>
       </c>
-      <c r="J189" s="12"/>
-      <c r="K189" s="31"/>
+      <c r="J189" s="32" t="s">
+        <v>684</v>
+      </c>
+      <c r="K189" s="30"/>
     </row>
     <row r="190" spans="1:11" ht="21.95" customHeight="1">
       <c r="A190" s="15" t="s">
@@ -8592,9 +8714,9 @@
         <v>300.3</v>
       </c>
       <c r="J190" s="12"/>
-      <c r="K190" s="31"/>
-    </row>
-    <row r="191" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K190" s="30"/>
+    </row>
+    <row r="191" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A191" s="15" t="s">
         <v>281</v>
       </c>
@@ -8627,7 +8749,7 @@
       <c r="J191" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="K191" s="31"/>
+      <c r="K191" s="30"/>
     </row>
     <row r="192" spans="1:11" ht="21.95" customHeight="1">
       <c r="A192" s="15" t="s">
@@ -8656,11 +8778,11 @@
         <v>0</v>
       </c>
       <c r="J192" s="12"/>
-      <c r="K192" s="31" t="s">
+      <c r="K192" s="30" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="21.95" customHeight="1">
+    <row r="193" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A193" s="15" t="s">
         <v>285</v>
       </c>
@@ -8691,7 +8813,7 @@
         <v>349.3</v>
       </c>
       <c r="J193" s="12"/>
-      <c r="K193" s="31"/>
+      <c r="K193" s="30"/>
     </row>
     <row r="194" spans="1:11" ht="21.95" customHeight="1">
       <c r="A194" s="15" t="s">
@@ -8722,9 +8844,9 @@
         <v>392</v>
       </c>
       <c r="J194" s="12"/>
-      <c r="K194" s="31"/>
-    </row>
-    <row r="195" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K194" s="30"/>
+    </row>
+    <row r="195" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A195" s="15" t="s">
         <v>287</v>
       </c>
@@ -8755,9 +8877,9 @@
         <v>382.2</v>
       </c>
       <c r="J195" s="12"/>
-      <c r="K195" s="31"/>
-    </row>
-    <row r="196" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K195" s="30"/>
+    </row>
+    <row r="196" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A196" s="15" t="s">
         <v>288</v>
       </c>
@@ -8788,7 +8910,7 @@
         <v>286.3</v>
       </c>
       <c r="J196" s="12"/>
-      <c r="K196" s="31"/>
+      <c r="K196" s="30"/>
     </row>
     <row r="197" spans="1:11" ht="21.95" customHeight="1">
       <c r="A197" s="15" t="s">
@@ -8819,9 +8941,9 @@
         <v>318.5</v>
       </c>
       <c r="J197" s="12"/>
-      <c r="K197" s="31"/>
-    </row>
-    <row r="198" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K197" s="30"/>
+    </row>
+    <row r="198" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A198" s="15" t="s">
         <v>290</v>
       </c>
@@ -8852,11 +8974,11 @@
         <v>430.5</v>
       </c>
       <c r="J198" s="12"/>
-      <c r="K198" s="31" t="s">
+      <c r="K198" s="30" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="21.95" customHeight="1">
+    <row r="199" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A199" s="15" t="s">
         <v>292</v>
       </c>
@@ -8887,7 +9009,7 @@
         <v>430.5</v>
       </c>
       <c r="J199" s="12"/>
-      <c r="K199" s="31"/>
+      <c r="K199" s="30"/>
     </row>
     <row r="200" spans="1:11" ht="21.95" customHeight="1">
       <c r="A200" s="15" t="s">
@@ -8917,8 +9039,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B200,İndirimler!$B$2:$B$110,C200)&gt;0,ROUND(G200*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B200,İndirimler!$B$2:$B$110,C200)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J200" s="12"/>
-      <c r="K200" s="31"/>
+      <c r="J200" s="32" t="s">
+        <v>679</v>
+      </c>
+      <c r="K200" s="30"/>
     </row>
     <row r="201" spans="1:11" ht="21.95" customHeight="1">
       <c r="A201" s="15" t="s">
@@ -8949,9 +9073,9 @@
         <v>577.5</v>
       </c>
       <c r="J201" s="12"/>
-      <c r="K201" s="31"/>
-    </row>
-    <row r="202" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K201" s="30"/>
+    </row>
+    <row r="202" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A202" s="15" t="s">
         <v>295</v>
       </c>
@@ -8982,9 +9106,9 @@
         <v>399</v>
       </c>
       <c r="J202" s="12"/>
-      <c r="K202" s="31"/>
-    </row>
-    <row r="203" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K202" s="30"/>
+    </row>
+    <row r="203" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A203" s="15" t="s">
         <v>296</v>
       </c>
@@ -9013,9 +9137,9 @@
         <v>0</v>
       </c>
       <c r="J203" s="12"/>
-      <c r="K203" s="31"/>
-    </row>
-    <row r="204" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K203" s="30"/>
+    </row>
+    <row r="204" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A204" s="15" t="s">
         <v>297</v>
       </c>
@@ -9048,7 +9172,7 @@
       <c r="J204" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="K204" s="31"/>
+      <c r="K204" s="30"/>
     </row>
     <row r="205" spans="1:11" ht="21.95" customHeight="1">
       <c r="A205" s="15" t="s">
@@ -9079,9 +9203,9 @@
         <v>425.6</v>
       </c>
       <c r="J205" s="12"/>
-      <c r="K205" s="31"/>
-    </row>
-    <row r="206" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K205" s="30"/>
+    </row>
+    <row r="206" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A206" s="15" t="s">
         <v>300</v>
       </c>
@@ -9112,7 +9236,7 @@
         <v>378</v>
       </c>
       <c r="J206" s="12"/>
-      <c r="K206" s="31"/>
+      <c r="K206" s="30"/>
     </row>
     <row r="207" spans="1:11" ht="21.95" customHeight="1">
       <c r="A207" s="15" t="s">
@@ -9143,7 +9267,7 @@
         <v>388.5</v>
       </c>
       <c r="J207" s="12"/>
-      <c r="K207" s="31"/>
+      <c r="K207" s="30"/>
     </row>
     <row r="208" spans="1:11" ht="21.95" customHeight="1">
       <c r="A208" s="15" t="s">
@@ -9176,7 +9300,7 @@
       <c r="J208" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="K208" s="31"/>
+      <c r="K208" s="30"/>
     </row>
     <row r="209" spans="1:11" ht="21.95" customHeight="1">
       <c r="A209" s="15" t="s">
@@ -9207,7 +9331,7 @@
         <v>369.6</v>
       </c>
       <c r="J209" s="12"/>
-      <c r="K209" s="31"/>
+      <c r="K209" s="30"/>
     </row>
     <row r="210" spans="1:11" ht="21.95" customHeight="1">
       <c r="A210" s="15" t="s">
@@ -9237,8 +9361,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B210,İndirimler!$B$2:$B$110,C210)&gt;0,ROUND(G210*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B210,İndirimler!$B$2:$B$110,C210)),2),"")</f>
         <v>363.3</v>
       </c>
-      <c r="J210" s="12"/>
-      <c r="K210" s="31"/>
+      <c r="J210" s="32" t="s">
+        <v>691</v>
+      </c>
+      <c r="K210" s="30"/>
     </row>
     <row r="211" spans="1:11" ht="21.95" customHeight="1">
       <c r="A211" s="15" t="s">
@@ -9269,7 +9395,7 @@
         <v>335.3</v>
       </c>
       <c r="J211" s="12"/>
-      <c r="K211" s="31"/>
+      <c r="K211" s="30"/>
     </row>
     <row r="212" spans="1:11" ht="21.95" customHeight="1">
       <c r="A212" s="15" t="s">
@@ -9300,9 +9426,9 @@
         <v>335.3</v>
       </c>
       <c r="J212" s="12"/>
-      <c r="K212" s="31"/>
-    </row>
-    <row r="213" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K212" s="30"/>
+    </row>
+    <row r="213" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A213" s="15" t="s">
         <v>308</v>
       </c>
@@ -9335,7 +9461,7 @@
       <c r="J213" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="K213" s="31"/>
+      <c r="K213" s="30"/>
     </row>
     <row r="214" spans="1:11" ht="21.95" customHeight="1">
       <c r="A214" s="15" t="s">
@@ -9364,11 +9490,11 @@
         <v>0</v>
       </c>
       <c r="J214" s="12"/>
-      <c r="K214" s="31" t="s">
+      <c r="K214" s="30" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="21.95" customHeight="1">
+    <row r="215" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A215" s="15" t="s">
         <v>312</v>
       </c>
@@ -9399,7 +9525,7 @@
         <v>367.5</v>
       </c>
       <c r="J215" s="12"/>
-      <c r="K215" s="31"/>
+      <c r="K215" s="30"/>
     </row>
     <row r="216" spans="1:11" ht="21.95" customHeight="1">
       <c r="A216" s="15" t="s">
@@ -9430,9 +9556,9 @@
         <v>413</v>
       </c>
       <c r="J216" s="12"/>
-      <c r="K216" s="31"/>
-    </row>
-    <row r="217" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K216" s="30"/>
+    </row>
+    <row r="217" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A217" s="15" t="s">
         <v>314</v>
       </c>
@@ -9463,9 +9589,9 @@
         <v>320.60000000000002</v>
       </c>
       <c r="J217" s="12"/>
-      <c r="K217" s="31"/>
-    </row>
-    <row r="218" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K217" s="30"/>
+    </row>
+    <row r="218" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A218" s="15" t="s">
         <v>315</v>
       </c>
@@ -9496,7 +9622,7 @@
         <v>353.5</v>
       </c>
       <c r="J218" s="12"/>
-      <c r="K218" s="31"/>
+      <c r="K218" s="30"/>
     </row>
     <row r="219" spans="1:11" ht="21.95" customHeight="1">
       <c r="A219" s="15" t="s">
@@ -9527,9 +9653,9 @@
         <v>318.5</v>
       </c>
       <c r="J219" s="12"/>
-      <c r="K219" s="31"/>
-    </row>
-    <row r="220" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K219" s="30"/>
+    </row>
+    <row r="220" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A220" s="15" t="s">
         <v>317</v>
       </c>
@@ -9558,7 +9684,7 @@
         <v>0</v>
       </c>
       <c r="J220" s="12"/>
-      <c r="K220" s="31"/>
+      <c r="K220" s="30"/>
     </row>
     <row r="221" spans="1:11" ht="21.95" customHeight="1">
       <c r="A221" s="15" t="s">
@@ -9587,9 +9713,9 @@
         <v>0</v>
       </c>
       <c r="J221" s="12"/>
-      <c r="K221" s="31"/>
-    </row>
-    <row r="222" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K221" s="30"/>
+    </row>
+    <row r="222" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A222" s="15" t="s">
         <v>319</v>
       </c>
@@ -9620,9 +9746,9 @@
         <v>541.1</v>
       </c>
       <c r="J222" s="12"/>
-      <c r="K222" s="31"/>
-    </row>
-    <row r="223" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K222" s="30"/>
+    </row>
+    <row r="223" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A223" s="15" t="s">
         <v>320</v>
       </c>
@@ -9651,9 +9777,9 @@
         <v>0</v>
       </c>
       <c r="J223" s="12"/>
-      <c r="K223" s="31"/>
-    </row>
-    <row r="224" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K223" s="30"/>
+    </row>
+    <row r="224" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A224" s="15" t="s">
         <v>321</v>
       </c>
@@ -9682,7 +9808,7 @@
         <v>0</v>
       </c>
       <c r="J224" s="12"/>
-      <c r="K224" s="31"/>
+      <c r="K224" s="30"/>
     </row>
     <row r="225" spans="1:11" ht="21.95" customHeight="1">
       <c r="A225" s="15" t="s">
@@ -9713,9 +9839,9 @@
         <v>343</v>
       </c>
       <c r="J225" s="12"/>
-      <c r="K225" s="31"/>
-    </row>
-    <row r="226" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K225" s="30"/>
+    </row>
+    <row r="226" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A226" s="15" t="s">
         <v>323</v>
       </c>
@@ -9746,7 +9872,7 @@
         <v>336</v>
       </c>
       <c r="J226" s="12"/>
-      <c r="K226" s="31"/>
+      <c r="K226" s="30"/>
     </row>
     <row r="227" spans="1:11" ht="21.95" customHeight="1">
       <c r="A227" s="15" t="s">
@@ -9777,7 +9903,7 @@
         <v>348.6</v>
       </c>
       <c r="J227" s="12"/>
-      <c r="K227" s="31"/>
+      <c r="K227" s="30"/>
     </row>
     <row r="228" spans="1:11" ht="21.95" customHeight="1">
       <c r="A228" s="15" t="s">
@@ -9808,7 +9934,7 @@
         <v>470.4</v>
       </c>
       <c r="J228" s="12"/>
-      <c r="K228" s="31"/>
+      <c r="K228" s="30"/>
     </row>
     <row r="229" spans="1:11" ht="21.95" customHeight="1">
       <c r="A229" s="15" t="s">
@@ -9837,7 +9963,7 @@
         <v>0</v>
       </c>
       <c r="J229" s="12"/>
-      <c r="K229" s="31"/>
+      <c r="K229" s="30"/>
     </row>
     <row r="230" spans="1:11" ht="21.95" customHeight="1">
       <c r="A230" s="15" t="s">
@@ -9866,7 +9992,7 @@
         <v>0</v>
       </c>
       <c r="J230" s="12"/>
-      <c r="K230" s="31"/>
+      <c r="K230" s="30"/>
     </row>
     <row r="231" spans="1:11" ht="21.95" customHeight="1">
       <c r="A231" s="15" t="s">
@@ -9895,7 +10021,7 @@
         <v>0</v>
       </c>
       <c r="J231" s="12"/>
-      <c r="K231" s="31"/>
+      <c r="K231" s="30"/>
     </row>
     <row r="232" spans="1:11" ht="21.95" customHeight="1">
       <c r="A232" s="15" t="s">
@@ -9924,9 +10050,9 @@
         <v>0</v>
       </c>
       <c r="J232" s="12"/>
-      <c r="K232" s="31"/>
-    </row>
-    <row r="233" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K232" s="30"/>
+    </row>
+    <row r="233" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A233" s="15" t="s">
         <v>330</v>
       </c>
@@ -9955,7 +10081,7 @@
         <v>0</v>
       </c>
       <c r="J233" s="12"/>
-      <c r="K233" s="31"/>
+      <c r="K233" s="30"/>
     </row>
     <row r="234" spans="1:11" ht="21.95" customHeight="1">
       <c r="A234" s="15" t="s">
@@ -9986,9 +10112,9 @@
         <v>348.6</v>
       </c>
       <c r="J234" s="12"/>
-      <c r="K234" s="31"/>
-    </row>
-    <row r="235" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K234" s="30"/>
+    </row>
+    <row r="235" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A235" s="15" t="s">
         <v>332</v>
       </c>
@@ -10019,7 +10145,7 @@
         <v>270.89999999999998</v>
       </c>
       <c r="J235" s="12"/>
-      <c r="K235" s="31"/>
+      <c r="K235" s="30"/>
     </row>
     <row r="236" spans="1:11" ht="21.95" customHeight="1">
       <c r="A236" s="15" t="s">
@@ -10048,7 +10174,7 @@
         <v>0</v>
       </c>
       <c r="J236" s="12"/>
-      <c r="K236" s="31"/>
+      <c r="K236" s="30"/>
     </row>
     <row r="237" spans="1:11" ht="21.95" customHeight="1">
       <c r="A237" s="15" t="s">
@@ -10077,9 +10203,9 @@
         <v>0</v>
       </c>
       <c r="J237" s="12"/>
-      <c r="K237" s="31"/>
-    </row>
-    <row r="238" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K237" s="30"/>
+    </row>
+    <row r="238" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A238" s="15" t="s">
         <v>335</v>
       </c>
@@ -10110,9 +10236,9 @@
         <v>279.3</v>
       </c>
       <c r="J238" s="12"/>
-      <c r="K238" s="31"/>
-    </row>
-    <row r="239" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K238" s="30"/>
+    </row>
+    <row r="239" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A239" s="15" t="s">
         <v>336</v>
       </c>
@@ -10143,9 +10269,9 @@
         <v>139.30000000000001</v>
       </c>
       <c r="J239" s="12"/>
-      <c r="K239" s="31"/>
-    </row>
-    <row r="240" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K239" s="30"/>
+    </row>
+    <row r="240" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A240" s="15" t="s">
         <v>337</v>
       </c>
@@ -10176,9 +10302,9 @@
         <v>479.5</v>
       </c>
       <c r="J240" s="12"/>
-      <c r="K240" s="31"/>
-    </row>
-    <row r="241" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K240" s="30"/>
+    </row>
+    <row r="241" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A241" s="15" t="s">
         <v>338</v>
       </c>
@@ -10209,9 +10335,9 @@
         <v>479.5</v>
       </c>
       <c r="J241" s="12"/>
-      <c r="K241" s="31"/>
-    </row>
-    <row r="242" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K241" s="30"/>
+    </row>
+    <row r="242" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A242" s="15" t="s">
         <v>339</v>
       </c>
@@ -10242,9 +10368,9 @@
         <v>243.6</v>
       </c>
       <c r="J242" s="12"/>
-      <c r="K242" s="31"/>
-    </row>
-    <row r="243" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K242" s="30"/>
+    </row>
+    <row r="243" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A243" s="15" t="s">
         <v>340</v>
       </c>
@@ -10275,7 +10401,7 @@
         <v>299.60000000000002</v>
       </c>
       <c r="J243" s="12"/>
-      <c r="K243" s="31"/>
+      <c r="K243" s="30"/>
     </row>
     <row r="244" spans="1:11" ht="21.95" customHeight="1">
       <c r="A244" s="15" t="s">
@@ -10306,7 +10432,7 @@
         <v>253.4</v>
       </c>
       <c r="J244" s="12"/>
-      <c r="K244" s="31"/>
+      <c r="K244" s="30"/>
     </row>
     <row r="245" spans="1:11" ht="21.95" customHeight="1">
       <c r="A245" s="15" t="s">
@@ -10337,7 +10463,7 @@
         <v>236.6</v>
       </c>
       <c r="J245" s="12"/>
-      <c r="K245" s="31"/>
+      <c r="K245" s="30"/>
     </row>
     <row r="246" spans="1:11" ht="21.95" customHeight="1">
       <c r="A246" s="15" t="s">
@@ -10368,7 +10494,7 @@
         <v>423.5</v>
       </c>
       <c r="J246" s="12"/>
-      <c r="K246" s="31"/>
+      <c r="K246" s="30"/>
     </row>
     <row r="247" spans="1:11" ht="21.95" customHeight="1">
       <c r="A247" s="15" t="s">
@@ -10399,7 +10525,7 @@
         <v>349.3</v>
       </c>
       <c r="J247" s="12"/>
-      <c r="K247" s="31"/>
+      <c r="K247" s="30"/>
     </row>
     <row r="248" spans="1:11" ht="21.95" customHeight="1">
       <c r="A248" s="15" t="s">
@@ -10428,7 +10554,7 @@
         <v>0</v>
       </c>
       <c r="J248" s="12"/>
-      <c r="K248" s="31"/>
+      <c r="K248" s="30"/>
     </row>
     <row r="249" spans="1:11" ht="21.95" customHeight="1">
       <c r="A249" s="15" t="s">
@@ -10457,7 +10583,7 @@
         <v>0</v>
       </c>
       <c r="J249" s="12"/>
-      <c r="K249" s="31"/>
+      <c r="K249" s="30"/>
     </row>
     <row r="250" spans="1:11" ht="21.95" customHeight="1">
       <c r="A250" s="15" t="s">
@@ -10488,9 +10614,9 @@
         <v>334.6</v>
       </c>
       <c r="J250" s="12"/>
-      <c r="K250" s="31"/>
-    </row>
-    <row r="251" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K250" s="30"/>
+    </row>
+    <row r="251" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A251" s="15" t="s">
         <v>348</v>
       </c>
@@ -10519,7 +10645,7 @@
         <v>0</v>
       </c>
       <c r="J251" s="12"/>
-      <c r="K251" s="31"/>
+      <c r="K251" s="30"/>
     </row>
     <row r="252" spans="1:11" ht="21.95" customHeight="1">
       <c r="A252" s="15" t="s">
@@ -10550,7 +10676,7 @@
         <v>352.8</v>
       </c>
       <c r="J252" s="12"/>
-      <c r="K252" s="31"/>
+      <c r="K252" s="30"/>
     </row>
     <row r="253" spans="1:11" ht="21.95" customHeight="1">
       <c r="A253" s="15" t="s">
@@ -10581,7 +10707,7 @@
         <v>349.3</v>
       </c>
       <c r="J253" s="12"/>
-      <c r="K253" s="31"/>
+      <c r="K253" s="30"/>
     </row>
     <row r="254" spans="1:11" ht="21.95" customHeight="1">
       <c r="A254" s="15" t="s">
@@ -10610,9 +10736,9 @@
         <v>0</v>
       </c>
       <c r="J254" s="12"/>
-      <c r="K254" s="31"/>
-    </row>
-    <row r="255" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K254" s="30"/>
+    </row>
+    <row r="255" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A255" s="15" t="s">
         <v>352</v>
       </c>
@@ -10643,9 +10769,9 @@
         <v>255.5</v>
       </c>
       <c r="J255" s="12"/>
-      <c r="K255" s="31"/>
-    </row>
-    <row r="256" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K255" s="30"/>
+    </row>
+    <row r="256" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A256" s="15" t="s">
         <v>353</v>
       </c>
@@ -10676,7 +10802,7 @@
         <v>454.3</v>
       </c>
       <c r="J256" s="12"/>
-      <c r="K256" s="31"/>
+      <c r="K256" s="30"/>
     </row>
     <row r="257" spans="1:11" ht="21.95" customHeight="1">
       <c r="A257" s="15" t="s">
@@ -10706,8 +10832,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B257,İndirimler!$B$2:$B$110,C257)&gt;0,ROUND(G257*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B257,İndirimler!$B$2:$B$110,C257)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J257" s="12"/>
-      <c r="K257" s="31"/>
+      <c r="J257" s="32" t="s">
+        <v>674</v>
+      </c>
+      <c r="K257" s="30"/>
     </row>
     <row r="258" spans="1:11" ht="21.95" customHeight="1">
       <c r="A258" s="15" t="s">
@@ -10738,9 +10866,9 @@
         <v>430.5</v>
       </c>
       <c r="J258" s="12"/>
-      <c r="K258" s="31"/>
-    </row>
-    <row r="259" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K258" s="30"/>
+    </row>
+    <row r="259" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A259" s="15" t="s">
         <v>359</v>
       </c>
@@ -10771,9 +10899,9 @@
         <v>360.5</v>
       </c>
       <c r="J259" s="12"/>
-      <c r="K259" s="31"/>
-    </row>
-    <row r="260" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K259" s="30"/>
+    </row>
+    <row r="260" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A260" s="15" t="s">
         <v>360</v>
       </c>
@@ -10802,9 +10930,9 @@
         <v>0</v>
       </c>
       <c r="J260" s="12"/>
-      <c r="K260" s="31"/>
-    </row>
-    <row r="261" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K260" s="30"/>
+    </row>
+    <row r="261" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A261" s="15" t="s">
         <v>361</v>
       </c>
@@ -10837,7 +10965,7 @@
       <c r="J261" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="K261" s="31"/>
+      <c r="K261" s="30"/>
     </row>
     <row r="262" spans="1:11" ht="21.95" customHeight="1">
       <c r="A262" s="15" t="s">
@@ -10868,9 +10996,9 @@
         <v>383.6</v>
       </c>
       <c r="J262" s="12"/>
-      <c r="K262" s="31"/>
-    </row>
-    <row r="263" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K262" s="30"/>
+    </row>
+    <row r="263" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A263" s="15" t="s">
         <v>364</v>
       </c>
@@ -10901,7 +11029,7 @@
         <v>504</v>
       </c>
       <c r="J263" s="12"/>
-      <c r="K263" s="31"/>
+      <c r="K263" s="30"/>
     </row>
     <row r="264" spans="1:11" ht="21.95" customHeight="1">
       <c r="A264" s="15" t="s">
@@ -10930,7 +11058,7 @@
         <v>0</v>
       </c>
       <c r="J264" s="12"/>
-      <c r="K264" s="31"/>
+      <c r="K264" s="30"/>
     </row>
     <row r="265" spans="1:11" ht="21.95" customHeight="1">
       <c r="A265" s="15" t="s">
@@ -10963,7 +11091,7 @@
       <c r="J265" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="K265" s="31"/>
+      <c r="K265" s="30"/>
     </row>
     <row r="266" spans="1:11" ht="21.95" customHeight="1">
       <c r="A266" s="15" t="s">
@@ -10994,7 +11122,7 @@
         <v>414.4</v>
       </c>
       <c r="J266" s="12"/>
-      <c r="K266" s="31"/>
+      <c r="K266" s="30"/>
     </row>
     <row r="267" spans="1:11" ht="21.95" customHeight="1">
       <c r="A267" s="15" t="s">
@@ -11024,10 +11152,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B267,İndirimler!$B$2:$B$110,C267)&gt;0,ROUND(G267*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B267,İndirimler!$B$2:$B$110,C267)),2),"")</f>
         <v>335.3</v>
       </c>
-      <c r="J267" s="12"/>
-      <c r="K267" s="31"/>
-    </row>
-    <row r="268" spans="1:11" ht="21.95" customHeight="1">
+      <c r="J267" s="32" t="s">
+        <v>685</v>
+      </c>
+      <c r="K267" s="30"/>
+    </row>
+    <row r="268" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A268" s="15" t="s">
         <v>371</v>
       </c>
@@ -11060,9 +11190,9 @@
       <c r="J268" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="K268" s="31"/>
-    </row>
-    <row r="269" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K268" s="30"/>
+    </row>
+    <row r="269" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A269" s="15" t="s">
         <v>373</v>
       </c>
@@ -11093,7 +11223,7 @@
         <v>332.5</v>
       </c>
       <c r="J269" s="12"/>
-      <c r="K269" s="31"/>
+      <c r="K269" s="30"/>
     </row>
     <row r="270" spans="1:11" ht="21.95" customHeight="1">
       <c r="A270" s="15" t="s">
@@ -11124,9 +11254,9 @@
         <v>383.6</v>
       </c>
       <c r="J270" s="12"/>
-      <c r="K270" s="31"/>
-    </row>
-    <row r="271" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K270" s="30"/>
+    </row>
+    <row r="271" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A271" s="15" t="s">
         <v>375</v>
       </c>
@@ -11157,7 +11287,7 @@
         <v>357</v>
       </c>
       <c r="J271" s="12"/>
-      <c r="K271" s="31"/>
+      <c r="K271" s="30"/>
     </row>
     <row r="272" spans="1:11" ht="21.95" customHeight="1">
       <c r="A272" s="15" t="s">
@@ -11188,9 +11318,9 @@
         <v>314.3</v>
       </c>
       <c r="J272" s="12"/>
-      <c r="K272" s="31"/>
-    </row>
-    <row r="273" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K272" s="30"/>
+    </row>
+    <row r="273" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A273" s="15" t="s">
         <v>377</v>
       </c>
@@ -11221,7 +11351,7 @@
         <v>241.5</v>
       </c>
       <c r="J273" s="12"/>
-      <c r="K273" s="31"/>
+      <c r="K273" s="30"/>
     </row>
     <row r="274" spans="1:11" ht="21.95" customHeight="1">
       <c r="A274" s="15" t="s">
@@ -11252,9 +11382,9 @@
         <v>286.3</v>
       </c>
       <c r="J274" s="12"/>
-      <c r="K274" s="31"/>
-    </row>
-    <row r="275" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K274" s="30"/>
+    </row>
+    <row r="275" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A275" s="15" t="s">
         <v>379</v>
       </c>
@@ -11285,7 +11415,7 @@
         <v>437.5</v>
       </c>
       <c r="J275" s="12"/>
-      <c r="K275" s="31"/>
+      <c r="K275" s="30"/>
     </row>
     <row r="276" spans="1:11" ht="21.95" customHeight="1">
       <c r="A276" s="15" t="s">
@@ -11315,8 +11445,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B276,İndirimler!$B$2:$B$110,C276)&gt;0,ROUND(G276*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B276,İndirimler!$B$2:$B$110,C276)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J276" s="12"/>
-      <c r="K276" s="31"/>
+      <c r="J276" s="32" t="s">
+        <v>680</v>
+      </c>
+      <c r="K276" s="30"/>
     </row>
     <row r="277" spans="1:11" ht="21.95" customHeight="1">
       <c r="A277" s="15" t="s">
@@ -11347,9 +11479,9 @@
         <v>444.5</v>
       </c>
       <c r="J277" s="12"/>
-      <c r="K277" s="31"/>
-    </row>
-    <row r="278" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K277" s="30"/>
+    </row>
+    <row r="278" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A278" s="15" t="s">
         <v>382</v>
       </c>
@@ -11380,9 +11512,9 @@
         <v>386.4</v>
       </c>
       <c r="J278" s="12"/>
-      <c r="K278" s="31"/>
-    </row>
-    <row r="279" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K278" s="30"/>
+    </row>
+    <row r="279" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A279" s="15" t="s">
         <v>383</v>
       </c>
@@ -11411,9 +11543,9 @@
         <v>0</v>
       </c>
       <c r="J279" s="12"/>
-      <c r="K279" s="31"/>
-    </row>
-    <row r="280" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K279" s="30"/>
+    </row>
+    <row r="280" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A280" s="15" t="s">
         <v>384</v>
       </c>
@@ -11446,7 +11578,7 @@
       <c r="J280" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="K280" s="31"/>
+      <c r="K280" s="30"/>
     </row>
     <row r="281" spans="1:11" ht="21.95" customHeight="1">
       <c r="A281" s="15" t="s">
@@ -11477,9 +11609,9 @@
         <v>434</v>
       </c>
       <c r="J281" s="12"/>
-      <c r="K281" s="31"/>
-    </row>
-    <row r="282" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K281" s="30"/>
+    </row>
+    <row r="282" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A282" s="15" t="s">
         <v>387</v>
       </c>
@@ -11510,7 +11642,7 @@
         <v>406</v>
       </c>
       <c r="J282" s="12"/>
-      <c r="K282" s="31"/>
+      <c r="K282" s="30"/>
     </row>
     <row r="283" spans="1:11" ht="21.95" customHeight="1">
       <c r="A283" s="15" t="s">
@@ -11539,7 +11671,7 @@
         <v>0</v>
       </c>
       <c r="J283" s="12"/>
-      <c r="K283" s="31"/>
+      <c r="K283" s="30"/>
     </row>
     <row r="284" spans="1:11" ht="21.95" customHeight="1">
       <c r="A284" s="15" t="s">
@@ -11572,7 +11704,7 @@
       <c r="J284" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="K284" s="31"/>
+      <c r="K284" s="30"/>
     </row>
     <row r="285" spans="1:11" ht="21.95" customHeight="1">
       <c r="A285" s="15" t="s">
@@ -11603,7 +11735,7 @@
         <v>392</v>
       </c>
       <c r="J285" s="12"/>
-      <c r="K285" s="31"/>
+      <c r="K285" s="30"/>
     </row>
     <row r="286" spans="1:11" ht="21.95" customHeight="1">
       <c r="A286" s="15" t="s">
@@ -11633,10 +11765,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B286,İndirimler!$B$2:$B$110,C286)&gt;0,ROUND(G286*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B286,İndirimler!$B$2:$B$110,C286)),2),"")</f>
         <v>363.3</v>
       </c>
-      <c r="J286" s="12"/>
-      <c r="K286" s="31"/>
-    </row>
-    <row r="287" spans="1:11" ht="21.95" customHeight="1">
+      <c r="J286" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="K286" s="30"/>
+    </row>
+    <row r="287" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A287" s="15" t="s">
         <v>393</v>
       </c>
@@ -11669,9 +11803,9 @@
       <c r="J287" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="K287" s="31"/>
-    </row>
-    <row r="288" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K287" s="30"/>
+    </row>
+    <row r="288" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A288" s="15" t="s">
         <v>395</v>
       </c>
@@ -11702,7 +11836,7 @@
         <v>332.5</v>
       </c>
       <c r="J288" s="12"/>
-      <c r="K288" s="31"/>
+      <c r="K288" s="30"/>
     </row>
     <row r="289" spans="1:11" ht="21.95" customHeight="1">
       <c r="A289" s="15" t="s">
@@ -11733,9 +11867,9 @@
         <v>404.6</v>
       </c>
       <c r="J289" s="12"/>
-      <c r="K289" s="31"/>
-    </row>
-    <row r="290" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K289" s="30"/>
+    </row>
+    <row r="290" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A290" s="15" t="s">
         <v>397</v>
       </c>
@@ -11766,7 +11900,7 @@
         <v>295.39999999999998</v>
       </c>
       <c r="J290" s="12"/>
-      <c r="K290" s="31"/>
+      <c r="K290" s="30"/>
     </row>
     <row r="291" spans="1:11" ht="21.95" customHeight="1">
       <c r="A291" s="15" t="s">
@@ -11797,9 +11931,9 @@
         <v>307.3</v>
       </c>
       <c r="J291" s="12"/>
-      <c r="K291" s="31"/>
-    </row>
-    <row r="292" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K291" s="30"/>
+    </row>
+    <row r="292" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A292" s="15" t="s">
         <v>399</v>
       </c>
@@ -11830,7 +11964,7 @@
         <v>241.5</v>
       </c>
       <c r="J292" s="12"/>
-      <c r="K292" s="31"/>
+      <c r="K292" s="30"/>
     </row>
     <row r="293" spans="1:11" ht="21.95" customHeight="1">
       <c r="A293" s="15" t="s">
@@ -11861,9 +11995,9 @@
         <v>286.3</v>
       </c>
       <c r="J293" s="12"/>
-      <c r="K293" s="31"/>
-    </row>
-    <row r="294" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K293" s="30"/>
+    </row>
+    <row r="294" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A294" s="15" t="s">
         <v>401</v>
       </c>
@@ -11892,7 +12026,7 @@
         <v>0</v>
       </c>
       <c r="J294" s="12"/>
-      <c r="K294" s="31"/>
+      <c r="K294" s="30"/>
     </row>
     <row r="295" spans="1:11" ht="21.95" customHeight="1">
       <c r="A295" s="15" t="s">
@@ -11921,9 +12055,9 @@
         <v>0</v>
       </c>
       <c r="J295" s="12"/>
-      <c r="K295" s="31"/>
-    </row>
-    <row r="296" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K295" s="30"/>
+    </row>
+    <row r="296" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A296" s="15" t="s">
         <v>403</v>
       </c>
@@ -11954,9 +12088,9 @@
         <v>412.3</v>
       </c>
       <c r="J296" s="12"/>
-      <c r="K296" s="31"/>
-    </row>
-    <row r="297" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K296" s="30"/>
+    </row>
+    <row r="297" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A297" s="15" t="s">
         <v>404</v>
       </c>
@@ -11985,9 +12119,9 @@
         <v>0</v>
       </c>
       <c r="J297" s="12"/>
-      <c r="K297" s="31"/>
-    </row>
-    <row r="298" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K297" s="30"/>
+    </row>
+    <row r="298" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A298" s="15" t="s">
         <v>405</v>
       </c>
@@ -12016,7 +12150,7 @@
         <v>0</v>
       </c>
       <c r="J298" s="12"/>
-      <c r="K298" s="31"/>
+      <c r="K298" s="30"/>
     </row>
     <row r="299" spans="1:11" ht="21.95" customHeight="1">
       <c r="A299" s="15" t="s">
@@ -12047,9 +12181,9 @@
         <v>343</v>
       </c>
       <c r="J299" s="12"/>
-      <c r="K299" s="31"/>
-    </row>
-    <row r="300" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K299" s="30"/>
+    </row>
+    <row r="300" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A300" s="15" t="s">
         <v>407</v>
       </c>
@@ -12080,7 +12214,7 @@
         <v>406</v>
       </c>
       <c r="J300" s="12"/>
-      <c r="K300" s="31"/>
+      <c r="K300" s="30"/>
     </row>
     <row r="301" spans="1:11" ht="21.95" customHeight="1">
       <c r="A301" s="15" t="s">
@@ -12109,7 +12243,7 @@
         <v>0</v>
       </c>
       <c r="J301" s="12"/>
-      <c r="K301" s="31"/>
+      <c r="K301" s="30"/>
     </row>
     <row r="302" spans="1:11" ht="21.95" customHeight="1">
       <c r="A302" s="15" t="s">
@@ -12140,7 +12274,7 @@
         <v>229.6</v>
       </c>
       <c r="J302" s="12"/>
-      <c r="K302" s="31"/>
+      <c r="K302" s="30"/>
     </row>
     <row r="303" spans="1:11" ht="21.95" customHeight="1">
       <c r="A303" s="15" t="s">
@@ -12171,7 +12305,7 @@
         <v>324.8</v>
       </c>
       <c r="J303" s="12"/>
-      <c r="K303" s="31"/>
+      <c r="K303" s="30"/>
     </row>
     <row r="304" spans="1:11" ht="21.95" customHeight="1">
       <c r="A304" s="15" t="s">
@@ -12199,10 +12333,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B304,İndirimler!$B$2:$B$110,C304)&gt;0,ROUND(G304*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B304,İndirimler!$B$2:$B$110,C304)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J304" s="12"/>
-      <c r="K304" s="31"/>
-    </row>
-    <row r="305" spans="1:11" ht="21.95" customHeight="1">
+      <c r="J304" s="32" t="s">
+        <v>696</v>
+      </c>
+      <c r="K304" s="30"/>
+    </row>
+    <row r="305" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A305" s="15" t="s">
         <v>412</v>
       </c>
@@ -12231,7 +12367,7 @@
         <v>0</v>
       </c>
       <c r="J305" s="12"/>
-      <c r="K305" s="31"/>
+      <c r="K305" s="30"/>
     </row>
     <row r="306" spans="1:11" ht="21.95" customHeight="1">
       <c r="A306" s="15" t="s">
@@ -12262,9 +12398,9 @@
         <v>313.60000000000002</v>
       </c>
       <c r="J306" s="12"/>
-      <c r="K306" s="31"/>
-    </row>
-    <row r="307" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K306" s="30"/>
+    </row>
+    <row r="307" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A307" s="15" t="s">
         <v>414</v>
       </c>
@@ -12295,7 +12431,7 @@
         <v>320.60000000000002</v>
       </c>
       <c r="J307" s="12"/>
-      <c r="K307" s="31"/>
+      <c r="K307" s="30"/>
     </row>
     <row r="308" spans="1:11" ht="21.95" customHeight="1">
       <c r="A308" s="15" t="s">
@@ -12324,7 +12460,7 @@
         <v>0</v>
       </c>
       <c r="J308" s="12"/>
-      <c r="K308" s="31"/>
+      <c r="K308" s="30"/>
     </row>
     <row r="309" spans="1:11" ht="21.95" customHeight="1">
       <c r="A309" s="15" t="s">
@@ -12353,9 +12489,9 @@
         <v>0</v>
       </c>
       <c r="J309" s="12"/>
-      <c r="K309" s="31"/>
-    </row>
-    <row r="310" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K309" s="30"/>
+    </row>
+    <row r="310" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A310" s="15" t="s">
         <v>417</v>
       </c>
@@ -12386,9 +12522,9 @@
         <v>430.5</v>
       </c>
       <c r="J310" s="12"/>
-      <c r="K310" s="31"/>
-    </row>
-    <row r="311" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K310" s="30"/>
+    </row>
+    <row r="311" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A311" s="15" t="s">
         <v>418</v>
       </c>
@@ -12419,9 +12555,9 @@
         <v>430.5</v>
       </c>
       <c r="J311" s="12"/>
-      <c r="K311" s="31"/>
-    </row>
-    <row r="312" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K311" s="30"/>
+    </row>
+    <row r="312" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A312" s="15" t="s">
         <v>419</v>
       </c>
@@ -12452,9 +12588,9 @@
         <v>250.6</v>
       </c>
       <c r="J312" s="12"/>
-      <c r="K312" s="31"/>
-    </row>
-    <row r="313" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K312" s="30"/>
+    </row>
+    <row r="313" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A313" s="15" t="s">
         <v>420</v>
       </c>
@@ -12485,9 +12621,9 @@
         <v>443.8</v>
       </c>
       <c r="J313" s="12"/>
-      <c r="K313" s="31"/>
-    </row>
-    <row r="314" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K313" s="30"/>
+    </row>
+    <row r="314" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A314" s="15" t="s">
         <v>421</v>
       </c>
@@ -12518,9 +12654,9 @@
         <v>192.5</v>
       </c>
       <c r="J314" s="12"/>
-      <c r="K314" s="31"/>
-    </row>
-    <row r="315" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K314" s="30"/>
+    </row>
+    <row r="315" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A315" s="15" t="s">
         <v>422</v>
       </c>
@@ -12551,7 +12687,7 @@
         <v>213.5</v>
       </c>
       <c r="J315" s="12"/>
-      <c r="K315" s="31"/>
+      <c r="K315" s="30"/>
     </row>
     <row r="316" spans="1:11" ht="21.95" customHeight="1">
       <c r="A316" s="15" t="s">
@@ -12582,7 +12718,7 @@
         <v>192.5</v>
       </c>
       <c r="J316" s="12"/>
-      <c r="K316" s="31"/>
+      <c r="K316" s="30"/>
     </row>
     <row r="317" spans="1:11" ht="21.95" customHeight="1">
       <c r="A317" s="15" t="s">
@@ -12613,7 +12749,7 @@
         <v>458.5</v>
       </c>
       <c r="J317" s="12"/>
-      <c r="K317" s="31"/>
+      <c r="K317" s="30"/>
     </row>
     <row r="318" spans="1:11" ht="21.95" customHeight="1">
       <c r="A318" s="15" t="s">
@@ -12644,7 +12780,7 @@
         <v>335.3</v>
       </c>
       <c r="J318" s="12"/>
-      <c r="K318" s="31"/>
+      <c r="K318" s="30"/>
     </row>
     <row r="319" spans="1:11" ht="21.95" customHeight="1">
       <c r="A319" s="15" t="s">
@@ -12675,7 +12811,7 @@
         <v>325.5</v>
       </c>
       <c r="J319" s="12"/>
-      <c r="K319" s="31"/>
+      <c r="K319" s="30"/>
     </row>
     <row r="320" spans="1:11" ht="21.95" customHeight="1">
       <c r="A320" s="15" t="s">
@@ -12706,7 +12842,7 @@
         <v>376.6</v>
       </c>
       <c r="J320" s="12"/>
-      <c r="K320" s="31"/>
+      <c r="K320" s="30"/>
     </row>
     <row r="321" spans="1:11" ht="21.95" customHeight="1">
       <c r="A321" s="15" t="s">
@@ -12735,7 +12871,7 @@
         <v>0</v>
       </c>
       <c r="J321" s="12"/>
-      <c r="K321" s="31"/>
+      <c r="K321" s="30"/>
     </row>
     <row r="322" spans="1:11" ht="21.95" customHeight="1">
       <c r="A322" s="15" t="s">
@@ -12766,9 +12902,9 @@
         <v>419.3</v>
       </c>
       <c r="J322" s="12"/>
-      <c r="K322" s="31"/>
-    </row>
-    <row r="323" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K322" s="30"/>
+    </row>
+    <row r="323" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A323" s="15" t="s">
         <v>430</v>
       </c>
@@ -12799,7 +12935,7 @@
         <v>276.5</v>
       </c>
       <c r="J323" s="12"/>
-      <c r="K323" s="31"/>
+      <c r="K323" s="30"/>
     </row>
     <row r="324" spans="1:11" ht="21.95" customHeight="1">
       <c r="A324" s="15" t="s">
@@ -12829,8 +12965,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B324,İndirimler!$B$2:$B$110,C324)&gt;0,ROUND(G324*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B324,İndirimler!$B$2:$B$110,C324)),2),"")</f>
         <v>384.3</v>
       </c>
-      <c r="J324" s="12"/>
-      <c r="K324" s="31"/>
+      <c r="J324" s="32" t="s">
+        <v>675</v>
+      </c>
+      <c r="K324" s="30"/>
     </row>
     <row r="325" spans="1:11" ht="21.95" customHeight="1">
       <c r="A325" s="15" t="s">
@@ -12861,9 +12999,9 @@
         <v>528.5</v>
       </c>
       <c r="J325" s="12"/>
-      <c r="K325" s="31"/>
-    </row>
-    <row r="326" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K325" s="30"/>
+    </row>
+    <row r="326" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A326" s="15" t="s">
         <v>434</v>
       </c>
@@ -12892,9 +13030,9 @@
         <v>0</v>
       </c>
       <c r="J326" s="12"/>
-      <c r="K326" s="31"/>
-    </row>
-    <row r="327" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K326" s="30"/>
+    </row>
+    <row r="327" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A327" s="15" t="s">
         <v>437</v>
       </c>
@@ -12925,11 +13063,11 @@
         <v>349.3</v>
       </c>
       <c r="J327" s="12"/>
-      <c r="K327" s="31" t="s">
+      <c r="K327" s="30" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="328" spans="1:11" ht="21.95" customHeight="1">
+    <row r="328" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A328" s="15" t="s">
         <v>438</v>
       </c>
@@ -12962,7 +13100,7 @@
       <c r="J328" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="K328" s="31"/>
+      <c r="K328" s="30"/>
     </row>
     <row r="329" spans="1:11" ht="21.95" customHeight="1">
       <c r="A329" s="15" t="s">
@@ -12993,9 +13131,9 @@
         <v>364</v>
       </c>
       <c r="J329" s="12"/>
-      <c r="K329" s="31"/>
-    </row>
-    <row r="330" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K329" s="30"/>
+    </row>
+    <row r="330" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A330" s="15" t="s">
         <v>441</v>
       </c>
@@ -13026,7 +13164,7 @@
         <v>350</v>
       </c>
       <c r="J330" s="12"/>
-      <c r="K330" s="31"/>
+      <c r="K330" s="30"/>
     </row>
     <row r="331" spans="1:11" ht="21.95" customHeight="1">
       <c r="A331" s="15" t="s">
@@ -13059,7 +13197,7 @@
       <c r="J331" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="K331" s="31"/>
+      <c r="K331" s="30"/>
     </row>
     <row r="332" spans="1:11" ht="21.95" customHeight="1">
       <c r="A332" s="15" t="s">
@@ -13090,7 +13228,7 @@
         <v>336</v>
       </c>
       <c r="J332" s="12"/>
-      <c r="K332" s="31"/>
+      <c r="K332" s="30"/>
     </row>
     <row r="333" spans="1:11" ht="21.95" customHeight="1">
       <c r="A333" s="15" t="s">
@@ -13120,8 +13258,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B333,İndirimler!$B$2:$B$110,C333)&gt;0,ROUND(G333*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B333,İndirimler!$B$2:$B$110,C333)),2),"")</f>
         <v>251.3</v>
       </c>
-      <c r="J333" s="12"/>
-      <c r="K333" s="31"/>
+      <c r="J333" s="32" t="s">
+        <v>687</v>
+      </c>
+      <c r="K333" s="30"/>
     </row>
     <row r="334" spans="1:11" ht="21.95" customHeight="1">
       <c r="A334" s="15" t="s">
@@ -13152,11 +13292,11 @@
         <v>314.3</v>
       </c>
       <c r="J334" s="12"/>
-      <c r="K334" s="31" t="s">
+      <c r="K334" s="30" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="335" spans="1:11" ht="21.95" customHeight="1">
+    <row r="335" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A335" s="15" t="s">
         <v>449</v>
       </c>
@@ -13187,11 +13327,11 @@
         <v>314.3</v>
       </c>
       <c r="J335" s="12"/>
-      <c r="K335" s="31" t="s">
+      <c r="K335" s="30" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="336" spans="1:11" ht="21.95" customHeight="1">
+    <row r="336" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A336" s="15" t="s">
         <v>450</v>
       </c>
@@ -13224,9 +13364,9 @@
       <c r="J336" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="K336" s="31"/>
-    </row>
-    <row r="337" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K336" s="30"/>
+    </row>
+    <row r="337" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A337" s="15" t="s">
         <v>452</v>
       </c>
@@ -13257,7 +13397,7 @@
         <v>314.3</v>
       </c>
       <c r="J337" s="12"/>
-      <c r="K337" s="31"/>
+      <c r="K337" s="30"/>
     </row>
     <row r="338" spans="1:11" ht="21.95" customHeight="1">
       <c r="A338" s="15" t="s">
@@ -13288,9 +13428,9 @@
         <v>406</v>
       </c>
       <c r="J338" s="12"/>
-      <c r="K338" s="31"/>
-    </row>
-    <row r="339" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K338" s="30"/>
+    </row>
+    <row r="339" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A339" s="15" t="s">
         <v>454</v>
       </c>
@@ -13321,7 +13461,7 @@
         <v>332.5</v>
       </c>
       <c r="J339" s="12"/>
-      <c r="K339" s="31"/>
+      <c r="K339" s="30"/>
     </row>
     <row r="340" spans="1:11" ht="21.95" customHeight="1">
       <c r="A340" s="15" t="s">
@@ -13352,9 +13492,9 @@
         <v>230.3</v>
       </c>
       <c r="J340" s="12"/>
-      <c r="K340" s="31"/>
-    </row>
-    <row r="341" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K340" s="30"/>
+    </row>
+    <row r="341" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A341" s="15" t="s">
         <v>457</v>
       </c>
@@ -13385,7 +13525,7 @@
         <v>251.3</v>
       </c>
       <c r="J341" s="12"/>
-      <c r="K341" s="31"/>
+      <c r="K341" s="30"/>
     </row>
     <row r="342" spans="1:11" ht="21.95" customHeight="1">
       <c r="A342" s="15" t="s">
@@ -13416,7 +13556,7 @@
         <v>251.3</v>
       </c>
       <c r="J342" s="12"/>
-      <c r="K342" s="31"/>
+      <c r="K342" s="30"/>
     </row>
     <row r="343" spans="1:11" ht="21.95" customHeight="1">
       <c r="A343" s="15" t="s">
@@ -13446,8 +13586,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B343,İndirimler!$B$2:$B$110,C343)&gt;0,ROUND(G343*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B343,İndirimler!$B$2:$B$110,C343)),2),"")</f>
         <v>440.3</v>
       </c>
-      <c r="J343" s="12"/>
-      <c r="K343" s="31"/>
+      <c r="J343" s="32" t="s">
+        <v>681</v>
+      </c>
+      <c r="K343" s="30"/>
     </row>
     <row r="344" spans="1:11" ht="21.95" customHeight="1">
       <c r="A344" s="15" t="s">
@@ -13478,9 +13620,9 @@
         <v>510.3</v>
       </c>
       <c r="J344" s="12"/>
-      <c r="K344" s="31"/>
-    </row>
-    <row r="345" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K344" s="30"/>
+    </row>
+    <row r="345" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A345" s="15" t="s">
         <v>461</v>
       </c>
@@ -13509,9 +13651,9 @@
         <v>0</v>
       </c>
       <c r="J345" s="12"/>
-      <c r="K345" s="31"/>
-    </row>
-    <row r="346" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K345" s="30"/>
+    </row>
+    <row r="346" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A346" s="15" t="s">
         <v>463</v>
       </c>
@@ -13542,11 +13684,11 @@
         <v>349.3</v>
       </c>
       <c r="J346" s="12"/>
-      <c r="K346" s="31" t="s">
+      <c r="K346" s="30" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="347" spans="1:11" ht="21.95" customHeight="1">
+    <row r="347" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A347" s="15" t="s">
         <v>464</v>
       </c>
@@ -13579,7 +13721,7 @@
       <c r="J347" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="K347" s="31"/>
+      <c r="K347" s="30"/>
     </row>
     <row r="348" spans="1:11" ht="21.95" customHeight="1">
       <c r="A348" s="15" t="s">
@@ -13610,9 +13752,9 @@
         <v>425.6</v>
       </c>
       <c r="J348" s="12"/>
-      <c r="K348" s="31"/>
-    </row>
-    <row r="349" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K348" s="30"/>
+    </row>
+    <row r="349" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A349" s="15" t="s">
         <v>467</v>
       </c>
@@ -13643,7 +13785,7 @@
         <v>378</v>
       </c>
       <c r="J349" s="12"/>
-      <c r="K349" s="31"/>
+      <c r="K349" s="30"/>
     </row>
     <row r="350" spans="1:11" ht="21.95" customHeight="1">
       <c r="A350" s="15" t="s">
@@ -13676,7 +13818,7 @@
       <c r="J350" s="12" t="s">
         <v>469</v>
       </c>
-      <c r="K350" s="31"/>
+      <c r="K350" s="30"/>
     </row>
     <row r="351" spans="1:11" ht="21.95" customHeight="1">
       <c r="A351" s="15" t="s">
@@ -13707,7 +13849,7 @@
         <v>347.2</v>
       </c>
       <c r="J351" s="12"/>
-      <c r="K351" s="31"/>
+      <c r="K351" s="30"/>
     </row>
     <row r="352" spans="1:11" ht="21.95" customHeight="1">
       <c r="A352" s="15" t="s">
@@ -13737,8 +13879,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B352,İndirimler!$B$2:$B$110,C352)&gt;0,ROUND(G352*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B352,İndirimler!$B$2:$B$110,C352)),2),"")</f>
         <v>251.3</v>
       </c>
-      <c r="J352" s="12"/>
-      <c r="K352" s="31"/>
+      <c r="J352" s="32" t="s">
+        <v>693</v>
+      </c>
+      <c r="K352" s="30"/>
     </row>
     <row r="353" spans="1:11" ht="21.95" customHeight="1">
       <c r="A353" s="15" t="s">
@@ -13769,11 +13913,11 @@
         <v>314.3</v>
       </c>
       <c r="J353" s="12"/>
-      <c r="K353" s="31" t="s">
+      <c r="K353" s="30" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="354" spans="1:11" ht="21.95" customHeight="1">
+    <row r="354" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A354" s="15" t="s">
         <v>474</v>
       </c>
@@ -13804,11 +13948,11 @@
         <v>314.3</v>
       </c>
       <c r="J354" s="12"/>
-      <c r="K354" s="31" t="s">
+      <c r="K354" s="30" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="355" spans="1:11" ht="21.95" customHeight="1">
+    <row r="355" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A355" s="15" t="s">
         <v>476</v>
       </c>
@@ -13841,9 +13985,9 @@
       <c r="J355" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="K355" s="31"/>
-    </row>
-    <row r="356" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K355" s="30"/>
+    </row>
+    <row r="356" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A356" s="15" t="s">
         <v>478</v>
       </c>
@@ -13874,7 +14018,7 @@
         <v>314.3</v>
       </c>
       <c r="J356" s="12"/>
-      <c r="K356" s="31"/>
+      <c r="K356" s="30"/>
     </row>
     <row r="357" spans="1:11" ht="21.95" customHeight="1">
       <c r="A357" s="15" t="s">
@@ -13905,9 +14049,9 @@
         <v>343</v>
       </c>
       <c r="J357" s="12"/>
-      <c r="K357" s="31"/>
-    </row>
-    <row r="358" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K357" s="30"/>
+    </row>
+    <row r="358" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A358" s="15" t="s">
         <v>480</v>
       </c>
@@ -13938,7 +14082,7 @@
         <v>295.39999999999998</v>
       </c>
       <c r="J358" s="12"/>
-      <c r="K358" s="31"/>
+      <c r="K358" s="30"/>
     </row>
     <row r="359" spans="1:11" ht="21.95" customHeight="1">
       <c r="A359" s="15" t="s">
@@ -13969,9 +14113,9 @@
         <v>248.5</v>
       </c>
       <c r="J359" s="12"/>
-      <c r="K359" s="31"/>
-    </row>
-    <row r="360" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K359" s="30"/>
+    </row>
+    <row r="360" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A360" s="15" t="s">
         <v>482</v>
       </c>
@@ -14002,7 +14146,7 @@
         <v>188.3</v>
       </c>
       <c r="J360" s="12"/>
-      <c r="K360" s="31"/>
+      <c r="K360" s="30"/>
     </row>
     <row r="361" spans="1:11" ht="21.95" customHeight="1">
       <c r="A361" s="15" t="s">
@@ -14033,7 +14177,7 @@
         <v>300.3</v>
       </c>
       <c r="J361" s="12"/>
-      <c r="K361" s="31"/>
+      <c r="K361" s="30"/>
     </row>
     <row r="362" spans="1:11" ht="21.95" customHeight="1">
       <c r="A362" s="15" t="s">
@@ -14062,9 +14206,9 @@
         <v>0</v>
       </c>
       <c r="J362" s="12"/>
-      <c r="K362" s="31"/>
-    </row>
-    <row r="363" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K362" s="30"/>
+    </row>
+    <row r="363" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A363" s="15" t="s">
         <v>485</v>
       </c>
@@ -14093,9 +14237,9 @@
         <v>0</v>
       </c>
       <c r="J363" s="12"/>
-      <c r="K363" s="31"/>
-    </row>
-    <row r="364" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K363" s="30"/>
+    </row>
+    <row r="364" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A364" s="15" t="s">
         <v>486</v>
       </c>
@@ -14124,7 +14268,7 @@
         <v>0</v>
       </c>
       <c r="J364" s="12"/>
-      <c r="K364" s="31"/>
+      <c r="K364" s="30"/>
     </row>
     <row r="365" spans="1:11" ht="21.95" customHeight="1">
       <c r="A365" s="15" t="s">
@@ -14155,9 +14299,9 @@
         <v>340.2</v>
       </c>
       <c r="J365" s="12"/>
-      <c r="K365" s="31"/>
-    </row>
-    <row r="366" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K365" s="30"/>
+    </row>
+    <row r="366" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A366" s="15" t="s">
         <v>488</v>
       </c>
@@ -14188,7 +14332,7 @@
         <v>364</v>
       </c>
       <c r="J366" s="12"/>
-      <c r="K366" s="31"/>
+      <c r="K366" s="30"/>
     </row>
     <row r="367" spans="1:11" ht="21.95" customHeight="1">
       <c r="A367" s="15" t="s">
@@ -14219,7 +14363,7 @@
         <v>256.2</v>
       </c>
       <c r="J367" s="12"/>
-      <c r="K367" s="31"/>
+      <c r="K367" s="30"/>
     </row>
     <row r="368" spans="1:11" ht="21.95" customHeight="1">
       <c r="A368" s="15" t="s">
@@ -14250,7 +14394,7 @@
         <v>425.6</v>
       </c>
       <c r="J368" s="12"/>
-      <c r="K368" s="31"/>
+      <c r="K368" s="30"/>
     </row>
     <row r="369" spans="1:11" ht="21.95" customHeight="1">
       <c r="A369" s="15" t="s">
@@ -14279,7 +14423,7 @@
         <v>0</v>
       </c>
       <c r="J369" s="12"/>
-      <c r="K369" s="31"/>
+      <c r="K369" s="30"/>
     </row>
     <row r="370" spans="1:11" ht="21.95" customHeight="1">
       <c r="A370" s="15" t="s">
@@ -14310,9 +14454,9 @@
         <v>349.3</v>
       </c>
       <c r="J370" s="12"/>
-      <c r="K370" s="31"/>
-    </row>
-    <row r="371" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K370" s="30"/>
+    </row>
+    <row r="371" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A371" s="15" t="s">
         <v>493</v>
       </c>
@@ -14341,7 +14485,7 @@
         <v>0</v>
       </c>
       <c r="J371" s="12"/>
-      <c r="K371" s="31"/>
+      <c r="K371" s="30"/>
     </row>
     <row r="372" spans="1:11" ht="21.95" customHeight="1">
       <c r="A372" s="15" t="s">
@@ -14372,9 +14516,9 @@
         <v>306.60000000000002</v>
       </c>
       <c r="J372" s="12"/>
-      <c r="K372" s="31"/>
-    </row>
-    <row r="373" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K372" s="30"/>
+    </row>
+    <row r="373" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A373" s="15" t="s">
         <v>495</v>
       </c>
@@ -14405,7 +14549,7 @@
         <v>320.60000000000002</v>
       </c>
       <c r="J373" s="12"/>
-      <c r="K373" s="31"/>
+      <c r="K373" s="30"/>
     </row>
     <row r="374" spans="1:11" ht="21.95" customHeight="1">
       <c r="A374" s="15" t="s">
@@ -14434,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="J374" s="12"/>
-      <c r="K374" s="31"/>
+      <c r="K374" s="30"/>
     </row>
     <row r="375" spans="1:11" ht="21.95" customHeight="1">
       <c r="A375" s="15" t="s">
@@ -14463,7 +14607,7 @@
         <v>0</v>
       </c>
       <c r="J375" s="12"/>
-      <c r="K375" s="31"/>
+      <c r="K375" s="30"/>
     </row>
     <row r="376" spans="1:11" ht="21.95" customHeight="1">
       <c r="A376" s="15" t="s">
@@ -14492,9 +14636,9 @@
         <v>0</v>
       </c>
       <c r="J376" s="12"/>
-      <c r="K376" s="31"/>
-    </row>
-    <row r="377" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K376" s="30"/>
+    </row>
+    <row r="377" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A377" s="15" t="s">
         <v>499</v>
       </c>
@@ -14525,9 +14669,9 @@
         <v>412.3</v>
       </c>
       <c r="J377" s="12"/>
-      <c r="K377" s="31"/>
-    </row>
-    <row r="378" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K377" s="30"/>
+    </row>
+    <row r="378" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A378" s="15" t="s">
         <v>500</v>
       </c>
@@ -14558,9 +14702,9 @@
         <v>412.3</v>
       </c>
       <c r="J378" s="12"/>
-      <c r="K378" s="31"/>
-    </row>
-    <row r="379" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K378" s="30"/>
+    </row>
+    <row r="379" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A379" s="15" t="s">
         <v>501</v>
       </c>
@@ -14591,7 +14735,7 @@
         <v>233.1</v>
       </c>
       <c r="J379" s="12"/>
-      <c r="K379" s="31"/>
+      <c r="K379" s="30"/>
     </row>
     <row r="380" spans="1:11" ht="21.95" customHeight="1">
       <c r="A380" s="15" t="s">
@@ -14622,7 +14766,7 @@
         <v>283.5</v>
       </c>
       <c r="J380" s="12"/>
-      <c r="K380" s="31"/>
+      <c r="K380" s="30"/>
     </row>
     <row r="381" spans="1:11" ht="21.95" customHeight="1">
       <c r="A381" s="15" t="s">
@@ -14653,7 +14797,7 @@
         <v>446.6</v>
       </c>
       <c r="J381" s="12"/>
-      <c r="K381" s="31"/>
+      <c r="K381" s="30"/>
     </row>
     <row r="382" spans="1:11" ht="21.95" customHeight="1">
       <c r="A382" s="15" t="s">
@@ -14684,7 +14828,7 @@
         <v>335.3</v>
       </c>
       <c r="J382" s="12"/>
-      <c r="K382" s="31"/>
+      <c r="K382" s="30"/>
     </row>
     <row r="383" spans="1:11" ht="21.95" customHeight="1">
       <c r="A383" s="15" t="s">
@@ -14715,7 +14859,7 @@
         <v>251.3</v>
       </c>
       <c r="J383" s="12"/>
-      <c r="K383" s="31"/>
+      <c r="K383" s="30"/>
     </row>
     <row r="384" spans="1:11" ht="21.95" customHeight="1">
       <c r="A384" s="15" t="s">
@@ -14746,7 +14890,7 @@
         <v>325.5</v>
       </c>
       <c r="J384" s="12"/>
-      <c r="K384" s="31"/>
+      <c r="K384" s="30"/>
     </row>
     <row r="385" spans="1:11" ht="21.95" customHeight="1">
       <c r="A385" s="15" t="s">
@@ -14777,9 +14921,9 @@
         <v>446.6</v>
       </c>
       <c r="J385" s="12"/>
-      <c r="K385" s="31"/>
-    </row>
-    <row r="386" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K385" s="30"/>
+    </row>
+    <row r="386" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A386" s="15" t="s">
         <v>508</v>
       </c>
@@ -14810,7 +14954,7 @@
         <v>276.5</v>
       </c>
       <c r="J386" s="12"/>
-      <c r="K386" s="31"/>
+      <c r="K386" s="30"/>
     </row>
     <row r="387" spans="1:11" ht="21.95" customHeight="1">
       <c r="A387" s="15" t="s">
@@ -14840,8 +14984,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B387,İndirimler!$B$2:$B$110,C387)&gt;0,ROUND(G387*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B387,İndirimler!$B$2:$B$110,C387)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J387" s="12"/>
-      <c r="K387" s="31"/>
+      <c r="J387" s="32" t="s">
+        <v>670</v>
+      </c>
+      <c r="K387" s="30"/>
     </row>
     <row r="388" spans="1:11" ht="21.95" customHeight="1">
       <c r="A388" s="15" t="s">
@@ -14872,9 +15018,9 @@
         <v>377.3</v>
       </c>
       <c r="J388" s="12"/>
-      <c r="K388" s="31"/>
-    </row>
-    <row r="389" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K388" s="30"/>
+    </row>
+    <row r="389" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A389" s="15" t="s">
         <v>512</v>
       </c>
@@ -14907,7 +15053,7 @@
       <c r="J389" s="12" t="s">
         <v>513</v>
       </c>
-      <c r="K389" s="31"/>
+      <c r="K389" s="30"/>
     </row>
     <row r="390" spans="1:11" ht="21.95" customHeight="1">
       <c r="A390" s="15" t="s">
@@ -14938,7 +15084,7 @@
         <v>383.6</v>
       </c>
       <c r="J390" s="12"/>
-      <c r="K390" s="31"/>
+      <c r="K390" s="30"/>
     </row>
     <row r="391" spans="1:11" ht="21.95" customHeight="1">
       <c r="A391" s="15" t="s">
@@ -14971,7 +15117,7 @@
       <c r="J391" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="K391" s="31"/>
+      <c r="K391" s="30"/>
     </row>
     <row r="392" spans="1:11" ht="21.95" customHeight="1">
       <c r="A392" s="15" t="s">
@@ -15002,7 +15148,7 @@
         <v>174.3</v>
       </c>
       <c r="J392" s="12"/>
-      <c r="K392" s="31"/>
+      <c r="K392" s="30"/>
     </row>
     <row r="393" spans="1:11" ht="21.95" customHeight="1">
       <c r="A393" s="15" t="s">
@@ -15032,10 +15178,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B393,İndirimler!$B$2:$B$110,C393)&gt;0,ROUND(G393*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B393,İndirimler!$B$2:$B$110,C393)),2),"")</f>
         <v>251.3</v>
       </c>
-      <c r="J393" s="12"/>
-      <c r="K393" s="31"/>
-    </row>
-    <row r="394" spans="1:11" ht="21.95" customHeight="1">
+      <c r="J393" s="32" t="s">
+        <v>686</v>
+      </c>
+      <c r="K393" s="30"/>
+    </row>
+    <row r="394" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A394" s="15" t="s">
         <v>520</v>
       </c>
@@ -15068,9 +15216,9 @@
       <c r="J394" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="K394" s="31"/>
-    </row>
-    <row r="395" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K394" s="30"/>
+    </row>
+    <row r="395" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A395" s="15" t="s">
         <v>522</v>
       </c>
@@ -15101,7 +15249,7 @@
         <v>300.3</v>
       </c>
       <c r="J395" s="12"/>
-      <c r="K395" s="31"/>
+      <c r="K395" s="30"/>
     </row>
     <row r="396" spans="1:11" ht="21.95" customHeight="1">
       <c r="A396" s="15" t="s">
@@ -15132,9 +15280,9 @@
         <v>383.6</v>
       </c>
       <c r="J396" s="12"/>
-      <c r="K396" s="31"/>
-    </row>
-    <row r="397" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K396" s="30"/>
+    </row>
+    <row r="397" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A397" s="15" t="s">
         <v>524</v>
       </c>
@@ -15165,9 +15313,9 @@
         <v>308</v>
       </c>
       <c r="J397" s="12"/>
-      <c r="K397" s="31"/>
-    </row>
-    <row r="398" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K397" s="30"/>
+    </row>
+    <row r="398" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A398" s="15" t="s">
         <v>525</v>
       </c>
@@ -15198,7 +15346,7 @@
         <v>206.5</v>
       </c>
       <c r="J398" s="12"/>
-      <c r="K398" s="31"/>
+      <c r="K398" s="30"/>
     </row>
     <row r="399" spans="1:11" ht="21.95" customHeight="1">
       <c r="A399" s="15" t="s">
@@ -15229,7 +15377,7 @@
         <v>335.3</v>
       </c>
       <c r="J399" s="12"/>
-      <c r="K399" s="31"/>
+      <c r="K399" s="30"/>
     </row>
     <row r="400" spans="1:11" ht="21.95" customHeight="1">
       <c r="A400" s="15" t="s">
@@ -15260,9 +15408,9 @@
         <v>545.29999999999995</v>
       </c>
       <c r="J400" s="12"/>
-      <c r="K400" s="31"/>
-    </row>
-    <row r="401" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K400" s="30"/>
+    </row>
+    <row r="401" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A401" s="15" t="s">
         <v>528</v>
       </c>
@@ -15295,7 +15443,7 @@
       <c r="J401" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="K401" s="31"/>
+      <c r="K401" s="30"/>
     </row>
     <row r="402" spans="1:11" ht="21.95" customHeight="1">
       <c r="A402" s="15" t="s">
@@ -15326,7 +15474,7 @@
         <v>425.6</v>
       </c>
       <c r="J402" s="12"/>
-      <c r="K402" s="31"/>
+      <c r="K402" s="30"/>
     </row>
     <row r="403" spans="1:11" ht="21.95" customHeight="1">
       <c r="A403" s="15" t="s">
@@ -15359,7 +15507,7 @@
       <c r="J403" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="K403" s="31"/>
+      <c r="K403" s="30"/>
     </row>
     <row r="404" spans="1:11" ht="21.95" customHeight="1">
       <c r="A404" s="15" t="s">
@@ -15390,7 +15538,7 @@
         <v>206.5</v>
       </c>
       <c r="J404" s="12"/>
-      <c r="K404" s="31"/>
+      <c r="K404" s="30"/>
     </row>
     <row r="405" spans="1:11" ht="21.95" customHeight="1">
       <c r="A405" s="15" t="s">
@@ -15420,10 +15568,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B405,İndirimler!$B$2:$B$110,C405)&gt;0,ROUND(G405*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B405,İndirimler!$B$2:$B$110,C405)),2),"")</f>
         <v>269.5</v>
       </c>
-      <c r="J405" s="12"/>
-      <c r="K405" s="31"/>
-    </row>
-    <row r="406" spans="1:11" ht="21.95" customHeight="1">
+      <c r="J405" s="32" t="s">
+        <v>694</v>
+      </c>
+      <c r="K405" s="30"/>
+    </row>
+    <row r="406" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A406" s="15" t="s">
         <v>535</v>
       </c>
@@ -15456,9 +15606,9 @@
       <c r="J406" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="K406" s="31"/>
-    </row>
-    <row r="407" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K406" s="30"/>
+    </row>
+    <row r="407" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A407" s="15" t="s">
         <v>537</v>
       </c>
@@ -15489,7 +15639,7 @@
         <v>300.3</v>
       </c>
       <c r="J407" s="12"/>
-      <c r="K407" s="31"/>
+      <c r="K407" s="30"/>
     </row>
     <row r="408" spans="1:11" ht="21.95" customHeight="1">
       <c r="A408" s="15" t="s">
@@ -15520,9 +15670,9 @@
         <v>433.3</v>
       </c>
       <c r="J408" s="12"/>
-      <c r="K408" s="31"/>
-    </row>
-    <row r="409" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K408" s="30"/>
+    </row>
+    <row r="409" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A409" s="15" t="s">
         <v>539</v>
       </c>
@@ -15553,9 +15703,9 @@
         <v>443.8</v>
       </c>
       <c r="J409" s="12"/>
-      <c r="K409" s="31"/>
-    </row>
-    <row r="410" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K409" s="30"/>
+    </row>
+    <row r="410" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A410" s="15" t="s">
         <v>540</v>
       </c>
@@ -15586,7 +15736,7 @@
         <v>206.5</v>
       </c>
       <c r="J410" s="12"/>
-      <c r="K410" s="31"/>
+      <c r="K410" s="30"/>
     </row>
     <row r="411" spans="1:11" ht="21.95" customHeight="1">
       <c r="A411" s="15" t="s">
@@ -15617,7 +15767,7 @@
         <v>269.5</v>
       </c>
       <c r="J411" s="12"/>
-      <c r="K411" s="31"/>
+      <c r="K411" s="30"/>
     </row>
     <row r="412" spans="1:11" ht="21.95" customHeight="1">
       <c r="A412" s="15" t="s">
@@ -15646,9 +15796,9 @@
         <v>0</v>
       </c>
       <c r="J412" s="12"/>
-      <c r="K412" s="31"/>
-    </row>
-    <row r="413" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K412" s="30"/>
+    </row>
+    <row r="413" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A413" s="15" t="s">
         <v>543</v>
       </c>
@@ -15677,7 +15827,7 @@
         <v>0</v>
       </c>
       <c r="J413" s="12"/>
-      <c r="K413" s="31"/>
+      <c r="K413" s="30"/>
     </row>
     <row r="414" spans="1:11" ht="21.95" customHeight="1">
       <c r="A414" s="15" t="s">
@@ -15708,7 +15858,7 @@
         <v>340.2</v>
       </c>
       <c r="J414" s="12"/>
-      <c r="K414" s="31"/>
+      <c r="K414" s="30"/>
     </row>
     <row r="415" spans="1:11" ht="21.95" customHeight="1">
       <c r="A415" s="15" t="s">
@@ -15739,7 +15889,7 @@
         <v>242.2</v>
       </c>
       <c r="J415" s="12"/>
-      <c r="K415" s="31"/>
+      <c r="K415" s="30"/>
     </row>
     <row r="416" spans="1:11" ht="21.95" customHeight="1">
       <c r="A416" s="15" t="s">
@@ -15768,7 +15918,7 @@
         <v>0</v>
       </c>
       <c r="J416" s="12"/>
-      <c r="K416" s="31"/>
+      <c r="K416" s="30"/>
     </row>
     <row r="417" spans="1:11" ht="21.95" customHeight="1">
       <c r="A417" s="15" t="s">
@@ -15797,9 +15947,9 @@
         <v>0</v>
       </c>
       <c r="J417" s="12"/>
-      <c r="K417" s="31"/>
-    </row>
-    <row r="418" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K417" s="30"/>
+    </row>
+    <row r="418" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A418" s="15" t="s">
         <v>548</v>
       </c>
@@ -15828,7 +15978,7 @@
         <v>0</v>
       </c>
       <c r="J418" s="12"/>
-      <c r="K418" s="31"/>
+      <c r="K418" s="30"/>
     </row>
     <row r="419" spans="1:11" ht="21.95" customHeight="1">
       <c r="A419" s="15" t="s">
@@ -15859,9 +16009,9 @@
         <v>324.8</v>
       </c>
       <c r="J419" s="12"/>
-      <c r="K419" s="31"/>
-    </row>
-    <row r="420" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K419" s="30"/>
+    </row>
+    <row r="420" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A420" s="15" t="s">
         <v>550</v>
       </c>
@@ -15892,7 +16042,7 @@
         <v>357</v>
       </c>
       <c r="J420" s="12"/>
-      <c r="K420" s="31"/>
+      <c r="K420" s="30"/>
     </row>
     <row r="421" spans="1:11" ht="21.95" customHeight="1">
       <c r="A421" s="15" t="s">
@@ -15921,7 +16071,7 @@
         <v>0</v>
       </c>
       <c r="J421" s="12"/>
-      <c r="K421" s="31"/>
+      <c r="K421" s="30"/>
     </row>
     <row r="422" spans="1:11" ht="21.95" customHeight="1">
       <c r="A422" s="15" t="s">
@@ -15950,7 +16100,7 @@
         <v>0</v>
       </c>
       <c r="J422" s="12"/>
-      <c r="K422" s="31"/>
+      <c r="K422" s="30"/>
     </row>
     <row r="423" spans="1:11" ht="21.95" customHeight="1">
       <c r="A423" s="15" t="s">
@@ -15981,7 +16131,7 @@
         <v>300.3</v>
       </c>
       <c r="J423" s="12"/>
-      <c r="K423" s="31"/>
+      <c r="K423" s="30"/>
     </row>
     <row r="424" spans="1:11" ht="21.95" customHeight="1">
       <c r="A424" s="15" t="s">
@@ -16012,7 +16162,7 @@
         <v>329</v>
       </c>
       <c r="J424" s="12"/>
-      <c r="K424" s="31"/>
+      <c r="K424" s="30"/>
     </row>
     <row r="425" spans="1:11" ht="21.95" customHeight="1">
       <c r="A425" s="15" t="s">
@@ -16040,8 +16190,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B425,İndirimler!$B$2:$B$110,C425)&gt;0,ROUND(G425*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B425,İndirimler!$B$2:$B$110,C425)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J425" s="12"/>
-      <c r="K425" s="31"/>
+      <c r="J425" s="32" t="s">
+        <v>671</v>
+      </c>
+      <c r="K425" s="30"/>
     </row>
     <row r="426" spans="1:11" ht="21.95" customHeight="1">
       <c r="A426" s="15" t="s">
@@ -16072,7 +16224,7 @@
         <v>461.3</v>
       </c>
       <c r="J426" s="12"/>
-      <c r="K426" s="31"/>
+      <c r="K426" s="30"/>
     </row>
     <row r="427" spans="1:11" ht="21.95" customHeight="1">
       <c r="A427" s="15" t="s">
@@ -16101,9 +16253,9 @@
         <v>0</v>
       </c>
       <c r="J427" s="12"/>
-      <c r="K427" s="31"/>
-    </row>
-    <row r="428" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K427" s="30"/>
+    </row>
+    <row r="428" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A428" s="15" t="s">
         <v>560</v>
       </c>
@@ -16136,7 +16288,7 @@
       <c r="J428" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="K428" s="31"/>
+      <c r="K428" s="30"/>
     </row>
     <row r="429" spans="1:11" ht="21.95" customHeight="1">
       <c r="A429" s="15" t="s">
@@ -16167,7 +16319,7 @@
         <v>433.3</v>
       </c>
       <c r="J429" s="12"/>
-      <c r="K429" s="31"/>
+      <c r="K429" s="30"/>
     </row>
     <row r="430" spans="1:11" ht="21.95" customHeight="1">
       <c r="A430" s="15" t="s">
@@ -16200,7 +16352,7 @@
       <c r="J430" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="K430" s="31"/>
+      <c r="K430" s="30"/>
     </row>
     <row r="431" spans="1:11" ht="21.95" customHeight="1">
       <c r="A431" s="15" t="s">
@@ -16230,8 +16382,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B431,İndirimler!$B$2:$B$110,C431)&gt;0,ROUND(G431*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B431,İndirimler!$B$2:$B$110,C431)),2),"")</f>
         <v>241.5</v>
       </c>
-      <c r="J431" s="12"/>
-      <c r="K431" s="31"/>
+      <c r="J431" s="32" t="s">
+        <v>688</v>
+      </c>
+      <c r="K431" s="30"/>
     </row>
     <row r="432" spans="1:11" ht="21.95" customHeight="1">
       <c r="A432" s="15" t="s">
@@ -16262,9 +16416,9 @@
         <v>241.5</v>
       </c>
       <c r="J432" s="12"/>
-      <c r="K432" s="31"/>
-    </row>
-    <row r="433" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K432" s="30"/>
+    </row>
+    <row r="433" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A433" s="15" t="s">
         <v>567</v>
       </c>
@@ -16297,9 +16451,9 @@
       <c r="J433" s="12" t="s">
         <v>568</v>
       </c>
-      <c r="K433" s="31"/>
-    </row>
-    <row r="434" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K433" s="30"/>
+    </row>
+    <row r="434" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A434" s="15" t="s">
         <v>569</v>
       </c>
@@ -16330,7 +16484,7 @@
         <v>314.3</v>
       </c>
       <c r="J434" s="12"/>
-      <c r="K434" s="31"/>
+      <c r="K434" s="30"/>
     </row>
     <row r="435" spans="1:11" ht="21.95" customHeight="1">
       <c r="A435" s="15" t="s">
@@ -16361,9 +16515,9 @@
         <v>406</v>
       </c>
       <c r="J435" s="12"/>
-      <c r="K435" s="31"/>
-    </row>
-    <row r="436" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K435" s="30"/>
+    </row>
+    <row r="436" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A436" s="15" t="s">
         <v>571</v>
       </c>
@@ -16394,9 +16548,9 @@
         <v>394.1</v>
       </c>
       <c r="J436" s="12"/>
-      <c r="K436" s="31"/>
-    </row>
-    <row r="437" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K436" s="30"/>
+    </row>
+    <row r="437" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A437" s="15" t="s">
         <v>572</v>
       </c>
@@ -16427,7 +16581,7 @@
         <v>269.5</v>
       </c>
       <c r="J437" s="12"/>
-      <c r="K437" s="31"/>
+      <c r="K437" s="30"/>
     </row>
     <row r="438" spans="1:11" ht="21.95" customHeight="1">
       <c r="A438" s="15" t="s">
@@ -16458,7 +16612,7 @@
         <v>318.5</v>
       </c>
       <c r="J438" s="12"/>
-      <c r="K438" s="31"/>
+      <c r="K438" s="30"/>
     </row>
     <row r="439" spans="1:11" ht="21.95" customHeight="1">
       <c r="A439" s="15" t="s">
@@ -16488,8 +16642,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B439,İndirimler!$B$2:$B$110,C439)&gt;0,ROUND(G439*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B439,İndirimler!$B$2:$B$110,C439)),2),"")</f>
         <v>290.5</v>
       </c>
-      <c r="J439" s="12"/>
-      <c r="K439" s="31"/>
+      <c r="J439" s="32" t="s">
+        <v>677</v>
+      </c>
+      <c r="K439" s="30"/>
     </row>
     <row r="440" spans="1:11" ht="21.95" customHeight="1">
       <c r="A440" s="15" t="s">
@@ -16520,7 +16676,7 @@
         <v>412.3</v>
       </c>
       <c r="J440" s="12"/>
-      <c r="K440" s="31"/>
+      <c r="K440" s="30"/>
     </row>
     <row r="441" spans="1:11" ht="21.95" customHeight="1">
       <c r="A441" s="15" t="s">
@@ -16549,9 +16705,9 @@
         <v>0</v>
       </c>
       <c r="J441" s="12"/>
-      <c r="K441" s="31"/>
-    </row>
-    <row r="442" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K441" s="30"/>
+    </row>
+    <row r="442" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A442" s="15" t="s">
         <v>577</v>
       </c>
@@ -16584,7 +16740,7 @@
       <c r="J442" s="12" t="s">
         <v>578</v>
       </c>
-      <c r="K442" s="31"/>
+      <c r="K442" s="30"/>
     </row>
     <row r="443" spans="1:11" ht="21.95" customHeight="1">
       <c r="A443" s="15" t="s">
@@ -16615,7 +16771,7 @@
         <v>439.6</v>
       </c>
       <c r="J443" s="12"/>
-      <c r="K443" s="31"/>
+      <c r="K443" s="30"/>
     </row>
     <row r="444" spans="1:11" ht="21.95" customHeight="1">
       <c r="A444" s="15" t="s">
@@ -16648,7 +16804,7 @@
       <c r="J444" s="12" t="s">
         <v>581</v>
       </c>
-      <c r="K444" s="31"/>
+      <c r="K444" s="30"/>
     </row>
     <row r="445" spans="1:11" ht="21.95" customHeight="1">
       <c r="A445" s="15" t="s">
@@ -16679,7 +16835,7 @@
         <v>206.5</v>
       </c>
       <c r="J445" s="12"/>
-      <c r="K445" s="31"/>
+      <c r="K445" s="30"/>
     </row>
     <row r="446" spans="1:11" ht="21.95" customHeight="1">
       <c r="A446" s="15" t="s">
@@ -16710,9 +16866,9 @@
         <v>251.3</v>
       </c>
       <c r="J446" s="12"/>
-      <c r="K446" s="31"/>
-    </row>
-    <row r="447" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K446" s="30"/>
+    </row>
+    <row r="447" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A447" s="15" t="s">
         <v>584</v>
       </c>
@@ -16745,9 +16901,9 @@
       <c r="J447" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="K447" s="31"/>
-    </row>
-    <row r="448" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K447" s="30"/>
+    </row>
+    <row r="448" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A448" s="15" t="s">
         <v>586</v>
       </c>
@@ -16778,7 +16934,7 @@
         <v>283.5</v>
       </c>
       <c r="J448" s="12"/>
-      <c r="K448" s="31"/>
+      <c r="K448" s="30"/>
     </row>
     <row r="449" spans="1:11" ht="21.95" customHeight="1">
       <c r="A449" s="15" t="s">
@@ -16809,9 +16965,9 @@
         <v>435.4</v>
       </c>
       <c r="J449" s="12"/>
-      <c r="K449" s="31"/>
-    </row>
-    <row r="450" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K449" s="30"/>
+    </row>
+    <row r="450" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A450" s="15" t="s">
         <v>588</v>
       </c>
@@ -16842,9 +16998,9 @@
         <v>332.5</v>
       </c>
       <c r="J450" s="12"/>
-      <c r="K450" s="31"/>
-    </row>
-    <row r="451" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K450" s="30"/>
+    </row>
+    <row r="451" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A451" s="15" t="s">
         <v>589</v>
       </c>
@@ -16875,7 +17031,7 @@
         <v>286.3</v>
       </c>
       <c r="J451" s="12"/>
-      <c r="K451" s="31"/>
+      <c r="K451" s="30"/>
     </row>
     <row r="452" spans="1:11" ht="21.95" customHeight="1">
       <c r="A452" s="15" t="s">
@@ -16906,7 +17062,7 @@
         <v>241.5</v>
       </c>
       <c r="J452" s="12"/>
-      <c r="K452" s="31"/>
+      <c r="K452" s="30"/>
     </row>
     <row r="453" spans="1:11" ht="21.95" customHeight="1">
       <c r="A453" s="15" t="s">
@@ -16935,7 +17091,7 @@
         <v>0</v>
       </c>
       <c r="J453" s="12"/>
-      <c r="K453" s="31"/>
+      <c r="K453" s="30"/>
     </row>
     <row r="454" spans="1:11" ht="21.95" customHeight="1">
       <c r="A454" s="15" t="s">
@@ -16964,9 +17120,9 @@
         <v>0</v>
       </c>
       <c r="J454" s="12"/>
-      <c r="K454" s="31"/>
-    </row>
-    <row r="455" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K454" s="30"/>
+    </row>
+    <row r="455" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A455" s="15" t="s">
         <v>593</v>
       </c>
@@ -16995,7 +17151,7 @@
         <v>0</v>
       </c>
       <c r="J455" s="12"/>
-      <c r="K455" s="31"/>
+      <c r="K455" s="30"/>
     </row>
     <row r="456" spans="1:11" ht="21.95" customHeight="1">
       <c r="A456" s="15" t="s">
@@ -17026,7 +17182,7 @@
         <v>348.6</v>
       </c>
       <c r="J456" s="12"/>
-      <c r="K456" s="31"/>
+      <c r="K456" s="30"/>
     </row>
     <row r="457" spans="1:11" ht="21.95" customHeight="1">
       <c r="A457" s="15" t="s">
@@ -17057,7 +17213,7 @@
         <v>242.2</v>
       </c>
       <c r="J457" s="12"/>
-      <c r="K457" s="31"/>
+      <c r="K457" s="30"/>
     </row>
     <row r="458" spans="1:11" ht="21.95" customHeight="1">
       <c r="A458" s="15" t="s">
@@ -17085,8 +17241,10 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B458,İndirimler!$B$2:$B$110,C458)&gt;0,ROUND(G458*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B458,İndirimler!$B$2:$B$110,C458)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J458" s="12"/>
-      <c r="K458" s="31"/>
+      <c r="J458" s="32" t="s">
+        <v>697</v>
+      </c>
+      <c r="K458" s="30"/>
     </row>
     <row r="459" spans="1:11" ht="21.95" customHeight="1">
       <c r="A459" s="15" t="s">
@@ -17115,9 +17273,9 @@
         <v>0</v>
       </c>
       <c r="J459" s="12"/>
-      <c r="K459" s="31"/>
-    </row>
-    <row r="460" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K459" s="30"/>
+    </row>
+    <row r="460" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A460" s="15" t="s">
         <v>598</v>
       </c>
@@ -17146,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="J460" s="12"/>
-      <c r="K460" s="31"/>
+      <c r="K460" s="30"/>
     </row>
     <row r="461" spans="1:11" ht="21.95" customHeight="1">
       <c r="A461" s="15" t="s">
@@ -17177,9 +17335,9 @@
         <v>343</v>
       </c>
       <c r="J461" s="12"/>
-      <c r="K461" s="31"/>
-    </row>
-    <row r="462" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K461" s="30"/>
+    </row>
+    <row r="462" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A462" s="15" t="s">
         <v>600</v>
       </c>
@@ -17210,7 +17368,7 @@
         <v>418.6</v>
       </c>
       <c r="J462" s="12"/>
-      <c r="K462" s="31"/>
+      <c r="K462" s="30"/>
     </row>
     <row r="463" spans="1:11" ht="21.95" customHeight="1">
       <c r="A463" s="15" t="s">
@@ -17239,7 +17397,7 @@
         <v>0</v>
       </c>
       <c r="J463" s="12"/>
-      <c r="K463" s="31"/>
+      <c r="K463" s="30"/>
     </row>
     <row r="464" spans="1:11" ht="21.95" customHeight="1">
       <c r="A464" s="15" t="s">
@@ -17268,7 +17426,7 @@
         <v>0</v>
       </c>
       <c r="J464" s="12"/>
-      <c r="K464" s="31"/>
+      <c r="K464" s="30"/>
     </row>
     <row r="465" spans="1:11" ht="21.95" customHeight="1">
       <c r="A465" s="15" t="s">
@@ -17299,7 +17457,7 @@
         <v>321.3</v>
       </c>
       <c r="J465" s="12"/>
-      <c r="K465" s="31"/>
+      <c r="K465" s="30"/>
     </row>
     <row r="466" spans="1:11" ht="21.95" customHeight="1">
       <c r="A466" s="15" t="s">
@@ -17330,7 +17488,7 @@
         <v>300.3</v>
       </c>
       <c r="J466" s="12"/>
-      <c r="K466" s="31"/>
+      <c r="K466" s="30"/>
     </row>
     <row r="467" spans="1:11" ht="21.95" customHeight="1">
       <c r="A467" s="15" t="s">
@@ -17361,9 +17519,9 @@
         <v>329</v>
       </c>
       <c r="J467" s="12"/>
-      <c r="K467" s="31"/>
-    </row>
-    <row r="468" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K467" s="30"/>
+    </row>
+    <row r="468" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A468" s="15" t="s">
         <v>606</v>
       </c>
@@ -17396,7 +17554,7 @@
       <c r="J468" s="12" t="s">
         <v>608</v>
       </c>
-      <c r="K468" s="31"/>
+      <c r="K468" s="30"/>
     </row>
     <row r="469" spans="1:11" ht="21.95" customHeight="1">
       <c r="A469" s="15" t="s">
@@ -17429,7 +17587,7 @@
       <c r="J469" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="K469" s="31"/>
+      <c r="K469" s="30"/>
     </row>
     <row r="470" spans="1:11" ht="21.95" customHeight="1">
       <c r="A470" s="15" t="s">
@@ -17459,10 +17617,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B470,İndirimler!$B$2:$B$110,C470)&gt;0,ROUND(G470*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B470,İndirimler!$B$2:$B$110,C470)),2),"")</f>
         <v>188.3</v>
       </c>
-      <c r="J470" s="12"/>
-      <c r="K470" s="31"/>
-    </row>
-    <row r="471" spans="1:11" ht="21.95" customHeight="1">
+      <c r="J470" s="32" t="s">
+        <v>695</v>
+      </c>
+      <c r="K470" s="30"/>
+    </row>
+    <row r="471" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A471" s="15" t="s">
         <v>612</v>
       </c>
@@ -17495,9 +17655,9 @@
       <c r="J471" s="12" t="s">
         <v>613</v>
       </c>
-      <c r="K471" s="31"/>
-    </row>
-    <row r="472" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K471" s="30"/>
+    </row>
+    <row r="472" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A472" s="15" t="s">
         <v>614</v>
       </c>
@@ -17528,9 +17688,9 @@
         <v>394.1</v>
       </c>
       <c r="J472" s="12"/>
-      <c r="K472" s="31"/>
-    </row>
-    <row r="473" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K472" s="30"/>
+    </row>
+    <row r="473" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A473" s="15" t="s">
         <v>615</v>
       </c>
@@ -17561,9 +17721,9 @@
         <v>241.5</v>
       </c>
       <c r="J473" s="12"/>
-      <c r="K473" s="31"/>
-    </row>
-    <row r="474" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K473" s="30"/>
+    </row>
+    <row r="474" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A474" s="15" t="s">
         <v>616</v>
       </c>
@@ -17592,7 +17752,7 @@
         <v>0</v>
       </c>
       <c r="J474" s="12"/>
-      <c r="K474" s="31"/>
+      <c r="K474" s="30"/>
     </row>
     <row r="475" spans="1:11" ht="21.95" customHeight="1">
       <c r="A475" s="15" t="s">
@@ -17623,7 +17783,7 @@
         <v>236.6</v>
       </c>
       <c r="J475" s="12"/>
-      <c r="K475" s="31"/>
+      <c r="K475" s="30"/>
     </row>
     <row r="476" spans="1:11" ht="21.95" customHeight="1">
       <c r="A476" s="15" t="s">
@@ -17654,7 +17814,7 @@
         <v>179.2</v>
       </c>
       <c r="J476" s="12"/>
-      <c r="K476" s="31"/>
+      <c r="K476" s="30"/>
     </row>
     <row r="477" spans="1:11" ht="21.95" customHeight="1">
       <c r="A477" s="15" t="s">
@@ -17683,9 +17843,9 @@
         <v>0</v>
       </c>
       <c r="J477" s="12"/>
-      <c r="K477" s="31"/>
-    </row>
-    <row r="478" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K477" s="30"/>
+    </row>
+    <row r="478" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A478" s="15" t="s">
         <v>620</v>
       </c>
@@ -17716,7 +17876,7 @@
         <v>345.1</v>
       </c>
       <c r="J478" s="12"/>
-      <c r="K478" s="31"/>
+      <c r="K478" s="30"/>
     </row>
     <row r="479" spans="1:11" ht="21.95" customHeight="1">
       <c r="A479" s="15" t="s">
@@ -17745,7 +17905,7 @@
         <v>0</v>
       </c>
       <c r="J479" s="12"/>
-      <c r="K479" s="31"/>
+      <c r="K479" s="30"/>
     </row>
     <row r="480" spans="1:11" ht="21.95" customHeight="1">
       <c r="A480" s="15" t="s">
@@ -17774,7 +17934,7 @@
         <v>0</v>
       </c>
       <c r="J480" s="12"/>
-      <c r="K480" s="31"/>
+      <c r="K480" s="30"/>
     </row>
     <row r="481" spans="1:11" ht="21.95" customHeight="1">
       <c r="A481" s="15" t="s">
@@ -17805,7 +17965,7 @@
         <v>300.3</v>
       </c>
       <c r="J481" s="12"/>
-      <c r="K481" s="31"/>
+      <c r="K481" s="30"/>
     </row>
     <row r="482" spans="1:11" ht="21.95" customHeight="1">
       <c r="A482" s="15" t="s">
@@ -17834,7 +17994,7 @@
         <v>0</v>
       </c>
       <c r="J482" s="12"/>
-      <c r="K482" s="31"/>
+      <c r="K482" s="30"/>
     </row>
     <row r="483" spans="1:11" ht="21.95" customHeight="1">
       <c r="A483" s="15" t="s">
@@ -17863,7 +18023,7 @@
         <v>0</v>
       </c>
       <c r="J483" s="12"/>
-      <c r="K483" s="31"/>
+      <c r="K483" s="30"/>
     </row>
     <row r="484" spans="1:11" ht="21.95" customHeight="1">
       <c r="A484" s="15" t="s">
@@ -17894,7 +18054,7 @@
         <v>111.3</v>
       </c>
       <c r="J484" s="12"/>
-      <c r="K484" s="31"/>
+      <c r="K484" s="30"/>
     </row>
     <row r="485" spans="1:11" ht="21.95" customHeight="1">
       <c r="A485" s="15" t="s">
@@ -17923,7 +18083,7 @@
         <v>0</v>
       </c>
       <c r="J485" s="12"/>
-      <c r="K485" s="31"/>
+      <c r="K485" s="30"/>
     </row>
     <row r="486" spans="1:11" ht="21.95" customHeight="1">
       <c r="A486" s="15" t="s">
@@ -17952,9 +18112,9 @@
         <v>0</v>
       </c>
       <c r="J486" s="12"/>
-      <c r="K486" s="31"/>
-    </row>
-    <row r="487" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K486" s="30"/>
+    </row>
+    <row r="487" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A487" s="15" t="s">
         <v>633</v>
       </c>
@@ -17985,9 +18145,9 @@
         <v>197.4</v>
       </c>
       <c r="J487" s="12"/>
-      <c r="K487" s="31"/>
-    </row>
-    <row r="488" spans="1:11" ht="21.95" customHeight="1">
+      <c r="K487" s="30"/>
+    </row>
+    <row r="488" spans="1:11" ht="21.95" hidden="1" customHeight="1">
       <c r="A488" s="16" t="s">
         <v>635</v>
       </c>
@@ -18018,12 +18178,43 @@
         <v>197.4</v>
       </c>
       <c r="J488" s="13"/>
-      <c r="K488" s="31"/>
+      <c r="K488" s="30"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J9" r:id="rId1" xr:uid="{8C6DB0BA-CEEB-4CF7-8B54-60593DBEE7A1}"/>
+    <hyperlink ref="J387" r:id="rId2" xr:uid="{CC6FADDF-A406-4847-9A40-C2540ECABA09}"/>
+    <hyperlink ref="J425" r:id="rId3" xr:uid="{B3D1E1FD-2E5B-4A11-9270-2D27D13D4171}"/>
+    <hyperlink ref="J59" r:id="rId4" xr:uid="{41FB5A73-7FBF-499C-A0F8-3FA0D2A05940}"/>
+    <hyperlink ref="J179" r:id="rId5" xr:uid="{F77B3188-B978-4877-8F93-2D53418D09A6}"/>
+    <hyperlink ref="J257" r:id="rId6" xr:uid="{8B027415-6E9D-4E50-9D68-04636C30D73F}"/>
+    <hyperlink ref="J324" r:id="rId7" xr:uid="{3FB72921-B159-43A8-858E-75489287861B}"/>
+    <hyperlink ref="J25" r:id="rId8" xr:uid="{22838C02-7B06-4362-9921-6FC80FBF0C98}"/>
+    <hyperlink ref="J439" r:id="rId9" xr:uid="{4CBE1E4A-C028-4CCB-AA65-DCBD0FDC1B46}"/>
+    <hyperlink ref="J87" r:id="rId10" xr:uid="{3C521EDC-45FF-40A8-A49E-65591AFBEFED}"/>
+    <hyperlink ref="J200" r:id="rId11" xr:uid="{0CF292ED-5205-4121-A062-5C452A2836D9}"/>
+    <hyperlink ref="J276" r:id="rId12" xr:uid="{73405A1F-C922-4CB3-9C65-69FF144BC058}"/>
+    <hyperlink ref="J343" r:id="rId13" xr:uid="{AAEDFD06-DFAB-4807-94EF-FC1012E837AF}"/>
+    <hyperlink ref="J17" r:id="rId14" xr:uid="{65A4602F-4358-43C2-8A9F-CF064622CE3D}"/>
+    <hyperlink ref="J71" r:id="rId15" xr:uid="{F0A67BD1-B7EB-414E-8F6B-93DE4405A3F7}"/>
+    <hyperlink ref="J189" r:id="rId16" xr:uid="{B97F3044-A7B1-464F-BDB5-FA9DEFDD0A7B}"/>
+    <hyperlink ref="J267" r:id="rId17" xr:uid="{A2B64DA9-83FA-43CE-A566-BB378FA18C53}"/>
+    <hyperlink ref="J393" r:id="rId18" xr:uid="{D67679FD-7B46-4DB7-AAF1-DB6593A50CBB}"/>
+    <hyperlink ref="J333" r:id="rId19" xr:uid="{EF5FEB81-AFE8-491E-831E-482627E0E45F}"/>
+    <hyperlink ref="J431" r:id="rId20" xr:uid="{59BB561E-6B82-42B1-81BC-BD60610BE6A9}"/>
+    <hyperlink ref="J32" r:id="rId21" xr:uid="{E16D1878-B413-4FB8-BF92-303F64937C27}"/>
+    <hyperlink ref="J98" r:id="rId22" xr:uid="{F0107520-F089-46D5-8A9A-BC2A4C8E441D}"/>
+    <hyperlink ref="J210" r:id="rId23" xr:uid="{9749174A-8154-4606-8743-036581E65142}"/>
+    <hyperlink ref="J286" r:id="rId24" xr:uid="{9539A062-3C74-4158-B220-DA675010CC20}"/>
+    <hyperlink ref="J352" r:id="rId25" xr:uid="{519D8CE8-CD80-47BA-A150-2F9AD7CE9AC1}"/>
+    <hyperlink ref="J405" r:id="rId26" xr:uid="{FCCD0D33-CF1B-41CC-A0EF-98C7A8CF3F31}"/>
+    <hyperlink ref="J470" r:id="rId27" xr:uid="{31A01E12-6AC8-4177-8B2D-7CFCD44E8417}"/>
+    <hyperlink ref="J304" r:id="rId28" xr:uid="{A4AE380D-4B87-4437-BB89-4773F040D583}"/>
+    <hyperlink ref="J458" r:id="rId29" xr:uid="{8A06FEE5-F34A-44C9-A3D0-3F22C02299CA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId30"/>
   </tableParts>
 </worksheet>
 </file>
@@ -18033,9 +18224,10 @@
   <dimension ref="A1:D110"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="19" customWidth="1"/>
+    <col min="1" max="1" width="23.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
@@ -19656,14 +19848,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="42" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>647</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="3" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A3" s="26" t="s">

--- a/output/Fiyat-Listesi-Yonetim.xlsx
+++ b/output/Fiyat-Listesi-Yonetim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALS\Documents\26-27 Fiyat Listeleri\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDCFB12-6446-4849-9699-1DBEB15D93EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA907828-5C1E-40B6-BEAE-17F90CC61F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2374,10 +2374,10 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2404,11 +2404,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UrunlerTablosu" displayName="UrunlerTablosu" ref="A1:K488" totalsRowShown="0">
-  <autoFilter ref="A1:K488" xr:uid="{00000000-0009-0000-0100-000002000000}">
-    <filterColumn colId="4">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Barkod"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Yayın"/>
@@ -2681,7 +2676,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="2" spans="1:11" ht="21.95" customHeight="1">
       <c r="A2" s="14" t="s">
         <v>10</v>
       </c>
@@ -2745,7 +2740,7 @@
       <c r="J3" s="12"/>
       <c r="K3" s="30"/>
     </row>
-    <row r="4" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="4" spans="1:11" ht="21.95" customHeight="1">
       <c r="A4" s="15" t="s">
         <v>18</v>
       </c>
@@ -2809,7 +2804,7 @@
       <c r="J5" s="12"/>
       <c r="K5" s="30"/>
     </row>
-    <row r="6" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="6" spans="1:11" ht="21.95" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>22</v>
       </c>
@@ -2840,7 +2835,7 @@
       <c r="J6" s="12"/>
       <c r="K6" s="30"/>
     </row>
-    <row r="7" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="7" spans="1:11" ht="21.95" customHeight="1">
       <c r="A7" s="15" t="s">
         <v>25</v>
       </c>
@@ -2871,7 +2866,7 @@
       <c r="J7" s="12"/>
       <c r="K7" s="30"/>
     </row>
-    <row r="8" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="8" spans="1:11" ht="21.95" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>27</v>
       </c>
@@ -2932,7 +2927,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B9,İndirimler!$B$2:$B$110,C9)&gt;0,ROUND(G9*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B9,İndirimler!$B$2:$B$110,C9)),2),"")</f>
         <v>384.3</v>
       </c>
-      <c r="J9" s="32" t="s">
+      <c r="J9" s="31" t="s">
         <v>669</v>
       </c>
       <c r="K9" s="30"/>
@@ -2968,7 +2963,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="30"/>
     </row>
-    <row r="11" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="11" spans="1:11" ht="21.95" customHeight="1">
       <c r="A11" s="15" t="s">
         <v>36</v>
       </c>
@@ -2999,7 +2994,7 @@
       <c r="J11" s="12"/>
       <c r="K11" s="30"/>
     </row>
-    <row r="12" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="12" spans="1:11" ht="21.95" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>39</v>
       </c>
@@ -3065,7 +3060,7 @@
       <c r="J13" s="12"/>
       <c r="K13" s="30"/>
     </row>
-    <row r="14" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="14" spans="1:11" ht="21.95" customHeight="1">
       <c r="A14" s="15" t="s">
         <v>44</v>
       </c>
@@ -3190,12 +3185,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B17,İndirimler!$B$2:$B$110,C17)&gt;0,ROUND(G17*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B17,İndirimler!$B$2:$B$110,C17)),2),"")</f>
         <v>230.3</v>
       </c>
-      <c r="J17" s="32" t="s">
+      <c r="J17" s="31" t="s">
         <v>682</v>
       </c>
       <c r="K17" s="30"/>
     </row>
-    <row r="18" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="18" spans="1:11" ht="21.95" customHeight="1">
       <c r="A18" s="15" t="s">
         <v>53</v>
       </c>
@@ -3230,7 +3225,7 @@
       </c>
       <c r="K18" s="30"/>
     </row>
-    <row r="19" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="19" spans="1:11" ht="21.95" customHeight="1">
       <c r="A19" s="15" t="s">
         <v>56</v>
       </c>
@@ -3294,7 +3289,7 @@
       <c r="J20" s="12"/>
       <c r="K20" s="30"/>
     </row>
-    <row r="21" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="21" spans="1:11" ht="21.95" customHeight="1">
       <c r="A21" s="15" t="s">
         <v>60</v>
       </c>
@@ -3327,7 +3322,7 @@
       <c r="J21" s="12"/>
       <c r="K21" s="30"/>
     </row>
-    <row r="22" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="22" spans="1:11" ht="21.95" customHeight="1">
       <c r="A22" s="15" t="s">
         <v>62</v>
       </c>
@@ -3450,7 +3445,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B25,İndirimler!$B$2:$B$110,C25)&gt;0,ROUND(G25*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B25,İndirimler!$B$2:$B$110,C25)),2),"")</f>
         <v>370.3</v>
       </c>
-      <c r="J25" s="32" t="s">
+      <c r="J25" s="31" t="s">
         <v>676</v>
       </c>
       <c r="K25" s="30"/>
@@ -3486,7 +3481,7 @@
       <c r="J26" s="12"/>
       <c r="K26" s="30"/>
     </row>
-    <row r="27" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="27" spans="1:11" ht="21.95" customHeight="1">
       <c r="A27" s="15" t="s">
         <v>70</v>
       </c>
@@ -3517,7 +3512,7 @@
       <c r="J27" s="12"/>
       <c r="K27" s="30"/>
     </row>
-    <row r="28" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="28" spans="1:11" ht="21.95" customHeight="1">
       <c r="A28" s="15" t="s">
         <v>71</v>
       </c>
@@ -3583,7 +3578,7 @@
       <c r="J29" s="12"/>
       <c r="K29" s="30"/>
     </row>
-    <row r="30" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="30" spans="1:11" ht="21.95" customHeight="1">
       <c r="A30" s="15" t="s">
         <v>74</v>
       </c>
@@ -3677,12 +3672,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B32,İndirimler!$B$2:$B$110,C32)&gt;0,ROUND(G32*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B32,İndirimler!$B$2:$B$110,C32)),2),"")</f>
         <v>335.3</v>
       </c>
-      <c r="J32" s="32" t="s">
+      <c r="J32" s="31" t="s">
         <v>689</v>
       </c>
       <c r="K32" s="30"/>
     </row>
-    <row r="33" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="33" spans="1:11" ht="21.95" customHeight="1">
       <c r="A33" s="15" t="s">
         <v>78</v>
       </c>
@@ -3717,7 +3712,7 @@
       </c>
       <c r="K33" s="30"/>
     </row>
-    <row r="34" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="34" spans="1:11" ht="21.95" customHeight="1">
       <c r="A34" s="15" t="s">
         <v>80</v>
       </c>
@@ -3781,7 +3776,7 @@
       <c r="J35" s="12"/>
       <c r="K35" s="30"/>
     </row>
-    <row r="36" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="36" spans="1:11" ht="21.95" customHeight="1">
       <c r="A36" s="15" t="s">
         <v>82</v>
       </c>
@@ -3845,7 +3840,7 @@
       <c r="J37" s="12"/>
       <c r="K37" s="30"/>
     </row>
-    <row r="38" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="38" spans="1:11" ht="21.95" customHeight="1">
       <c r="A38" s="15" t="s">
         <v>84</v>
       </c>
@@ -3938,7 +3933,7 @@
       <c r="J40" s="12"/>
       <c r="K40" s="30"/>
     </row>
-    <row r="41" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="41" spans="1:11" ht="21.95" customHeight="1">
       <c r="A41" s="15" t="s">
         <v>88</v>
       </c>
@@ -3969,7 +3964,7 @@
       <c r="J41" s="12"/>
       <c r="K41" s="30"/>
     </row>
-    <row r="42" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="42" spans="1:11" ht="21.95" customHeight="1">
       <c r="A42" s="15" t="s">
         <v>89</v>
       </c>
@@ -4031,7 +4026,7 @@
       <c r="J43" s="12"/>
       <c r="K43" s="30"/>
     </row>
-    <row r="44" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="44" spans="1:11" ht="21.95" customHeight="1">
       <c r="A44" s="15" t="s">
         <v>92</v>
       </c>
@@ -4124,7 +4119,7 @@
       <c r="J46" s="12"/>
       <c r="K46" s="30"/>
     </row>
-    <row r="47" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="47" spans="1:11" ht="21.95" customHeight="1">
       <c r="A47" s="15" t="s">
         <v>95</v>
       </c>
@@ -4186,7 +4181,7 @@
       <c r="J48" s="12"/>
       <c r="K48" s="30"/>
     </row>
-    <row r="49" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="49" spans="1:11" ht="21.95" customHeight="1">
       <c r="A49" s="15" t="s">
         <v>97</v>
       </c>
@@ -4306,7 +4301,7 @@
       <c r="J52" s="12"/>
       <c r="K52" s="30"/>
     </row>
-    <row r="53" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="53" spans="1:11" ht="21.95" customHeight="1">
       <c r="A53" s="15" t="s">
         <v>101</v>
       </c>
@@ -4339,7 +4334,7 @@
       <c r="J53" s="12"/>
       <c r="K53" s="30"/>
     </row>
-    <row r="54" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="54" spans="1:11" ht="21.95" customHeight="1">
       <c r="A54" s="15" t="s">
         <v>102</v>
       </c>
@@ -4372,7 +4367,7 @@
       <c r="J54" s="12"/>
       <c r="K54" s="30"/>
     </row>
-    <row r="55" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="55" spans="1:11" ht="21.95" customHeight="1">
       <c r="A55" s="15" t="s">
         <v>105</v>
       </c>
@@ -4405,7 +4400,7 @@
       <c r="J55" s="12"/>
       <c r="K55" s="30"/>
     </row>
-    <row r="56" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="56" spans="1:11" ht="21.95" customHeight="1">
       <c r="A56" s="15" t="s">
         <v>106</v>
       </c>
@@ -4436,7 +4431,7 @@
       <c r="J56" s="12"/>
       <c r="K56" s="30"/>
     </row>
-    <row r="57" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="57" spans="1:11" ht="21.95" customHeight="1">
       <c r="A57" s="15" t="s">
         <v>109</v>
       </c>
@@ -4469,7 +4464,7 @@
       <c r="J57" s="12"/>
       <c r="K57" s="30"/>
     </row>
-    <row r="58" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="58" spans="1:11" ht="21.95" customHeight="1">
       <c r="A58" s="15" t="s">
         <v>110</v>
       </c>
@@ -4532,7 +4527,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B59,İndirimler!$B$2:$B$110,C59)&gt;0,ROUND(G59*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B59,İndirimler!$B$2:$B$110,C59)),2),"")</f>
         <v>489.3</v>
       </c>
-      <c r="J59" s="32" t="s">
+      <c r="J59" s="31" t="s">
         <v>672</v>
       </c>
       <c r="K59" s="30"/>
@@ -4599,7 +4594,7 @@
       <c r="J61" s="12"/>
       <c r="K61" s="30"/>
     </row>
-    <row r="62" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="62" spans="1:11" ht="21.95" customHeight="1">
       <c r="A62" s="15" t="s">
         <v>118</v>
       </c>
@@ -4632,7 +4627,7 @@
       <c r="J62" s="12"/>
       <c r="K62" s="30"/>
     </row>
-    <row r="63" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="63" spans="1:11" ht="21.95" customHeight="1">
       <c r="A63" s="15" t="s">
         <v>121</v>
       </c>
@@ -4667,7 +4662,7 @@
       </c>
       <c r="K63" s="30"/>
     </row>
-    <row r="64" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="64" spans="1:11" ht="21.95" customHeight="1">
       <c r="A64" s="15" t="s">
         <v>124</v>
       </c>
@@ -4700,7 +4695,7 @@
       <c r="J64" s="12"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="65" spans="1:11" ht="21.95" customHeight="1">
       <c r="A65" s="15" t="s">
         <v>125</v>
       </c>
@@ -4733,7 +4728,7 @@
       <c r="J65" s="12"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="66" spans="1:11" ht="21.95" customHeight="1">
       <c r="A66" s="15" t="s">
         <v>126</v>
       </c>
@@ -4766,7 +4761,7 @@
       <c r="J66" s="12"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="67" spans="1:11" ht="21.95" customHeight="1">
       <c r="A67" s="15" t="s">
         <v>128</v>
       </c>
@@ -4832,7 +4827,7 @@
       <c r="J68" s="12"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="69" spans="1:11" ht="21.95" customHeight="1">
       <c r="A69" s="15" t="s">
         <v>131</v>
       </c>
@@ -4865,7 +4860,7 @@
       <c r="J69" s="12"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="70" spans="1:11" ht="21.95" customHeight="1">
       <c r="A70" s="15" t="s">
         <v>133</v>
       </c>
@@ -4926,12 +4921,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B71,İndirimler!$B$2:$B$110,C71)&gt;0,ROUND(G71*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B71,İndirimler!$B$2:$B$110,C71)),2),"")</f>
         <v>433.3</v>
       </c>
-      <c r="J71" s="32" t="s">
+      <c r="J71" s="31" t="s">
         <v>683</v>
       </c>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="72" spans="1:11" ht="21.95" customHeight="1">
       <c r="A72" s="15" t="s">
         <v>135</v>
       </c>
@@ -4948,7 +4943,7 @@
         <v>37</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G72" s="18">
         <v>799</v>
@@ -4964,7 +4959,7 @@
       <c r="J72" s="12"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="73" spans="1:11" ht="21.95" customHeight="1">
       <c r="A73" s="15" t="s">
         <v>136</v>
       </c>
@@ -4999,7 +4994,7 @@
       </c>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="74" spans="1:11" ht="21.95" customHeight="1">
       <c r="A74" s="15" t="s">
         <v>139</v>
       </c>
@@ -5032,7 +5027,7 @@
       <c r="J74" s="12"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="75" spans="1:11" ht="21.95" customHeight="1">
       <c r="A75" s="15" t="s">
         <v>141</v>
       </c>
@@ -5065,7 +5060,7 @@
       <c r="J75" s="12"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="76" spans="1:11" ht="21.95" customHeight="1">
       <c r="A76" s="15" t="s">
         <v>142</v>
       </c>
@@ -5098,7 +5093,7 @@
       <c r="J76" s="12"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="77" spans="1:11" ht="21.95" customHeight="1">
       <c r="A77" s="15" t="s">
         <v>143</v>
       </c>
@@ -5129,7 +5124,7 @@
       <c r="J77" s="12"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="78" spans="1:11" ht="21.95" customHeight="1">
       <c r="A78" s="15" t="s">
         <v>144</v>
       </c>
@@ -5224,7 +5219,7 @@
       <c r="J80" s="12"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="81" spans="1:11" ht="21.95" customHeight="1">
       <c r="A81" s="15" t="s">
         <v>147</v>
       </c>
@@ -5288,7 +5283,7 @@
       <c r="J82" s="12"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="83" spans="1:11" ht="21.95" customHeight="1">
       <c r="A83" s="15" t="s">
         <v>149</v>
       </c>
@@ -5321,7 +5316,7 @@
       <c r="J83" s="12"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="84" spans="1:11" ht="21.95" customHeight="1">
       <c r="A84" s="15" t="s">
         <v>150</v>
       </c>
@@ -5352,7 +5347,7 @@
       <c r="J84" s="12"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="85" spans="1:11" ht="21.95" customHeight="1">
       <c r="A85" s="15" t="s">
         <v>151</v>
       </c>
@@ -5385,7 +5380,7 @@
       <c r="J85" s="12"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="86" spans="1:11" ht="21.95" customHeight="1">
       <c r="A86" s="15" t="s">
         <v>152</v>
       </c>
@@ -5446,7 +5441,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B87,İndirimler!$B$2:$B$110,C87)&gt;0,ROUND(G87*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B87,İndirimler!$B$2:$B$110,C87)),2),"")</f>
         <v>517.29999999999995</v>
       </c>
-      <c r="J87" s="32" t="s">
+      <c r="J87" s="31" t="s">
         <v>678</v>
       </c>
       <c r="K87" s="30"/>
@@ -5513,7 +5508,7 @@
       <c r="J89" s="12"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="90" spans="1:11" ht="21.95" customHeight="1">
       <c r="A90" s="15" t="s">
         <v>156</v>
       </c>
@@ -5546,7 +5541,7 @@
       <c r="J90" s="12"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="91" spans="1:11" ht="21.95" customHeight="1">
       <c r="A91" s="15" t="s">
         <v>157</v>
       </c>
@@ -5581,7 +5576,7 @@
       </c>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="92" spans="1:11" ht="21.95" customHeight="1">
       <c r="A92" s="15" t="s">
         <v>159</v>
       </c>
@@ -5614,7 +5609,7 @@
       <c r="J92" s="12"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="93" spans="1:11" ht="21.95" customHeight="1">
       <c r="A93" s="15" t="s">
         <v>160</v>
       </c>
@@ -5647,7 +5642,7 @@
       <c r="J93" s="12"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="94" spans="1:11" ht="21.95" customHeight="1">
       <c r="A94" s="15" t="s">
         <v>161</v>
       </c>
@@ -5713,7 +5708,7 @@
       <c r="J95" s="12"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="96" spans="1:11" ht="21.95" customHeight="1">
       <c r="A96" s="15" t="s">
         <v>164</v>
       </c>
@@ -5746,7 +5741,7 @@
       <c r="J96" s="12"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="97" spans="1:11" ht="21.95" customHeight="1">
       <c r="A97" s="15" t="s">
         <v>165</v>
       </c>
@@ -5807,12 +5802,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B98,İndirimler!$B$2:$B$110,C98)&gt;0,ROUND(G98*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B98,İndirimler!$B$2:$B$110,C98)),2),"")</f>
         <v>479.5</v>
       </c>
-      <c r="J98" s="32" t="s">
+      <c r="J98" s="31" t="s">
         <v>690</v>
       </c>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="99" spans="1:11" ht="21.95" customHeight="1">
       <c r="A99" s="15" t="s">
         <v>167</v>
       </c>
@@ -5829,7 +5824,7 @@
         <v>37</v>
       </c>
       <c r="F99" s="12" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G99" s="18">
         <v>819</v>
@@ -5845,7 +5840,7 @@
       <c r="J99" s="12"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="100" spans="1:11" ht="21.95" customHeight="1">
       <c r="A100" s="15" t="s">
         <v>168</v>
       </c>
@@ -5911,7 +5906,7 @@
       <c r="J101" s="12"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="102" spans="1:11" ht="21.95" customHeight="1">
       <c r="A102" s="15" t="s">
         <v>171</v>
       </c>
@@ -5944,7 +5939,7 @@
       <c r="J102" s="12"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="103" spans="1:11" ht="21.95" customHeight="1">
       <c r="A103" s="15" t="s">
         <v>172</v>
       </c>
@@ -5977,7 +5972,7 @@
       <c r="J103" s="12"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="104" spans="1:11" ht="21.95" customHeight="1">
       <c r="A104" s="15" t="s">
         <v>173</v>
       </c>
@@ -6008,7 +6003,7 @@
       <c r="J104" s="12"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="105" spans="1:11" ht="21.95" customHeight="1">
       <c r="A105" s="15" t="s">
         <v>174</v>
       </c>
@@ -6103,7 +6098,7 @@
       <c r="J107" s="12"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="108" spans="1:11" ht="21.95" customHeight="1">
       <c r="A108" s="15" t="s">
         <v>177</v>
       </c>
@@ -6196,7 +6191,7 @@
       <c r="J110" s="12"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="111" spans="1:11" ht="21.95" customHeight="1">
       <c r="A111" s="15" t="s">
         <v>180</v>
       </c>
@@ -6227,7 +6222,7 @@
       <c r="J111" s="12"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="112" spans="1:11" ht="21.95" customHeight="1">
       <c r="A112" s="15" t="s">
         <v>181</v>
       </c>
@@ -6258,7 +6253,7 @@
       <c r="J112" s="12"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="113" spans="1:11" ht="21.95" customHeight="1">
       <c r="A113" s="15" t="s">
         <v>182</v>
       </c>
@@ -6349,7 +6344,7 @@
       <c r="J115" s="12"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="116" spans="1:11" ht="21.95" customHeight="1">
       <c r="A116" s="15" t="s">
         <v>187</v>
       </c>
@@ -6382,7 +6377,7 @@
       <c r="J116" s="12"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="117" spans="1:11" ht="21.95" customHeight="1">
       <c r="A117" s="15" t="s">
         <v>188</v>
       </c>
@@ -6413,7 +6408,7 @@
       <c r="J117" s="12"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="118" spans="1:11" ht="21.95" customHeight="1">
       <c r="A118" s="15" t="s">
         <v>189</v>
       </c>
@@ -6475,7 +6470,7 @@
       <c r="J119" s="12"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="120" spans="1:11" ht="21.95" customHeight="1">
       <c r="A120" s="15" t="s">
         <v>192</v>
       </c>
@@ -6508,7 +6503,7 @@
       <c r="J120" s="12"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="121" spans="1:11" ht="21.95" customHeight="1">
       <c r="A121" s="15" t="s">
         <v>193</v>
       </c>
@@ -6541,7 +6536,7 @@
       <c r="J121" s="12"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="122" spans="1:11" ht="21.95" customHeight="1">
       <c r="A122" s="15" t="s">
         <v>194</v>
       </c>
@@ -6603,7 +6598,7 @@
       <c r="J123" s="12"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="124" spans="1:11" ht="21.95" customHeight="1">
       <c r="A124" s="15" t="s">
         <v>196</v>
       </c>
@@ -6634,7 +6629,7 @@
       <c r="J124" s="12"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="125" spans="1:11" ht="21.95" customHeight="1">
       <c r="A125" s="15" t="s">
         <v>197</v>
       </c>
@@ -6725,7 +6720,7 @@
       <c r="J127" s="12"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="128" spans="1:11" ht="21.95" customHeight="1">
       <c r="A128" s="15" t="s">
         <v>200</v>
       </c>
@@ -6756,7 +6751,7 @@
       <c r="J128" s="12"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="129" spans="1:11" ht="21.95" customHeight="1">
       <c r="A129" s="15" t="s">
         <v>201</v>
       </c>
@@ -6789,7 +6784,7 @@
       <c r="J129" s="12"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="130" spans="1:11" ht="21.95" customHeight="1">
       <c r="A130" s="15" t="s">
         <v>202</v>
       </c>
@@ -6820,7 +6815,7 @@
       <c r="J130" s="12"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="131" spans="1:11" ht="21.95" customHeight="1">
       <c r="A131" s="15" t="s">
         <v>203</v>
       </c>
@@ -7000,7 +6995,7 @@
       <c r="J136" s="12"/>
       <c r="K136" s="30"/>
     </row>
-    <row r="137" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="137" spans="1:11" ht="21.95" customHeight="1">
       <c r="A137" s="15" t="s">
         <v>210</v>
       </c>
@@ -7033,7 +7028,7 @@
       <c r="J137" s="12"/>
       <c r="K137" s="30"/>
     </row>
-    <row r="138" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="138" spans="1:11" ht="21.95" customHeight="1">
       <c r="A138" s="15" t="s">
         <v>211</v>
       </c>
@@ -7097,7 +7092,7 @@
       <c r="J139" s="12"/>
       <c r="K139" s="30"/>
     </row>
-    <row r="140" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="140" spans="1:11" ht="21.95" customHeight="1">
       <c r="A140" s="15" t="s">
         <v>213</v>
       </c>
@@ -7130,7 +7125,7 @@
       <c r="J140" s="12"/>
       <c r="K140" s="30"/>
     </row>
-    <row r="141" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="141" spans="1:11" ht="21.95" customHeight="1">
       <c r="A141" s="15" t="s">
         <v>214</v>
       </c>
@@ -7163,7 +7158,7 @@
       <c r="J141" s="12"/>
       <c r="K141" s="30"/>
     </row>
-    <row r="142" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="142" spans="1:11" ht="21.95" customHeight="1">
       <c r="A142" s="15" t="s">
         <v>215</v>
       </c>
@@ -7196,7 +7191,7 @@
       <c r="J142" s="12"/>
       <c r="K142" s="30"/>
     </row>
-    <row r="143" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="143" spans="1:11" ht="21.95" customHeight="1">
       <c r="A143" s="15" t="s">
         <v>216</v>
       </c>
@@ -7229,7 +7224,7 @@
       <c r="J143" s="12"/>
       <c r="K143" s="30"/>
     </row>
-    <row r="144" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="144" spans="1:11" ht="21.95" customHeight="1">
       <c r="A144" s="15" t="s">
         <v>217</v>
       </c>
@@ -7262,7 +7257,7 @@
       <c r="J144" s="12"/>
       <c r="K144" s="30"/>
     </row>
-    <row r="145" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="145" spans="1:11" ht="21.95" customHeight="1">
       <c r="A145" s="15" t="s">
         <v>218</v>
       </c>
@@ -7293,7 +7288,7 @@
       <c r="J145" s="12"/>
       <c r="K145" s="30"/>
     </row>
-    <row r="146" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="146" spans="1:11" ht="21.95" customHeight="1">
       <c r="A146" s="15" t="s">
         <v>219</v>
       </c>
@@ -7326,7 +7321,7 @@
       <c r="J146" s="12"/>
       <c r="K146" s="30"/>
     </row>
-    <row r="147" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="147" spans="1:11" ht="21.95" customHeight="1">
       <c r="A147" s="15" t="s">
         <v>221</v>
       </c>
@@ -7357,7 +7352,7 @@
       <c r="J147" s="12"/>
       <c r="K147" s="30"/>
     </row>
-    <row r="148" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="148" spans="1:11" ht="21.95" customHeight="1">
       <c r="A148" s="15" t="s">
         <v>223</v>
       </c>
@@ -7390,7 +7385,7 @@
       <c r="J148" s="12"/>
       <c r="K148" s="30"/>
     </row>
-    <row r="149" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="149" spans="1:11" ht="21.95" customHeight="1">
       <c r="A149" s="15" t="s">
         <v>224</v>
       </c>
@@ -7454,7 +7449,7 @@
       <c r="J150" s="12"/>
       <c r="K150" s="30"/>
     </row>
-    <row r="151" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="151" spans="1:11" ht="21.95" customHeight="1">
       <c r="A151" s="15" t="s">
         <v>226</v>
       </c>
@@ -7485,7 +7480,7 @@
       <c r="J151" s="12"/>
       <c r="K151" s="30"/>
     </row>
-    <row r="152" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="152" spans="1:11" ht="21.95" customHeight="1">
       <c r="A152" s="15" t="s">
         <v>228</v>
       </c>
@@ -7516,7 +7511,7 @@
       <c r="J152" s="12"/>
       <c r="K152" s="30"/>
     </row>
-    <row r="153" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="153" spans="1:11" ht="21.95" customHeight="1">
       <c r="A153" s="15" t="s">
         <v>230</v>
       </c>
@@ -7609,7 +7604,7 @@
       <c r="J155" s="12"/>
       <c r="K155" s="30"/>
     </row>
-    <row r="156" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="156" spans="1:11" ht="21.95" customHeight="1">
       <c r="A156" s="15" t="s">
         <v>233</v>
       </c>
@@ -7640,7 +7635,7 @@
       <c r="J156" s="12"/>
       <c r="K156" s="30"/>
     </row>
-    <row r="157" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="157" spans="1:11" ht="21.95" customHeight="1">
       <c r="A157" s="15" t="s">
         <v>234</v>
       </c>
@@ -7764,7 +7759,7 @@
       <c r="J160" s="12"/>
       <c r="K160" s="30"/>
     </row>
-    <row r="161" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="161" spans="1:11" ht="21.95" customHeight="1">
       <c r="A161" s="15" t="s">
         <v>239</v>
       </c>
@@ -7797,7 +7792,7 @@
       <c r="J161" s="12"/>
       <c r="K161" s="30"/>
     </row>
-    <row r="162" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="162" spans="1:11" ht="21.95" customHeight="1">
       <c r="A162" s="15" t="s">
         <v>240</v>
       </c>
@@ -7861,7 +7856,7 @@
       <c r="J163" s="12"/>
       <c r="K163" s="30"/>
     </row>
-    <row r="164" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="164" spans="1:11" ht="21.95" customHeight="1">
       <c r="A164" s="15" t="s">
         <v>244</v>
       </c>
@@ -7925,7 +7920,7 @@
       <c r="J165" s="12"/>
       <c r="K165" s="30"/>
     </row>
-    <row r="166" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="166" spans="1:11" ht="21.95" customHeight="1">
       <c r="A166" s="15" t="s">
         <v>247</v>
       </c>
@@ -8016,7 +8011,7 @@
       <c r="J168" s="12"/>
       <c r="K168" s="30"/>
     </row>
-    <row r="169" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="169" spans="1:11" ht="21.95" customHeight="1">
       <c r="A169" s="15" t="s">
         <v>250</v>
       </c>
@@ -8107,7 +8102,7 @@
       <c r="J171" s="12"/>
       <c r="K171" s="30"/>
     </row>
-    <row r="172" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="172" spans="1:11" ht="21.95" customHeight="1">
       <c r="A172" s="15" t="s">
         <v>254</v>
       </c>
@@ -8140,7 +8135,7 @@
       <c r="J172" s="12"/>
       <c r="K172" s="30"/>
     </row>
-    <row r="173" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="173" spans="1:11" ht="21.95" customHeight="1">
       <c r="A173" s="15" t="s">
         <v>255</v>
       </c>
@@ -8231,7 +8226,7 @@
       <c r="J175" s="12"/>
       <c r="K175" s="30"/>
     </row>
-    <row r="176" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="176" spans="1:11" ht="21.95" customHeight="1">
       <c r="A176" s="15" t="s">
         <v>258</v>
       </c>
@@ -8264,7 +8259,7 @@
       <c r="J176" s="12"/>
       <c r="K176" s="30"/>
     </row>
-    <row r="177" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="177" spans="1:11" ht="21.95" customHeight="1">
       <c r="A177" s="15" t="s">
         <v>262</v>
       </c>
@@ -8297,7 +8292,7 @@
       <c r="J177" s="12"/>
       <c r="K177" s="30"/>
     </row>
-    <row r="178" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="178" spans="1:11" ht="21.95" customHeight="1">
       <c r="A178" s="15" t="s">
         <v>263</v>
       </c>
@@ -8358,7 +8353,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B179,İndirimler!$B$2:$B$110,C179)&gt;0,ROUND(G179*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B179,İndirimler!$B$2:$B$110,C179)),2),"")</f>
         <v>377.3</v>
       </c>
-      <c r="J179" s="32" t="s">
+      <c r="J179" s="31" t="s">
         <v>673</v>
       </c>
       <c r="K179" s="30"/>
@@ -8394,7 +8389,7 @@
       <c r="J180" s="12"/>
       <c r="K180" s="30"/>
     </row>
-    <row r="181" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="181" spans="1:11" ht="21.95" customHeight="1">
       <c r="A181" s="15" t="s">
         <v>266</v>
       </c>
@@ -8427,7 +8422,7 @@
       <c r="J181" s="12"/>
       <c r="K181" s="30"/>
     </row>
-    <row r="182" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="182" spans="1:11" ht="21.95" customHeight="1">
       <c r="A182" s="15" t="s">
         <v>268</v>
       </c>
@@ -8458,7 +8453,7 @@
       <c r="J182" s="12"/>
       <c r="K182" s="30"/>
     </row>
-    <row r="183" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="183" spans="1:11" ht="21.95" customHeight="1">
       <c r="A183" s="15" t="s">
         <v>269</v>
       </c>
@@ -8524,7 +8519,7 @@
       <c r="J184" s="12"/>
       <c r="K184" s="30"/>
     </row>
-    <row r="185" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="185" spans="1:11" ht="21.95" customHeight="1">
       <c r="A185" s="15" t="s">
         <v>272</v>
       </c>
@@ -8680,7 +8675,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B189,İndirimler!$B$2:$B$110,C189)&gt;0,ROUND(G189*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B189,İndirimler!$B$2:$B$110,C189)),2),"")</f>
         <v>335.3</v>
       </c>
-      <c r="J189" s="32" t="s">
+      <c r="J189" s="31" t="s">
         <v>684</v>
       </c>
       <c r="K189" s="30"/>
@@ -8716,7 +8711,7 @@
       <c r="J190" s="12"/>
       <c r="K190" s="30"/>
     </row>
-    <row r="191" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="191" spans="1:11" ht="21.95" customHeight="1">
       <c r="A191" s="15" t="s">
         <v>281</v>
       </c>
@@ -8782,7 +8777,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="193" spans="1:11" ht="21.95" customHeight="1">
       <c r="A193" s="15" t="s">
         <v>285</v>
       </c>
@@ -8846,7 +8841,7 @@
       <c r="J194" s="12"/>
       <c r="K194" s="30"/>
     </row>
-    <row r="195" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="195" spans="1:11" ht="21.95" customHeight="1">
       <c r="A195" s="15" t="s">
         <v>287</v>
       </c>
@@ -8879,7 +8874,7 @@
       <c r="J195" s="12"/>
       <c r="K195" s="30"/>
     </row>
-    <row r="196" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="196" spans="1:11" ht="21.95" customHeight="1">
       <c r="A196" s="15" t="s">
         <v>288</v>
       </c>
@@ -8943,7 +8938,7 @@
       <c r="J197" s="12"/>
       <c r="K197" s="30"/>
     </row>
-    <row r="198" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="198" spans="1:11" ht="21.95" customHeight="1">
       <c r="A198" s="15" t="s">
         <v>290</v>
       </c>
@@ -8978,7 +8973,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="199" spans="1:11" ht="21.95" customHeight="1">
       <c r="A199" s="15" t="s">
         <v>292</v>
       </c>
@@ -9039,7 +9034,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B200,İndirimler!$B$2:$B$110,C200)&gt;0,ROUND(G200*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B200,İndirimler!$B$2:$B$110,C200)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J200" s="32" t="s">
+      <c r="J200" s="31" t="s">
         <v>679</v>
       </c>
       <c r="K200" s="30"/>
@@ -9075,7 +9070,7 @@
       <c r="J201" s="12"/>
       <c r="K201" s="30"/>
     </row>
-    <row r="202" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="202" spans="1:11" ht="21.95" customHeight="1">
       <c r="A202" s="15" t="s">
         <v>295</v>
       </c>
@@ -9108,7 +9103,7 @@
       <c r="J202" s="12"/>
       <c r="K202" s="30"/>
     </row>
-    <row r="203" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="203" spans="1:11" ht="21.95" customHeight="1">
       <c r="A203" s="15" t="s">
         <v>296</v>
       </c>
@@ -9139,7 +9134,7 @@
       <c r="J203" s="12"/>
       <c r="K203" s="30"/>
     </row>
-    <row r="204" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="204" spans="1:11" ht="21.95" customHeight="1">
       <c r="A204" s="15" t="s">
         <v>297</v>
       </c>
@@ -9205,7 +9200,7 @@
       <c r="J205" s="12"/>
       <c r="K205" s="30"/>
     </row>
-    <row r="206" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="206" spans="1:11" ht="21.95" customHeight="1">
       <c r="A206" s="15" t="s">
         <v>300</v>
       </c>
@@ -9361,7 +9356,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B210,İndirimler!$B$2:$B$110,C210)&gt;0,ROUND(G210*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B210,İndirimler!$B$2:$B$110,C210)),2),"")</f>
         <v>363.3</v>
       </c>
-      <c r="J210" s="32" t="s">
+      <c r="J210" s="31" t="s">
         <v>691</v>
       </c>
       <c r="K210" s="30"/>
@@ -9428,7 +9423,7 @@
       <c r="J212" s="12"/>
       <c r="K212" s="30"/>
     </row>
-    <row r="213" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="213" spans="1:11" ht="21.95" customHeight="1">
       <c r="A213" s="15" t="s">
         <v>308</v>
       </c>
@@ -9494,7 +9489,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="215" spans="1:11" ht="21.95" customHeight="1">
       <c r="A215" s="15" t="s">
         <v>312</v>
       </c>
@@ -9558,7 +9553,7 @@
       <c r="J216" s="12"/>
       <c r="K216" s="30"/>
     </row>
-    <row r="217" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="217" spans="1:11" ht="21.95" customHeight="1">
       <c r="A217" s="15" t="s">
         <v>314</v>
       </c>
@@ -9591,7 +9586,7 @@
       <c r="J217" s="12"/>
       <c r="K217" s="30"/>
     </row>
-    <row r="218" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="218" spans="1:11" ht="21.95" customHeight="1">
       <c r="A218" s="15" t="s">
         <v>315</v>
       </c>
@@ -9655,7 +9650,7 @@
       <c r="J219" s="12"/>
       <c r="K219" s="30"/>
     </row>
-    <row r="220" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="220" spans="1:11" ht="21.95" customHeight="1">
       <c r="A220" s="15" t="s">
         <v>317</v>
       </c>
@@ -9715,7 +9710,7 @@
       <c r="J221" s="12"/>
       <c r="K221" s="30"/>
     </row>
-    <row r="222" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="222" spans="1:11" ht="21.95" customHeight="1">
       <c r="A222" s="15" t="s">
         <v>319</v>
       </c>
@@ -9748,7 +9743,7 @@
       <c r="J222" s="12"/>
       <c r="K222" s="30"/>
     </row>
-    <row r="223" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="223" spans="1:11" ht="21.95" customHeight="1">
       <c r="A223" s="15" t="s">
         <v>320</v>
       </c>
@@ -9779,7 +9774,7 @@
       <c r="J223" s="12"/>
       <c r="K223" s="30"/>
     </row>
-    <row r="224" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="224" spans="1:11" ht="21.95" customHeight="1">
       <c r="A224" s="15" t="s">
         <v>321</v>
       </c>
@@ -9841,7 +9836,7 @@
       <c r="J225" s="12"/>
       <c r="K225" s="30"/>
     </row>
-    <row r="226" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="226" spans="1:11" ht="21.95" customHeight="1">
       <c r="A226" s="15" t="s">
         <v>323</v>
       </c>
@@ -10052,7 +10047,7 @@
       <c r="J232" s="12"/>
       <c r="K232" s="30"/>
     </row>
-    <row r="233" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="233" spans="1:11" ht="21.95" customHeight="1">
       <c r="A233" s="15" t="s">
         <v>330</v>
       </c>
@@ -10114,7 +10109,7 @@
       <c r="J234" s="12"/>
       <c r="K234" s="30"/>
     </row>
-    <row r="235" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="235" spans="1:11" ht="21.95" customHeight="1">
       <c r="A235" s="15" t="s">
         <v>332</v>
       </c>
@@ -10205,7 +10200,7 @@
       <c r="J237" s="12"/>
       <c r="K237" s="30"/>
     </row>
-    <row r="238" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="238" spans="1:11" ht="21.95" customHeight="1">
       <c r="A238" s="15" t="s">
         <v>335</v>
       </c>
@@ -10238,7 +10233,7 @@
       <c r="J238" s="12"/>
       <c r="K238" s="30"/>
     </row>
-    <row r="239" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="239" spans="1:11" ht="21.95" customHeight="1">
       <c r="A239" s="15" t="s">
         <v>336</v>
       </c>
@@ -10271,7 +10266,7 @@
       <c r="J239" s="12"/>
       <c r="K239" s="30"/>
     </row>
-    <row r="240" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="240" spans="1:11" ht="21.95" customHeight="1">
       <c r="A240" s="15" t="s">
         <v>337</v>
       </c>
@@ -10304,7 +10299,7 @@
       <c r="J240" s="12"/>
       <c r="K240" s="30"/>
     </row>
-    <row r="241" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="241" spans="1:11" ht="21.95" customHeight="1">
       <c r="A241" s="15" t="s">
         <v>338</v>
       </c>
@@ -10337,7 +10332,7 @@
       <c r="J241" s="12"/>
       <c r="K241" s="30"/>
     </row>
-    <row r="242" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="242" spans="1:11" ht="21.95" customHeight="1">
       <c r="A242" s="15" t="s">
         <v>339</v>
       </c>
@@ -10370,7 +10365,7 @@
       <c r="J242" s="12"/>
       <c r="K242" s="30"/>
     </row>
-    <row r="243" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="243" spans="1:11" ht="21.95" customHeight="1">
       <c r="A243" s="15" t="s">
         <v>340</v>
       </c>
@@ -10616,7 +10611,7 @@
       <c r="J250" s="12"/>
       <c r="K250" s="30"/>
     </row>
-    <row r="251" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="251" spans="1:11" ht="21.95" customHeight="1">
       <c r="A251" s="15" t="s">
         <v>348</v>
       </c>
@@ -10738,7 +10733,7 @@
       <c r="J254" s="12"/>
       <c r="K254" s="30"/>
     </row>
-    <row r="255" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="255" spans="1:11" ht="21.95" customHeight="1">
       <c r="A255" s="15" t="s">
         <v>352</v>
       </c>
@@ -10771,7 +10766,7 @@
       <c r="J255" s="12"/>
       <c r="K255" s="30"/>
     </row>
-    <row r="256" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="256" spans="1:11" ht="21.95" customHeight="1">
       <c r="A256" s="15" t="s">
         <v>353</v>
       </c>
@@ -10832,7 +10827,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B257,İndirimler!$B$2:$B$110,C257)&gt;0,ROUND(G257*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B257,İndirimler!$B$2:$B$110,C257)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J257" s="32" t="s">
+      <c r="J257" s="31" t="s">
         <v>674</v>
       </c>
       <c r="K257" s="30"/>
@@ -10868,7 +10863,7 @@
       <c r="J258" s="12"/>
       <c r="K258" s="30"/>
     </row>
-    <row r="259" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="259" spans="1:11" ht="21.95" customHeight="1">
       <c r="A259" s="15" t="s">
         <v>359</v>
       </c>
@@ -10901,7 +10896,7 @@
       <c r="J259" s="12"/>
       <c r="K259" s="30"/>
     </row>
-    <row r="260" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="260" spans="1:11" ht="21.95" customHeight="1">
       <c r="A260" s="15" t="s">
         <v>360</v>
       </c>
@@ -10932,7 +10927,7 @@
       <c r="J260" s="12"/>
       <c r="K260" s="30"/>
     </row>
-    <row r="261" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="261" spans="1:11" ht="21.95" customHeight="1">
       <c r="A261" s="15" t="s">
         <v>361</v>
       </c>
@@ -10998,7 +10993,7 @@
       <c r="J262" s="12"/>
       <c r="K262" s="30"/>
     </row>
-    <row r="263" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="263" spans="1:11" ht="21.95" customHeight="1">
       <c r="A263" s="15" t="s">
         <v>364</v>
       </c>
@@ -11152,12 +11147,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B267,İndirimler!$B$2:$B$110,C267)&gt;0,ROUND(G267*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B267,İndirimler!$B$2:$B$110,C267)),2),"")</f>
         <v>335.3</v>
       </c>
-      <c r="J267" s="32" t="s">
+      <c r="J267" s="31" t="s">
         <v>685</v>
       </c>
       <c r="K267" s="30"/>
     </row>
-    <row r="268" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="268" spans="1:11" ht="21.95" customHeight="1">
       <c r="A268" s="15" t="s">
         <v>371</v>
       </c>
@@ -11192,7 +11187,7 @@
       </c>
       <c r="K268" s="30"/>
     </row>
-    <row r="269" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="269" spans="1:11" ht="21.95" customHeight="1">
       <c r="A269" s="15" t="s">
         <v>373</v>
       </c>
@@ -11256,7 +11251,7 @@
       <c r="J270" s="12"/>
       <c r="K270" s="30"/>
     </row>
-    <row r="271" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="271" spans="1:11" ht="21.95" customHeight="1">
       <c r="A271" s="15" t="s">
         <v>375</v>
       </c>
@@ -11320,7 +11315,7 @@
       <c r="J272" s="12"/>
       <c r="K272" s="30"/>
     </row>
-    <row r="273" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="273" spans="1:11" ht="21.95" customHeight="1">
       <c r="A273" s="15" t="s">
         <v>377</v>
       </c>
@@ -11384,7 +11379,7 @@
       <c r="J274" s="12"/>
       <c r="K274" s="30"/>
     </row>
-    <row r="275" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="275" spans="1:11" ht="21.95" customHeight="1">
       <c r="A275" s="15" t="s">
         <v>379</v>
       </c>
@@ -11445,7 +11440,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B276,İndirimler!$B$2:$B$110,C276)&gt;0,ROUND(G276*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B276,İndirimler!$B$2:$B$110,C276)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J276" s="32" t="s">
+      <c r="J276" s="31" t="s">
         <v>680</v>
       </c>
       <c r="K276" s="30"/>
@@ -11481,7 +11476,7 @@
       <c r="J277" s="12"/>
       <c r="K277" s="30"/>
     </row>
-    <row r="278" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="278" spans="1:11" ht="21.95" customHeight="1">
       <c r="A278" s="15" t="s">
         <v>382</v>
       </c>
@@ -11514,7 +11509,7 @@
       <c r="J278" s="12"/>
       <c r="K278" s="30"/>
     </row>
-    <row r="279" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="279" spans="1:11" ht="21.95" customHeight="1">
       <c r="A279" s="15" t="s">
         <v>383</v>
       </c>
@@ -11545,7 +11540,7 @@
       <c r="J279" s="12"/>
       <c r="K279" s="30"/>
     </row>
-    <row r="280" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="280" spans="1:11" ht="21.95" customHeight="1">
       <c r="A280" s="15" t="s">
         <v>384</v>
       </c>
@@ -11611,7 +11606,7 @@
       <c r="J281" s="12"/>
       <c r="K281" s="30"/>
     </row>
-    <row r="282" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="282" spans="1:11" ht="21.95" customHeight="1">
       <c r="A282" s="15" t="s">
         <v>387</v>
       </c>
@@ -11765,12 +11760,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B286,İndirimler!$B$2:$B$110,C286)&gt;0,ROUND(G286*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B286,İndirimler!$B$2:$B$110,C286)),2),"")</f>
         <v>363.3</v>
       </c>
-      <c r="J286" s="32" t="s">
+      <c r="J286" s="31" t="s">
         <v>692</v>
       </c>
       <c r="K286" s="30"/>
     </row>
-    <row r="287" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="287" spans="1:11" ht="21.95" customHeight="1">
       <c r="A287" s="15" t="s">
         <v>393</v>
       </c>
@@ -11805,7 +11800,7 @@
       </c>
       <c r="K287" s="30"/>
     </row>
-    <row r="288" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="288" spans="1:11" ht="21.95" customHeight="1">
       <c r="A288" s="15" t="s">
         <v>395</v>
       </c>
@@ -11869,7 +11864,7 @@
       <c r="J289" s="12"/>
       <c r="K289" s="30"/>
     </row>
-    <row r="290" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="290" spans="1:11" ht="21.95" customHeight="1">
       <c r="A290" s="15" t="s">
         <v>397</v>
       </c>
@@ -11933,7 +11928,7 @@
       <c r="J291" s="12"/>
       <c r="K291" s="30"/>
     </row>
-    <row r="292" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="292" spans="1:11" ht="21.95" customHeight="1">
       <c r="A292" s="15" t="s">
         <v>399</v>
       </c>
@@ -11997,7 +11992,7 @@
       <c r="J293" s="12"/>
       <c r="K293" s="30"/>
     </row>
-    <row r="294" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="294" spans="1:11" ht="21.95" customHeight="1">
       <c r="A294" s="15" t="s">
         <v>401</v>
       </c>
@@ -12057,7 +12052,7 @@
       <c r="J295" s="12"/>
       <c r="K295" s="30"/>
     </row>
-    <row r="296" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="296" spans="1:11" ht="21.95" customHeight="1">
       <c r="A296" s="15" t="s">
         <v>403</v>
       </c>
@@ -12090,7 +12085,7 @@
       <c r="J296" s="12"/>
       <c r="K296" s="30"/>
     </row>
-    <row r="297" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="297" spans="1:11" ht="21.95" customHeight="1">
       <c r="A297" s="15" t="s">
         <v>404</v>
       </c>
@@ -12121,7 +12116,7 @@
       <c r="J297" s="12"/>
       <c r="K297" s="30"/>
     </row>
-    <row r="298" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="298" spans="1:11" ht="21.95" customHeight="1">
       <c r="A298" s="15" t="s">
         <v>405</v>
       </c>
@@ -12183,7 +12178,7 @@
       <c r="J299" s="12"/>
       <c r="K299" s="30"/>
     </row>
-    <row r="300" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="300" spans="1:11" ht="21.95" customHeight="1">
       <c r="A300" s="15" t="s">
         <v>407</v>
       </c>
@@ -12333,12 +12328,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B304,İndirimler!$B$2:$B$110,C304)&gt;0,ROUND(G304*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B304,İndirimler!$B$2:$B$110,C304)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J304" s="32" t="s">
+      <c r="J304" s="31" t="s">
         <v>696</v>
       </c>
       <c r="K304" s="30"/>
     </row>
-    <row r="305" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="305" spans="1:11" ht="21.95" customHeight="1">
       <c r="A305" s="15" t="s">
         <v>412</v>
       </c>
@@ -12400,7 +12395,7 @@
       <c r="J306" s="12"/>
       <c r="K306" s="30"/>
     </row>
-    <row r="307" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="307" spans="1:11" ht="21.95" customHeight="1">
       <c r="A307" s="15" t="s">
         <v>414</v>
       </c>
@@ -12491,7 +12486,7 @@
       <c r="J309" s="12"/>
       <c r="K309" s="30"/>
     </row>
-    <row r="310" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="310" spans="1:11" ht="21.95" customHeight="1">
       <c r="A310" s="15" t="s">
         <v>417</v>
       </c>
@@ -12524,7 +12519,7 @@
       <c r="J310" s="12"/>
       <c r="K310" s="30"/>
     </row>
-    <row r="311" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="311" spans="1:11" ht="21.95" customHeight="1">
       <c r="A311" s="15" t="s">
         <v>418</v>
       </c>
@@ -12557,7 +12552,7 @@
       <c r="J311" s="12"/>
       <c r="K311" s="30"/>
     </row>
-    <row r="312" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="312" spans="1:11" ht="21.95" customHeight="1">
       <c r="A312" s="15" t="s">
         <v>419</v>
       </c>
@@ -12590,7 +12585,7 @@
       <c r="J312" s="12"/>
       <c r="K312" s="30"/>
     </row>
-    <row r="313" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="313" spans="1:11" ht="21.95" customHeight="1">
       <c r="A313" s="15" t="s">
         <v>420</v>
       </c>
@@ -12623,7 +12618,7 @@
       <c r="J313" s="12"/>
       <c r="K313" s="30"/>
     </row>
-    <row r="314" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="314" spans="1:11" ht="21.95" customHeight="1">
       <c r="A314" s="15" t="s">
         <v>421</v>
       </c>
@@ -12656,7 +12651,7 @@
       <c r="J314" s="12"/>
       <c r="K314" s="30"/>
     </row>
-    <row r="315" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="315" spans="1:11" ht="21.95" customHeight="1">
       <c r="A315" s="15" t="s">
         <v>422</v>
       </c>
@@ -12904,7 +12899,7 @@
       <c r="J322" s="12"/>
       <c r="K322" s="30"/>
     </row>
-    <row r="323" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="323" spans="1:11" ht="21.95" customHeight="1">
       <c r="A323" s="15" t="s">
         <v>430</v>
       </c>
@@ -12965,7 +12960,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B324,İndirimler!$B$2:$B$110,C324)&gt;0,ROUND(G324*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B324,İndirimler!$B$2:$B$110,C324)),2),"")</f>
         <v>384.3</v>
       </c>
-      <c r="J324" s="32" t="s">
+      <c r="J324" s="31" t="s">
         <v>675</v>
       </c>
       <c r="K324" s="30"/>
@@ -13001,7 +12996,7 @@
       <c r="J325" s="12"/>
       <c r="K325" s="30"/>
     </row>
-    <row r="326" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="326" spans="1:11" ht="21.95" customHeight="1">
       <c r="A326" s="15" t="s">
         <v>434</v>
       </c>
@@ -13032,7 +13027,7 @@
       <c r="J326" s="12"/>
       <c r="K326" s="30"/>
     </row>
-    <row r="327" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="327" spans="1:11" ht="21.95" customHeight="1">
       <c r="A327" s="15" t="s">
         <v>437</v>
       </c>
@@ -13067,7 +13062,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="328" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="328" spans="1:11" ht="21.95" customHeight="1">
       <c r="A328" s="15" t="s">
         <v>438</v>
       </c>
@@ -13133,7 +13128,7 @@
       <c r="J329" s="12"/>
       <c r="K329" s="30"/>
     </row>
-    <row r="330" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="330" spans="1:11" ht="21.95" customHeight="1">
       <c r="A330" s="15" t="s">
         <v>441</v>
       </c>
@@ -13258,7 +13253,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B333,İndirimler!$B$2:$B$110,C333)&gt;0,ROUND(G333*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B333,İndirimler!$B$2:$B$110,C333)),2),"")</f>
         <v>251.3</v>
       </c>
-      <c r="J333" s="32" t="s">
+      <c r="J333" s="31" t="s">
         <v>687</v>
       </c>
       <c r="K333" s="30"/>
@@ -13296,7 +13291,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="335" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="335" spans="1:11" ht="21.95" customHeight="1">
       <c r="A335" s="15" t="s">
         <v>449</v>
       </c>
@@ -13331,7 +13326,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="336" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="336" spans="1:11" ht="21.95" customHeight="1">
       <c r="A336" s="15" t="s">
         <v>450</v>
       </c>
@@ -13366,7 +13361,7 @@
       </c>
       <c r="K336" s="30"/>
     </row>
-    <row r="337" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="337" spans="1:11" ht="21.95" customHeight="1">
       <c r="A337" s="15" t="s">
         <v>452</v>
       </c>
@@ -13430,7 +13425,7 @@
       <c r="J338" s="12"/>
       <c r="K338" s="30"/>
     </row>
-    <row r="339" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="339" spans="1:11" ht="21.95" customHeight="1">
       <c r="A339" s="15" t="s">
         <v>454</v>
       </c>
@@ -13494,7 +13489,7 @@
       <c r="J340" s="12"/>
       <c r="K340" s="30"/>
     </row>
-    <row r="341" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="341" spans="1:11" ht="21.95" customHeight="1">
       <c r="A341" s="15" t="s">
         <v>457</v>
       </c>
@@ -13586,7 +13581,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B343,İndirimler!$B$2:$B$110,C343)&gt;0,ROUND(G343*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B343,İndirimler!$B$2:$B$110,C343)),2),"")</f>
         <v>440.3</v>
       </c>
-      <c r="J343" s="32" t="s">
+      <c r="J343" s="31" t="s">
         <v>681</v>
       </c>
       <c r="K343" s="30"/>
@@ -13622,7 +13617,7 @@
       <c r="J344" s="12"/>
       <c r="K344" s="30"/>
     </row>
-    <row r="345" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="345" spans="1:11" ht="21.95" customHeight="1">
       <c r="A345" s="15" t="s">
         <v>461</v>
       </c>
@@ -13653,7 +13648,7 @@
       <c r="J345" s="12"/>
       <c r="K345" s="30"/>
     </row>
-    <row r="346" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="346" spans="1:11" ht="21.95" customHeight="1">
       <c r="A346" s="15" t="s">
         <v>463</v>
       </c>
@@ -13688,7 +13683,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="347" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="347" spans="1:11" ht="21.95" customHeight="1">
       <c r="A347" s="15" t="s">
         <v>464</v>
       </c>
@@ -13754,7 +13749,7 @@
       <c r="J348" s="12"/>
       <c r="K348" s="30"/>
     </row>
-    <row r="349" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="349" spans="1:11" ht="21.95" customHeight="1">
       <c r="A349" s="15" t="s">
         <v>467</v>
       </c>
@@ -13879,7 +13874,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B352,İndirimler!$B$2:$B$110,C352)&gt;0,ROUND(G352*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B352,İndirimler!$B$2:$B$110,C352)),2),"")</f>
         <v>251.3</v>
       </c>
-      <c r="J352" s="32" t="s">
+      <c r="J352" s="31" t="s">
         <v>693</v>
       </c>
       <c r="K352" s="30"/>
@@ -13917,7 +13912,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="354" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="354" spans="1:11" ht="21.95" customHeight="1">
       <c r="A354" s="15" t="s">
         <v>474</v>
       </c>
@@ -13952,7 +13947,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="355" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="355" spans="1:11" ht="21.95" customHeight="1">
       <c r="A355" s="15" t="s">
         <v>476</v>
       </c>
@@ -13987,7 +13982,7 @@
       </c>
       <c r="K355" s="30"/>
     </row>
-    <row r="356" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="356" spans="1:11" ht="21.95" customHeight="1">
       <c r="A356" s="15" t="s">
         <v>478</v>
       </c>
@@ -14051,7 +14046,7 @@
       <c r="J357" s="12"/>
       <c r="K357" s="30"/>
     </row>
-    <row r="358" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="358" spans="1:11" ht="21.95" customHeight="1">
       <c r="A358" s="15" t="s">
         <v>480</v>
       </c>
@@ -14115,7 +14110,7 @@
       <c r="J359" s="12"/>
       <c r="K359" s="30"/>
     </row>
-    <row r="360" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="360" spans="1:11" ht="21.95" customHeight="1">
       <c r="A360" s="15" t="s">
         <v>482</v>
       </c>
@@ -14208,7 +14203,7 @@
       <c r="J362" s="12"/>
       <c r="K362" s="30"/>
     </row>
-    <row r="363" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="363" spans="1:11" ht="21.95" customHeight="1">
       <c r="A363" s="15" t="s">
         <v>485</v>
       </c>
@@ -14239,7 +14234,7 @@
       <c r="J363" s="12"/>
       <c r="K363" s="30"/>
     </row>
-    <row r="364" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="364" spans="1:11" ht="21.95" customHeight="1">
       <c r="A364" s="15" t="s">
         <v>486</v>
       </c>
@@ -14301,7 +14296,7 @@
       <c r="J365" s="12"/>
       <c r="K365" s="30"/>
     </row>
-    <row r="366" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="366" spans="1:11" ht="21.95" customHeight="1">
       <c r="A366" s="15" t="s">
         <v>488</v>
       </c>
@@ -14456,7 +14451,7 @@
       <c r="J370" s="12"/>
       <c r="K370" s="30"/>
     </row>
-    <row r="371" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="371" spans="1:11" ht="21.95" customHeight="1">
       <c r="A371" s="15" t="s">
         <v>493</v>
       </c>
@@ -14518,7 +14513,7 @@
       <c r="J372" s="12"/>
       <c r="K372" s="30"/>
     </row>
-    <row r="373" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="373" spans="1:11" ht="21.95" customHeight="1">
       <c r="A373" s="15" t="s">
         <v>495</v>
       </c>
@@ -14638,7 +14633,7 @@
       <c r="J376" s="12"/>
       <c r="K376" s="30"/>
     </row>
-    <row r="377" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="377" spans="1:11" ht="21.95" customHeight="1">
       <c r="A377" s="15" t="s">
         <v>499</v>
       </c>
@@ -14671,7 +14666,7 @@
       <c r="J377" s="12"/>
       <c r="K377" s="30"/>
     </row>
-    <row r="378" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="378" spans="1:11" ht="21.95" customHeight="1">
       <c r="A378" s="15" t="s">
         <v>500</v>
       </c>
@@ -14704,7 +14699,7 @@
       <c r="J378" s="12"/>
       <c r="K378" s="30"/>
     </row>
-    <row r="379" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="379" spans="1:11" ht="21.95" customHeight="1">
       <c r="A379" s="15" t="s">
         <v>501</v>
       </c>
@@ -14923,7 +14918,7 @@
       <c r="J385" s="12"/>
       <c r="K385" s="30"/>
     </row>
-    <row r="386" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="386" spans="1:11" ht="21.95" customHeight="1">
       <c r="A386" s="15" t="s">
         <v>508</v>
       </c>
@@ -14984,7 +14979,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B387,İndirimler!$B$2:$B$110,C387)&gt;0,ROUND(G387*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B387,İndirimler!$B$2:$B$110,C387)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J387" s="32" t="s">
+      <c r="J387" s="31" t="s">
         <v>670</v>
       </c>
       <c r="K387" s="30"/>
@@ -15020,7 +15015,7 @@
       <c r="J388" s="12"/>
       <c r="K388" s="30"/>
     </row>
-    <row r="389" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="389" spans="1:11" ht="21.95" customHeight="1">
       <c r="A389" s="15" t="s">
         <v>512</v>
       </c>
@@ -15178,12 +15173,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B393,İndirimler!$B$2:$B$110,C393)&gt;0,ROUND(G393*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B393,İndirimler!$B$2:$B$110,C393)),2),"")</f>
         <v>251.3</v>
       </c>
-      <c r="J393" s="32" t="s">
+      <c r="J393" s="31" t="s">
         <v>686</v>
       </c>
       <c r="K393" s="30"/>
     </row>
-    <row r="394" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="394" spans="1:11" ht="21.95" customHeight="1">
       <c r="A394" s="15" t="s">
         <v>520</v>
       </c>
@@ -15218,7 +15213,7 @@
       </c>
       <c r="K394" s="30"/>
     </row>
-    <row r="395" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="395" spans="1:11" ht="21.95" customHeight="1">
       <c r="A395" s="15" t="s">
         <v>522</v>
       </c>
@@ -15282,7 +15277,7 @@
       <c r="J396" s="12"/>
       <c r="K396" s="30"/>
     </row>
-    <row r="397" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="397" spans="1:11" ht="21.95" customHeight="1">
       <c r="A397" s="15" t="s">
         <v>524</v>
       </c>
@@ -15315,7 +15310,7 @@
       <c r="J397" s="12"/>
       <c r="K397" s="30"/>
     </row>
-    <row r="398" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="398" spans="1:11" ht="21.95" customHeight="1">
       <c r="A398" s="15" t="s">
         <v>525</v>
       </c>
@@ -15410,7 +15405,7 @@
       <c r="J400" s="12"/>
       <c r="K400" s="30"/>
     </row>
-    <row r="401" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="401" spans="1:11" ht="21.95" customHeight="1">
       <c r="A401" s="15" t="s">
         <v>528</v>
       </c>
@@ -15568,12 +15563,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B405,İndirimler!$B$2:$B$110,C405)&gt;0,ROUND(G405*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B405,İndirimler!$B$2:$B$110,C405)),2),"")</f>
         <v>269.5</v>
       </c>
-      <c r="J405" s="32" t="s">
+      <c r="J405" s="31" t="s">
         <v>694</v>
       </c>
       <c r="K405" s="30"/>
     </row>
-    <row r="406" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="406" spans="1:11" ht="21.95" customHeight="1">
       <c r="A406" s="15" t="s">
         <v>535</v>
       </c>
@@ -15608,7 +15603,7 @@
       </c>
       <c r="K406" s="30"/>
     </row>
-    <row r="407" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="407" spans="1:11" ht="21.95" customHeight="1">
       <c r="A407" s="15" t="s">
         <v>537</v>
       </c>
@@ -15672,7 +15667,7 @@
       <c r="J408" s="12"/>
       <c r="K408" s="30"/>
     </row>
-    <row r="409" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="409" spans="1:11" ht="21.95" customHeight="1">
       <c r="A409" s="15" t="s">
         <v>539</v>
       </c>
@@ -15705,7 +15700,7 @@
       <c r="J409" s="12"/>
       <c r="K409" s="30"/>
     </row>
-    <row r="410" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="410" spans="1:11" ht="21.95" customHeight="1">
       <c r="A410" s="15" t="s">
         <v>540</v>
       </c>
@@ -15798,7 +15793,7 @@
       <c r="J412" s="12"/>
       <c r="K412" s="30"/>
     </row>
-    <row r="413" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="413" spans="1:11" ht="21.95" customHeight="1">
       <c r="A413" s="15" t="s">
         <v>543</v>
       </c>
@@ -15949,7 +15944,7 @@
       <c r="J417" s="12"/>
       <c r="K417" s="30"/>
     </row>
-    <row r="418" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="418" spans="1:11" ht="21.95" customHeight="1">
       <c r="A418" s="15" t="s">
         <v>548</v>
       </c>
@@ -16011,7 +16006,7 @@
       <c r="J419" s="12"/>
       <c r="K419" s="30"/>
     </row>
-    <row r="420" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="420" spans="1:11" ht="21.95" customHeight="1">
       <c r="A420" s="15" t="s">
         <v>550</v>
       </c>
@@ -16190,7 +16185,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B425,İndirimler!$B$2:$B$110,C425)&gt;0,ROUND(G425*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B425,İndirimler!$B$2:$B$110,C425)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J425" s="32" t="s">
+      <c r="J425" s="31" t="s">
         <v>671</v>
       </c>
       <c r="K425" s="30"/>
@@ -16255,7 +16250,7 @@
       <c r="J427" s="12"/>
       <c r="K427" s="30"/>
     </row>
-    <row r="428" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="428" spans="1:11" ht="21.95" customHeight="1">
       <c r="A428" s="15" t="s">
         <v>560</v>
       </c>
@@ -16382,7 +16377,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B431,İndirimler!$B$2:$B$110,C431)&gt;0,ROUND(G431*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B431,İndirimler!$B$2:$B$110,C431)),2),"")</f>
         <v>241.5</v>
       </c>
-      <c r="J431" s="32" t="s">
+      <c r="J431" s="31" t="s">
         <v>688</v>
       </c>
       <c r="K431" s="30"/>
@@ -16418,7 +16413,7 @@
       <c r="J432" s="12"/>
       <c r="K432" s="30"/>
     </row>
-    <row r="433" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="433" spans="1:11" ht="21.95" customHeight="1">
       <c r="A433" s="15" t="s">
         <v>567</v>
       </c>
@@ -16453,7 +16448,7 @@
       </c>
       <c r="K433" s="30"/>
     </row>
-    <row r="434" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="434" spans="1:11" ht="21.95" customHeight="1">
       <c r="A434" s="15" t="s">
         <v>569</v>
       </c>
@@ -16517,7 +16512,7 @@
       <c r="J435" s="12"/>
       <c r="K435" s="30"/>
     </row>
-    <row r="436" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="436" spans="1:11" ht="21.95" customHeight="1">
       <c r="A436" s="15" t="s">
         <v>571</v>
       </c>
@@ -16550,7 +16545,7 @@
       <c r="J436" s="12"/>
       <c r="K436" s="30"/>
     </row>
-    <row r="437" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="437" spans="1:11" ht="21.95" customHeight="1">
       <c r="A437" s="15" t="s">
         <v>572</v>
       </c>
@@ -16642,7 +16637,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B439,İndirimler!$B$2:$B$110,C439)&gt;0,ROUND(G439*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B439,İndirimler!$B$2:$B$110,C439)),2),"")</f>
         <v>290.5</v>
       </c>
-      <c r="J439" s="32" t="s">
+      <c r="J439" s="31" t="s">
         <v>677</v>
       </c>
       <c r="K439" s="30"/>
@@ -16707,7 +16702,7 @@
       <c r="J441" s="12"/>
       <c r="K441" s="30"/>
     </row>
-    <row r="442" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="442" spans="1:11" ht="21.95" customHeight="1">
       <c r="A442" s="15" t="s">
         <v>577</v>
       </c>
@@ -16868,7 +16863,7 @@
       <c r="J446" s="12"/>
       <c r="K446" s="30"/>
     </row>
-    <row r="447" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="447" spans="1:11" ht="21.95" customHeight="1">
       <c r="A447" s="15" t="s">
         <v>584</v>
       </c>
@@ -16903,7 +16898,7 @@
       </c>
       <c r="K447" s="30"/>
     </row>
-    <row r="448" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="448" spans="1:11" ht="21.95" customHeight="1">
       <c r="A448" s="15" t="s">
         <v>586</v>
       </c>
@@ -16967,7 +16962,7 @@
       <c r="J449" s="12"/>
       <c r="K449" s="30"/>
     </row>
-    <row r="450" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="450" spans="1:11" ht="21.95" customHeight="1">
       <c r="A450" s="15" t="s">
         <v>588</v>
       </c>
@@ -17000,7 +16995,7 @@
       <c r="J450" s="12"/>
       <c r="K450" s="30"/>
     </row>
-    <row r="451" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="451" spans="1:11" ht="21.95" customHeight="1">
       <c r="A451" s="15" t="s">
         <v>589</v>
       </c>
@@ -17122,7 +17117,7 @@
       <c r="J454" s="12"/>
       <c r="K454" s="30"/>
     </row>
-    <row r="455" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="455" spans="1:11" ht="21.95" customHeight="1">
       <c r="A455" s="15" t="s">
         <v>593</v>
       </c>
@@ -17241,7 +17236,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B458,İndirimler!$B$2:$B$110,C458)&gt;0,ROUND(G458*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B458,İndirimler!$B$2:$B$110,C458)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J458" s="32" t="s">
+      <c r="J458" s="31" t="s">
         <v>697</v>
       </c>
       <c r="K458" s="30"/>
@@ -17275,7 +17270,7 @@
       <c r="J459" s="12"/>
       <c r="K459" s="30"/>
     </row>
-    <row r="460" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="460" spans="1:11" ht="21.95" customHeight="1">
       <c r="A460" s="15" t="s">
         <v>598</v>
       </c>
@@ -17337,7 +17332,7 @@
       <c r="J461" s="12"/>
       <c r="K461" s="30"/>
     </row>
-    <row r="462" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="462" spans="1:11" ht="21.95" customHeight="1">
       <c r="A462" s="15" t="s">
         <v>600</v>
       </c>
@@ -17521,7 +17516,7 @@
       <c r="J467" s="12"/>
       <c r="K467" s="30"/>
     </row>
-    <row r="468" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="468" spans="1:11" ht="21.95" customHeight="1">
       <c r="A468" s="15" t="s">
         <v>606</v>
       </c>
@@ -17617,12 +17612,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B470,İndirimler!$B$2:$B$110,C470)&gt;0,ROUND(G470*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B470,İndirimler!$B$2:$B$110,C470)),2),"")</f>
         <v>188.3</v>
       </c>
-      <c r="J470" s="32" t="s">
+      <c r="J470" s="31" t="s">
         <v>695</v>
       </c>
       <c r="K470" s="30"/>
     </row>
-    <row r="471" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="471" spans="1:11" ht="21.95" customHeight="1">
       <c r="A471" s="15" t="s">
         <v>612</v>
       </c>
@@ -17657,7 +17652,7 @@
       </c>
       <c r="K471" s="30"/>
     </row>
-    <row r="472" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="472" spans="1:11" ht="21.95" customHeight="1">
       <c r="A472" s="15" t="s">
         <v>614</v>
       </c>
@@ -17690,7 +17685,7 @@
       <c r="J472" s="12"/>
       <c r="K472" s="30"/>
     </row>
-    <row r="473" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="473" spans="1:11" ht="21.95" customHeight="1">
       <c r="A473" s="15" t="s">
         <v>615</v>
       </c>
@@ -17723,7 +17718,7 @@
       <c r="J473" s="12"/>
       <c r="K473" s="30"/>
     </row>
-    <row r="474" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="474" spans="1:11" ht="21.95" customHeight="1">
       <c r="A474" s="15" t="s">
         <v>616</v>
       </c>
@@ -17845,7 +17840,7 @@
       <c r="J477" s="12"/>
       <c r="K477" s="30"/>
     </row>
-    <row r="478" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="478" spans="1:11" ht="21.95" customHeight="1">
       <c r="A478" s="15" t="s">
         <v>620</v>
       </c>
@@ -18114,7 +18109,7 @@
       <c r="J486" s="12"/>
       <c r="K486" s="30"/>
     </row>
-    <row r="487" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="487" spans="1:11" ht="21.95" customHeight="1">
       <c r="A487" s="15" t="s">
         <v>633</v>
       </c>
@@ -18147,7 +18142,7 @@
       <c r="J487" s="12"/>
       <c r="K487" s="30"/>
     </row>
-    <row r="488" spans="1:11" ht="21.95" hidden="1" customHeight="1">
+    <row r="488" spans="1:11" ht="21.95" customHeight="1">
       <c r="A488" s="16" t="s">
         <v>635</v>
       </c>
@@ -19848,14 +19843,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="42" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>647</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="3" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A3" s="26" t="s">

--- a/output/Fiyat-Listesi-Yonetim.xlsx
+++ b/output/Fiyat-Listesi-Yonetim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALS\Documents\26-27 Fiyat Listeleri\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA907828-5C1E-40B6-BEAE-17F90CC61F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FEE42A-E80D-4B17-9C5B-4A72B7DD618D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3008" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3079" uniqueCount="774">
   <si>
     <t>Barkod</t>
   </si>
@@ -2128,6 +2128,234 @@
   </si>
   <si>
     <t>https://online.fliphtml5.com/udqwy/yntn/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/lxrj/#p=1</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/yois/#p=1</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/jhtg/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/etlo/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/wcqa/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/llma/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/lspl/#p=1</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/cewx/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/puqp/</t>
+  </si>
+  <si>
+    <t>Konu Anlatımlı 1</t>
+  </si>
+  <si>
+    <t>Konu Anlatımlı 2</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/btbf/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/uoyw/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/ywyp/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/ebfi/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/mgkp/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/jwjt/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/hqex/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/nzux/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/emrs/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/xubu/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/xgsh/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/vmkd/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/muup/#p=1</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/hicw/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/xurw/#p=1</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/ufuz/#p=1</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/erke/#p=1</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/ktlu/#p=1</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/rjsu/#p=1</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/cyqo/#p=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://online.fliphtml5.com/wrbmv/vxmu/#p=1</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/wrbmv/ibrt/#p=1</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/kaoj/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/qanl/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/mdzj/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/sonr/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/mqkz/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/abfr/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/qkuq/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/ijlj/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/kima/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/pobr/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/hdvv/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/kilo/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/odoj/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/fdhk/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/ykpf/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/behf/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/vrgv/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/kgkl/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/lmsz/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/sdlj/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/oanf/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/xhqw/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/povz/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/vjuv/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/szhp/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/bspn/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/nyli/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/oumc/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/cotrr/vydq/</t>
+  </si>
+  <si>
+    <t>https://biyotik.com.tr/view/img/pdf/9_bikaf_demo.pdf</t>
+  </si>
+  <si>
+    <t>https://biyotik.com.tr/view/img/pdf/9.pdf</t>
+  </si>
+  <si>
+    <t>https://biyotik.com.tr/view/img/pdf/9_btt_demo.pdf</t>
+  </si>
+  <si>
+    <t>https://biyotik.com.tr/view/img/kitap/2026-10.sinif-konu-anlatim-foyleri-demo.pdf</t>
+  </si>
+  <si>
+    <t>https://biyotik.com.tr/view/img/kitap/2026_yeni_mufredat_10_sinif_soru_bankasi_DEMO_yeni.pdf</t>
+  </si>
+  <si>
+    <t>https://biyotik.com.tr/view/img/pdf/10_btt_demo.pdf</t>
+  </si>
+  <si>
+    <t>https://biyotik.com.tr/view/img/pdf/11.pdf</t>
+  </si>
+  <si>
+    <t>https://capyayinlari.com/Kitap/9._Sinif_Kimya_Seti/B2E5693C613F48C7B83C7DEF86D4147D</t>
+  </si>
+  <si>
+    <t>https://capyayinlari.com/Kitap/9._Sinif_Biyoloji_Seti/FFC79E08ED0B4A30A4A4523AD4D359A8</t>
+  </si>
+  <si>
+    <t>https://capyayinlari.com/Kitap/9._Sinif_Tarih_Seti/B01E33FFEF7E4440B6F781C9A950305F</t>
+  </si>
+  <si>
+    <t>https://capyayinlari.com/Kitap/9._Sinif_Co%C4%9Frafya_Seti/51AAAD61DD8349F2BA61C6ED823808B8</t>
+  </si>
+  <si>
+    <t>https://capyayinlari.com/Kitap/9_TDE_Soru_Bankasi/AE0784D7574C4AC8A3127A26DC0A6898</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/mibj/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/xxtv/</t>
   </si>
 </sst>
 </file>
@@ -2960,7 +3188,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B10,İndirimler!$B$2:$B$110,C10)&gt;0,ROUND(G10*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B10,İndirimler!$B$2:$B$110,C10)),2),"")</f>
         <v>395.5</v>
       </c>
-      <c r="J10" s="12"/>
+      <c r="J10" s="31" t="s">
+        <v>772</v>
+      </c>
       <c r="K10" s="30"/>
     </row>
     <row r="11" spans="1:11" ht="21.95" customHeight="1">
@@ -3057,7 +3287,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B13,İndirimler!$B$2:$B$110,C13)&gt;0,ROUND(G13*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B13,İndirimler!$B$2:$B$110,C13)),2),"")</f>
         <v>468.3</v>
       </c>
-      <c r="J13" s="12"/>
+      <c r="J13" s="12" t="s">
+        <v>731</v>
+      </c>
       <c r="K13" s="30"/>
     </row>
     <row r="14" spans="1:11" ht="21.95" customHeight="1">
@@ -3286,7 +3518,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B20,İndirimler!$B$2:$B$110,C20)&gt;0,ROUND(G20*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B20,İndirimler!$B$2:$B$110,C20)),2),"")</f>
         <v>438.2</v>
       </c>
-      <c r="J20" s="12"/>
+      <c r="J20" s="31" t="s">
+        <v>705</v>
+      </c>
       <c r="K20" s="30"/>
     </row>
     <row r="21" spans="1:11" ht="21.95" customHeight="1">
@@ -3352,7 +3586,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B22,İndirimler!$B$2:$B$110,C22)&gt;0,ROUND(G22*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B22,İndirimler!$B$2:$B$110,C22)),2),"")</f>
         <v>363.3</v>
       </c>
-      <c r="J22" s="12"/>
+      <c r="J22" s="31" t="s">
+        <v>771</v>
+      </c>
       <c r="K22" s="30"/>
     </row>
     <row r="23" spans="1:11" ht="21.95" customHeight="1">
@@ -3575,7 +3811,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B29,İndirimler!$B$2:$B$110,C29)&gt;0,ROUND(G29*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B29,İndirimler!$B$2:$B$110,C29)),2),"")</f>
         <v>478.8</v>
       </c>
-      <c r="J29" s="12"/>
+      <c r="J29" s="12" t="s">
+        <v>732</v>
+      </c>
       <c r="K29" s="30"/>
     </row>
     <row r="30" spans="1:11" ht="21.95" customHeight="1">
@@ -3773,7 +4011,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B35,İndirimler!$B$2:$B$110,C35)&gt;0,ROUND(G35*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B35,İndirimler!$B$2:$B$110,C35)),2),"")</f>
         <v>435.4</v>
       </c>
-      <c r="J35" s="12"/>
+      <c r="J35" s="12" t="s">
+        <v>733</v>
+      </c>
       <c r="K35" s="30"/>
     </row>
     <row r="36" spans="1:11" ht="21.95" customHeight="1">
@@ -4023,7 +4263,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B43,İndirimler!$B$2:$B$110,C43)&gt;0,ROUND(G43*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B43,İndirimler!$B$2:$B$110,C43)),2),"")</f>
         <v>382.2</v>
       </c>
-      <c r="J43" s="12"/>
+      <c r="J43" s="12" t="s">
+        <v>745</v>
+      </c>
       <c r="K43" s="30"/>
     </row>
     <row r="44" spans="1:11" ht="21.95" customHeight="1">
@@ -4178,7 +4420,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B48,İndirimler!$B$2:$B$110,C48)&gt;0,ROUND(G48*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B48,İndirimler!$B$2:$B$110,C48)),2),"")</f>
         <v>343</v>
       </c>
-      <c r="J48" s="12"/>
+      <c r="J48" s="12" t="s">
+        <v>746</v>
+      </c>
       <c r="K48" s="30"/>
     </row>
     <row r="49" spans="1:11" ht="21.95" customHeight="1">
@@ -4591,7 +4835,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B61,İndirimler!$B$2:$B$110,C61)&gt;0,ROUND(G61*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B61,İndirimler!$B$2:$B$110,C61)),2),"")</f>
         <v>629.29999999999995</v>
       </c>
-      <c r="J61" s="12"/>
+      <c r="J61" s="31" t="s">
+        <v>773</v>
+      </c>
       <c r="K61" s="30"/>
     </row>
     <row r="62" spans="1:11" ht="21.95" customHeight="1">
@@ -4624,7 +4870,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B62,İndirimler!$B$2:$B$110,C62)&gt;0,ROUND(G62*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B62,İndirimler!$B$2:$B$110,C62)),2),"")</f>
         <v>450.8</v>
       </c>
-      <c r="J62" s="12"/>
+      <c r="J62" s="31" t="s">
+        <v>698</v>
+      </c>
       <c r="K62" s="30"/>
     </row>
     <row r="63" spans="1:11" ht="21.95" customHeight="1">
@@ -4675,11 +4923,9 @@
       <c r="D64" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E64" s="12" t="s">
-        <v>61</v>
-      </c>
+      <c r="E64" s="12"/>
       <c r="F64" s="12" t="s">
-        <v>38</v>
+        <v>707</v>
       </c>
       <c r="G64" s="18">
         <v>576</v>
@@ -4692,7 +4938,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B64,İndirimler!$B$2:$B$110,C64)&gt;0,ROUND(G64*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B64,İndirimler!$B$2:$B$110,C64)),2),"")</f>
         <v>403.2</v>
       </c>
-      <c r="J64" s="12"/>
+      <c r="J64" s="31" t="s">
+        <v>706</v>
+      </c>
       <c r="K64" s="30"/>
     </row>
     <row r="65" spans="1:11" ht="21.95" customHeight="1">
@@ -4708,11 +4956,9 @@
       <c r="D65" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E65" s="12" t="s">
-        <v>61</v>
-      </c>
+      <c r="E65" s="12"/>
       <c r="F65" s="12" t="s">
-        <v>38</v>
+        <v>708</v>
       </c>
       <c r="G65" s="18">
         <v>576</v>
@@ -4725,7 +4971,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B65,İndirimler!$B$2:$B$110,C65)&gt;0,ROUND(G65*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B65,İndirimler!$B$2:$B$110,C65)),2),"")</f>
         <v>403.2</v>
       </c>
-      <c r="J65" s="12"/>
+      <c r="J65" s="12" t="s">
+        <v>709</v>
+      </c>
       <c r="K65" s="30"/>
     </row>
     <row r="66" spans="1:11" ht="21.95" customHeight="1">
@@ -4873,9 +5121,7 @@
       <c r="D70" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E70" s="12" t="s">
-        <v>61</v>
-      </c>
+      <c r="E70" s="12"/>
       <c r="F70" s="12" t="s">
         <v>15</v>
       </c>
@@ -4890,7 +5136,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B70,İndirimler!$B$2:$B$110,C70)&gt;0,ROUND(G70*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B70,İndirimler!$B$2:$B$110,C70)),2),"")</f>
         <v>425.6</v>
       </c>
-      <c r="J70" s="12"/>
+      <c r="J70" s="31" t="s">
+        <v>699</v>
+      </c>
       <c r="K70" s="30"/>
     </row>
     <row r="71" spans="1:11" ht="21.95" customHeight="1">
@@ -5073,9 +5321,7 @@
       <c r="D76" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E76" s="12" t="s">
-        <v>61</v>
-      </c>
+      <c r="E76" s="12"/>
       <c r="F76" s="12" t="s">
         <v>15</v>
       </c>
@@ -5090,7 +5336,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B76,İndirimler!$B$2:$B$110,C76)&gt;0,ROUND(G76*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B76,İndirimler!$B$2:$B$110,C76)),2),"")</f>
         <v>473.2</v>
       </c>
-      <c r="J76" s="12"/>
+      <c r="J76" s="31" t="s">
+        <v>710</v>
+      </c>
       <c r="K76" s="30"/>
     </row>
     <row r="77" spans="1:11" ht="21.95" customHeight="1">
@@ -5538,7 +5786,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B90,İndirimler!$B$2:$B$110,C90)&gt;0,ROUND(G90*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B90,İndirimler!$B$2:$B$110,C90)),2),"")</f>
         <v>414.4</v>
       </c>
-      <c r="J90" s="12"/>
+      <c r="J90" s="12" t="s">
+        <v>721</v>
+      </c>
       <c r="K90" s="30"/>
     </row>
     <row r="91" spans="1:11" ht="21.95" customHeight="1">
@@ -5606,7 +5856,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B92,İndirimler!$B$2:$B$110,C92)&gt;0,ROUND(G92*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B92,İndirimler!$B$2:$B$110,C92)),2),"")</f>
         <v>474.6</v>
       </c>
-      <c r="J92" s="12"/>
+      <c r="J92" s="12" t="s">
+        <v>733</v>
+      </c>
       <c r="K92" s="30"/>
     </row>
     <row r="93" spans="1:11" ht="21.95" customHeight="1">
@@ -5771,7 +6023,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B97,İndirimler!$B$2:$B$110,C97)&gt;0,ROUND(G97*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B97,İndirimler!$B$2:$B$110,C97)),2),"")</f>
         <v>358.4</v>
       </c>
-      <c r="J97" s="12"/>
+      <c r="J97" s="12" t="s">
+        <v>722</v>
+      </c>
       <c r="K97" s="30"/>
     </row>
     <row r="98" spans="1:11" ht="21.95" customHeight="1">
@@ -5969,7 +6223,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B103,İndirimler!$B$2:$B$110,C103)&gt;0,ROUND(G103*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B103,İndirimler!$B$2:$B$110,C103)),2),"")</f>
         <v>469</v>
       </c>
-      <c r="J103" s="12"/>
+      <c r="J103" s="12" t="s">
+        <v>734</v>
+      </c>
       <c r="K103" s="30"/>
     </row>
     <row r="104" spans="1:11" ht="21.95" customHeight="1">
@@ -6500,7 +6756,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B120,İndirimler!$B$2:$B$110,C120)&gt;0,ROUND(G120*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B120,İndirimler!$B$2:$B$110,C120)),2),"")</f>
         <v>382.2</v>
       </c>
-      <c r="J120" s="12"/>
+      <c r="J120" s="12" t="s">
+        <v>747</v>
+      </c>
       <c r="K120" s="30"/>
     </row>
     <row r="121" spans="1:11" ht="21.95" customHeight="1">
@@ -6781,7 +7039,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B129,İndirimler!$B$2:$B$110,C129)&gt;0,ROUND(G129*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B129,İndirimler!$B$2:$B$110,C129)),2),"")</f>
         <v>348.6</v>
       </c>
-      <c r="J129" s="12"/>
+      <c r="J129" s="31" t="s">
+        <v>748</v>
+      </c>
       <c r="K129" s="30"/>
     </row>
     <row r="130" spans="1:11" ht="21.95" customHeight="1">
@@ -7188,7 +7448,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B142,İndirimler!$B$2:$B$110,C142)&gt;0,ROUND(G142*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B142,İndirimler!$B$2:$B$110,C142)),2),"")</f>
         <v>385</v>
       </c>
-      <c r="J142" s="12"/>
+      <c r="J142" s="12" t="s">
+        <v>728</v>
+      </c>
       <c r="K142" s="30"/>
     </row>
     <row r="143" spans="1:11" ht="21.95" customHeight="1">
@@ -8386,7 +8648,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B180,İndirimler!$B$2:$B$110,C180)&gt;0,ROUND(G180*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B180,İndirimler!$B$2:$B$110,C180)),2),"")</f>
         <v>479.5</v>
       </c>
-      <c r="J180" s="12"/>
+      <c r="J180" s="31"/>
       <c r="K180" s="30"/>
     </row>
     <row r="181" spans="1:11" ht="21.95" customHeight="1">
@@ -8419,7 +8681,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B181,İndirimler!$B$2:$B$110,C181)&gt;0,ROUND(G181*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B181,İndirimler!$B$2:$B$110,C181)),2),"")</f>
         <v>334.6</v>
       </c>
-      <c r="J181" s="12"/>
+      <c r="J181" s="31" t="s">
+        <v>700</v>
+      </c>
       <c r="K181" s="30"/>
     </row>
     <row r="182" spans="1:11" ht="21.95" customHeight="1">
@@ -8516,7 +8780,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B184,İndirimler!$B$2:$B$110,C184)&gt;0,ROUND(G184*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B184,İndirimler!$B$2:$B$110,C184)),2),"")</f>
         <v>403.2</v>
       </c>
-      <c r="J184" s="12"/>
+      <c r="J184" s="12" t="s">
+        <v>711</v>
+      </c>
       <c r="K184" s="30"/>
     </row>
     <row r="185" spans="1:11" ht="21.95" customHeight="1">
@@ -8644,7 +8910,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B188,İndirimler!$B$2:$B$110,C188)&gt;0,ROUND(G188*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B188,İndirimler!$B$2:$B$110,C188)),2),"")</f>
         <v>291.2</v>
       </c>
-      <c r="J188" s="12"/>
+      <c r="J188" s="31" t="s">
+        <v>701</v>
+      </c>
       <c r="K188" s="30"/>
     </row>
     <row r="189" spans="1:11" ht="21.95" customHeight="1">
@@ -8838,7 +9106,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B194,İndirimler!$B$2:$B$110,C194)&gt;0,ROUND(G194*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B194,İndirimler!$B$2:$B$110,C194)),2),"")</f>
         <v>392</v>
       </c>
-      <c r="J194" s="12"/>
+      <c r="J194" s="31" t="s">
+        <v>712</v>
+      </c>
       <c r="K194" s="30"/>
     </row>
     <row r="195" spans="1:11" ht="21.95" customHeight="1">
@@ -9100,7 +9370,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B202,İndirimler!$B$2:$B$110,C202)&gt;0,ROUND(G202*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B202,İndirimler!$B$2:$B$110,C202)),2),"")</f>
         <v>399</v>
       </c>
-      <c r="J202" s="12"/>
+      <c r="J202" s="12" t="s">
+        <v>723</v>
+      </c>
       <c r="K202" s="30"/>
     </row>
     <row r="203" spans="1:11" ht="21.95" customHeight="1">
@@ -9197,7 +9469,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B205,İndirimler!$B$2:$B$110,C205)&gt;0,ROUND(G205*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B205,İndirimler!$B$2:$B$110,C205)),2),"")</f>
         <v>425.6</v>
       </c>
-      <c r="J205" s="12"/>
+      <c r="J205" s="12" t="s">
+        <v>735</v>
+      </c>
       <c r="K205" s="30"/>
     </row>
     <row r="206" spans="1:11" ht="21.95" customHeight="1">
@@ -9325,7 +9599,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B209,İndirimler!$B$2:$B$110,C209)&gt;0,ROUND(G209*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B209,İndirimler!$B$2:$B$110,C209)),2),"")</f>
         <v>369.6</v>
       </c>
-      <c r="J209" s="12"/>
+      <c r="J209" s="12" t="s">
+        <v>724</v>
+      </c>
       <c r="K209" s="30"/>
     </row>
     <row r="210" spans="1:11" ht="21.95" customHeight="1">
@@ -9550,7 +9826,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B216,İndirimler!$B$2:$B$110,C216)&gt;0,ROUND(G216*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B216,İndirimler!$B$2:$B$110,C216)),2),"")</f>
         <v>413</v>
       </c>
-      <c r="J216" s="12"/>
+      <c r="J216" s="12" t="s">
+        <v>736</v>
+      </c>
       <c r="K216" s="30"/>
     </row>
     <row r="217" spans="1:11" ht="21.95" customHeight="1">
@@ -9833,7 +10111,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B225,İndirimler!$B$2:$B$110,C225)&gt;0,ROUND(G225*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B225,İndirimler!$B$2:$B$110,C225)),2),"")</f>
         <v>343</v>
       </c>
-      <c r="J225" s="12"/>
+      <c r="J225" s="12" t="s">
+        <v>749</v>
+      </c>
       <c r="K225" s="30"/>
     </row>
     <row r="226" spans="1:11" ht="21.95" customHeight="1">
@@ -10106,7 +10386,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B234,İndirimler!$B$2:$B$110,C234)&gt;0,ROUND(G234*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B234,İndirimler!$B$2:$B$110,C234)),2),"")</f>
         <v>348.6</v>
       </c>
-      <c r="J234" s="12"/>
+      <c r="J234" s="12" t="s">
+        <v>750</v>
+      </c>
       <c r="K234" s="30"/>
     </row>
     <row r="235" spans="1:11" ht="21.95" customHeight="1">
@@ -10362,7 +10644,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B242,İndirimler!$B$2:$B$110,C242)&gt;0,ROUND(G242*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B242,İndirimler!$B$2:$B$110,C242)),2),"")</f>
         <v>243.6</v>
       </c>
-      <c r="J242" s="12"/>
+      <c r="J242" s="12" t="s">
+        <v>729</v>
+      </c>
       <c r="K242" s="30"/>
     </row>
     <row r="243" spans="1:11" ht="21.95" customHeight="1">
@@ -10860,7 +11144,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B258,İndirimler!$B$2:$B$110,C258)&gt;0,ROUND(G258*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B258,İndirimler!$B$2:$B$110,C258)),2),"")</f>
         <v>430.5</v>
       </c>
-      <c r="J258" s="12"/>
+      <c r="J258" s="12" t="s">
+        <v>767</v>
+      </c>
       <c r="K258" s="30"/>
     </row>
     <row r="259" spans="1:11" ht="21.95" customHeight="1">
@@ -10893,7 +11179,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B259,İndirimler!$B$2:$B$110,C259)&gt;0,ROUND(G259*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B259,İndirimler!$B$2:$B$110,C259)),2),"")</f>
         <v>360.5</v>
       </c>
-      <c r="J259" s="12"/>
+      <c r="J259" s="31" t="s">
+        <v>702</v>
+      </c>
       <c r="K259" s="30"/>
     </row>
     <row r="260" spans="1:11" ht="21.95" customHeight="1">
@@ -10990,7 +11278,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B262,İndirimler!$B$2:$B$110,C262)&gt;0,ROUND(G262*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B262,İndirimler!$B$2:$B$110,C262)),2),"")</f>
         <v>383.6</v>
       </c>
-      <c r="J262" s="12"/>
+      <c r="J262" s="31" t="s">
+        <v>713</v>
+      </c>
       <c r="K262" s="30"/>
     </row>
     <row r="263" spans="1:11" ht="21.95" customHeight="1">
@@ -11116,7 +11406,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B266,İndirimler!$B$2:$B$110,C266)&gt;0,ROUND(G266*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B266,İndirimler!$B$2:$B$110,C266)),2),"")</f>
         <v>414.4</v>
       </c>
-      <c r="J266" s="12"/>
+      <c r="J266" s="31" t="s">
+        <v>704</v>
+      </c>
       <c r="K266" s="30"/>
     </row>
     <row r="267" spans="1:11" ht="21.95" customHeight="1">
@@ -11248,7 +11540,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B270,İndirimler!$B$2:$B$110,C270)&gt;0,ROUND(G270*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B270,İndirimler!$B$2:$B$110,C270)),2),"")</f>
         <v>383.6</v>
       </c>
-      <c r="J270" s="12"/>
+      <c r="J270" s="31" t="s">
+        <v>714</v>
+      </c>
       <c r="K270" s="30"/>
     </row>
     <row r="271" spans="1:11" ht="21.95" customHeight="1">
@@ -11506,7 +11800,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B278,İndirimler!$B$2:$B$110,C278)&gt;0,ROUND(G278*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B278,İndirimler!$B$2:$B$110,C278)),2),"")</f>
         <v>386.4</v>
       </c>
-      <c r="J278" s="12"/>
+      <c r="J278" s="12" t="s">
+        <v>725</v>
+      </c>
       <c r="K278" s="30"/>
     </row>
     <row r="279" spans="1:11" ht="21.95" customHeight="1">
@@ -11603,7 +11899,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B281,İndirimler!$B$2:$B$110,C281)&gt;0,ROUND(G281*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B281,İndirimler!$B$2:$B$110,C281)),2),"")</f>
         <v>434</v>
       </c>
-      <c r="J281" s="12"/>
+      <c r="J281" s="12" t="s">
+        <v>737</v>
+      </c>
       <c r="K281" s="30"/>
     </row>
     <row r="282" spans="1:11" ht="21.95" customHeight="1">
@@ -11729,7 +12027,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B285,İndirimler!$B$2:$B$110,C285)&gt;0,ROUND(G285*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B285,İndirimler!$B$2:$B$110,C285)),2),"")</f>
         <v>392</v>
       </c>
-      <c r="J285" s="12"/>
+      <c r="J285" s="12" t="s">
+        <v>726</v>
+      </c>
       <c r="K285" s="30"/>
     </row>
     <row r="286" spans="1:11" ht="21.95" customHeight="1">
@@ -11861,7 +12161,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B289,İndirimler!$B$2:$B$110,C289)&gt;0,ROUND(G289*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B289,İndirimler!$B$2:$B$110,C289)),2),"")</f>
         <v>404.6</v>
       </c>
-      <c r="J289" s="12"/>
+      <c r="J289" s="12" t="s">
+        <v>738</v>
+      </c>
       <c r="K289" s="30"/>
     </row>
     <row r="290" spans="1:11" ht="21.95" customHeight="1">
@@ -12175,7 +12477,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B299,İndirimler!$B$2:$B$110,C299)&gt;0,ROUND(G299*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B299,İndirimler!$B$2:$B$110,C299)),2),"")</f>
         <v>343</v>
       </c>
-      <c r="J299" s="12"/>
+      <c r="J299" s="12" t="s">
+        <v>751</v>
+      </c>
       <c r="K299" s="30"/>
     </row>
     <row r="300" spans="1:11" ht="21.95" customHeight="1">
@@ -12392,7 +12696,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B306,İndirimler!$B$2:$B$110,C306)&gt;0,ROUND(G306*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B306,İndirimler!$B$2:$B$110,C306)),2),"")</f>
         <v>313.60000000000002</v>
       </c>
-      <c r="J306" s="12"/>
+      <c r="J306" s="12" t="s">
+        <v>752</v>
+      </c>
       <c r="K306" s="30"/>
     </row>
     <row r="307" spans="1:11" ht="21.95" customHeight="1">
@@ -12582,7 +12888,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B312,İndirimler!$B$2:$B$110,C312)&gt;0,ROUND(G312*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B312,İndirimler!$B$2:$B$110,C312)),2),"")</f>
         <v>250.6</v>
       </c>
-      <c r="J312" s="12"/>
+      <c r="J312" s="12" t="s">
+        <v>730</v>
+      </c>
       <c r="K312" s="30"/>
     </row>
     <row r="313" spans="1:11" ht="21.95" customHeight="1">
@@ -12993,7 +13301,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B325,İndirimler!$B$2:$B$110,C325)&gt;0,ROUND(G325*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B325,İndirimler!$B$2:$B$110,C325)),2),"")</f>
         <v>528.5</v>
       </c>
-      <c r="J325" s="12"/>
+      <c r="J325" s="12" t="s">
+        <v>768</v>
+      </c>
       <c r="K325" s="30"/>
     </row>
     <row r="326" spans="1:11" ht="21.95" customHeight="1">
@@ -13057,7 +13367,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B327,İndirimler!$B$2:$B$110,C327)&gt;0,ROUND(G327*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B327,İndirimler!$B$2:$B$110,C327)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J327" s="12"/>
+      <c r="J327" s="12" t="s">
+        <v>760</v>
+      </c>
       <c r="K327" s="30" t="s">
         <v>435</v>
       </c>
@@ -13125,7 +13437,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B329,İndirimler!$B$2:$B$110,C329)&gt;0,ROUND(G329*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B329,İndirimler!$B$2:$B$110,C329)),2),"")</f>
         <v>364</v>
       </c>
-      <c r="J329" s="12"/>
+      <c r="J329" s="31" t="s">
+        <v>715</v>
+      </c>
       <c r="K329" s="30"/>
     </row>
     <row r="330" spans="1:11" ht="21.95" customHeight="1">
@@ -13222,7 +13536,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B332,İndirimler!$B$2:$B$110,C332)&gt;0,ROUND(G332*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B332,İndirimler!$B$2:$B$110,C332)),2),"")</f>
         <v>336</v>
       </c>
-      <c r="J332" s="12"/>
+      <c r="J332" s="31" t="s">
+        <v>703</v>
+      </c>
       <c r="K332" s="30"/>
     </row>
     <row r="333" spans="1:11" ht="21.95" customHeight="1">
@@ -13286,7 +13602,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B334,İndirimler!$B$2:$B$110,C334)&gt;0,ROUND(G334*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B334,İndirimler!$B$2:$B$110,C334)),2),"")</f>
         <v>314.3</v>
       </c>
-      <c r="J334" s="12"/>
+      <c r="J334" s="12" t="s">
+        <v>761</v>
+      </c>
       <c r="K334" s="30" t="s">
         <v>446</v>
       </c>
@@ -13321,7 +13639,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B335,İndirimler!$B$2:$B$110,C335)&gt;0,ROUND(G335*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B335,İndirimler!$B$2:$B$110,C335)),2),"")</f>
         <v>314.3</v>
       </c>
-      <c r="J335" s="12"/>
+      <c r="J335" s="12" t="s">
+        <v>762</v>
+      </c>
       <c r="K335" s="30" t="s">
         <v>448</v>
       </c>
@@ -13422,7 +13742,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B338,İndirimler!$B$2:$B$110,C338)&gt;0,ROUND(G338*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B338,İndirimler!$B$2:$B$110,C338)),2),"")</f>
         <v>406</v>
       </c>
-      <c r="J338" s="12"/>
+      <c r="J338" s="31" t="s">
+        <v>716</v>
+      </c>
       <c r="K338" s="30"/>
     </row>
     <row r="339" spans="1:11" ht="21.95" customHeight="1">
@@ -13678,7 +14000,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B346,İndirimler!$B$2:$B$110,C346)&gt;0,ROUND(G346*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B346,İndirimler!$B$2:$B$110,C346)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J346" s="12"/>
+      <c r="J346" s="12" t="s">
+        <v>763</v>
+      </c>
       <c r="K346" s="30" t="s">
         <v>462</v>
       </c>
@@ -13746,7 +14070,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B348,İndirimler!$B$2:$B$110,C348)&gt;0,ROUND(G348*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B348,İndirimler!$B$2:$B$110,C348)),2),"")</f>
         <v>425.6</v>
       </c>
-      <c r="J348" s="12"/>
+      <c r="J348" s="12" t="s">
+        <v>739</v>
+      </c>
       <c r="K348" s="30"/>
     </row>
     <row r="349" spans="1:11" ht="21.95" customHeight="1">
@@ -13843,7 +14169,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B351,İndirimler!$B$2:$B$110,C351)&gt;0,ROUND(G351*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B351,İndirimler!$B$2:$B$110,C351)),2),"")</f>
         <v>347.2</v>
       </c>
-      <c r="J351" s="12"/>
+      <c r="J351" s="12" t="s">
+        <v>727</v>
+      </c>
       <c r="K351" s="30"/>
     </row>
     <row r="352" spans="1:11" ht="21.95" customHeight="1">
@@ -13907,7 +14235,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B353,İndirimler!$B$2:$B$110,C353)&gt;0,ROUND(G353*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B353,İndirimler!$B$2:$B$110,C353)),2),"")</f>
         <v>314.3</v>
       </c>
-      <c r="J353" s="12"/>
+      <c r="J353" s="12" t="s">
+        <v>764</v>
+      </c>
       <c r="K353" s="30" t="s">
         <v>472</v>
       </c>
@@ -13942,7 +14272,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B354,İndirimler!$B$2:$B$110,C354)&gt;0,ROUND(G354*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B354,İndirimler!$B$2:$B$110,C354)),2),"")</f>
         <v>314.3</v>
       </c>
-      <c r="J354" s="12"/>
+      <c r="J354" s="12" t="s">
+        <v>765</v>
+      </c>
       <c r="K354" s="30" t="s">
         <v>475</v>
       </c>
@@ -14043,7 +14375,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B357,İndirimler!$B$2:$B$110,C357)&gt;0,ROUND(G357*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B357,İndirimler!$B$2:$B$110,C357)),2),"")</f>
         <v>343</v>
       </c>
-      <c r="J357" s="12"/>
+      <c r="J357" s="12" t="s">
+        <v>740</v>
+      </c>
       <c r="K357" s="30"/>
     </row>
     <row r="358" spans="1:11" ht="21.95" customHeight="1">
@@ -14293,7 +14627,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B365,İndirimler!$B$2:$B$110,C365)&gt;0,ROUND(G365*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B365,İndirimler!$B$2:$B$110,C365)),2),"")</f>
         <v>340.2</v>
       </c>
-      <c r="J365" s="12"/>
+      <c r="J365" s="12" t="s">
+        <v>753</v>
+      </c>
       <c r="K365" s="30"/>
     </row>
     <row r="366" spans="1:11" ht="21.95" customHeight="1">
@@ -14448,7 +14784,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B370,İndirimler!$B$2:$B$110,C370)&gt;0,ROUND(G370*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B370,İndirimler!$B$2:$B$110,C370)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J370" s="12"/>
+      <c r="J370" s="12" t="s">
+        <v>766</v>
+      </c>
       <c r="K370" s="30"/>
     </row>
     <row r="371" spans="1:11" ht="21.95" customHeight="1">
@@ -14510,7 +14848,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B372,İndirimler!$B$2:$B$110,C372)&gt;0,ROUND(G372*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B372,İndirimler!$B$2:$B$110,C372)),2),"")</f>
         <v>306.60000000000002</v>
       </c>
-      <c r="J372" s="12"/>
+      <c r="J372" s="12" t="s">
+        <v>754</v>
+      </c>
       <c r="K372" s="30"/>
     </row>
     <row r="373" spans="1:11" ht="21.95" customHeight="1">
@@ -15012,7 +15352,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B388,İndirimler!$B$2:$B$110,C388)&gt;0,ROUND(G388*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B388,İndirimler!$B$2:$B$110,C388)),2),"")</f>
         <v>377.3</v>
       </c>
-      <c r="J388" s="12"/>
+      <c r="J388" s="12" t="s">
+        <v>769</v>
+      </c>
       <c r="K388" s="30"/>
     </row>
     <row r="389" spans="1:11" ht="21.95" customHeight="1">
@@ -15078,7 +15420,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B390,İndirimler!$B$2:$B$110,C390)&gt;0,ROUND(G390*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B390,İndirimler!$B$2:$B$110,C390)),2),"")</f>
         <v>383.6</v>
       </c>
-      <c r="J390" s="12"/>
+      <c r="J390" s="12" t="s">
+        <v>717</v>
+      </c>
       <c r="K390" s="30"/>
     </row>
     <row r="391" spans="1:11" ht="21.95" customHeight="1">
@@ -15274,7 +15618,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B396,İndirimler!$B$2:$B$110,C396)&gt;0,ROUND(G396*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B396,İndirimler!$B$2:$B$110,C396)),2),"")</f>
         <v>383.6</v>
       </c>
-      <c r="J396" s="12"/>
+      <c r="J396" s="12" t="s">
+        <v>718</v>
+      </c>
       <c r="K396" s="30"/>
     </row>
     <row r="397" spans="1:11" ht="21.95" customHeight="1">
@@ -15468,7 +15814,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B402,İndirimler!$B$2:$B$110,C402)&gt;0,ROUND(G402*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B402,İndirimler!$B$2:$B$110,C402)),2),"")</f>
         <v>425.6</v>
       </c>
-      <c r="J402" s="12"/>
+      <c r="J402" s="12" t="s">
+        <v>741</v>
+      </c>
       <c r="K402" s="30"/>
     </row>
     <row r="403" spans="1:11" ht="21.95" customHeight="1">
@@ -15664,7 +16012,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B408,İndirimler!$B$2:$B$110,C408)&gt;0,ROUND(G408*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B408,İndirimler!$B$2:$B$110,C408)),2),"")</f>
         <v>433.3</v>
       </c>
-      <c r="J408" s="12"/>
+      <c r="J408" s="12" t="s">
+        <v>742</v>
+      </c>
       <c r="K408" s="30"/>
     </row>
     <row r="409" spans="1:11" ht="21.95" customHeight="1">
@@ -15852,7 +16202,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B414,İndirimler!$B$2:$B$110,C414)&gt;0,ROUND(G414*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B414,İndirimler!$B$2:$B$110,C414)),2),"")</f>
         <v>340.2</v>
       </c>
-      <c r="J414" s="12"/>
+      <c r="J414" s="12" t="s">
+        <v>755</v>
+      </c>
       <c r="K414" s="30"/>
     </row>
     <row r="415" spans="1:11" ht="21.95" customHeight="1">
@@ -16003,7 +16355,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B419,İndirimler!$B$2:$B$110,C419)&gt;0,ROUND(G419*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B419,İndirimler!$B$2:$B$110,C419)),2),"")</f>
         <v>324.8</v>
       </c>
-      <c r="J419" s="12"/>
+      <c r="J419" s="12" t="s">
+        <v>756</v>
+      </c>
       <c r="K419" s="30"/>
     </row>
     <row r="420" spans="1:11" ht="21.95" customHeight="1">
@@ -16218,7 +16572,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B426,İndirimler!$B$2:$B$110,C426)&gt;0,ROUND(G426*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B426,İndirimler!$B$2:$B$110,C426)),2),"")</f>
         <v>461.3</v>
       </c>
-      <c r="J426" s="12"/>
+      <c r="J426" s="12" t="s">
+        <v>770</v>
+      </c>
       <c r="K426" s="30"/>
     </row>
     <row r="427" spans="1:11" ht="21.95" customHeight="1">
@@ -16313,7 +16669,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B429,İndirimler!$B$2:$B$110,C429)&gt;0,ROUND(G429*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B429,İndirimler!$B$2:$B$110,C429)),2),"")</f>
         <v>433.3</v>
       </c>
-      <c r="J429" s="12"/>
+      <c r="J429" s="31" t="s">
+        <v>719</v>
+      </c>
       <c r="K429" s="30"/>
     </row>
     <row r="430" spans="1:11" ht="21.95" customHeight="1">
@@ -16509,7 +16867,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B435,İndirimler!$B$2:$B$110,C435)&gt;0,ROUND(G435*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B435,İndirimler!$B$2:$B$110,C435)),2),"")</f>
         <v>406</v>
       </c>
-      <c r="J435" s="12"/>
+      <c r="J435" s="12" t="s">
+        <v>720</v>
+      </c>
       <c r="K435" s="30"/>
     </row>
     <row r="436" spans="1:11" ht="21.95" customHeight="1">
@@ -16765,7 +17125,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B443,İndirimler!$B$2:$B$110,C443)&gt;0,ROUND(G443*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B443,İndirimler!$B$2:$B$110,C443)),2),"")</f>
         <v>439.6</v>
       </c>
-      <c r="J443" s="12"/>
+      <c r="J443" s="12" t="s">
+        <v>743</v>
+      </c>
       <c r="K443" s="30"/>
     </row>
     <row r="444" spans="1:11" ht="21.95" customHeight="1">
@@ -16959,7 +17321,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B449,İndirimler!$B$2:$B$110,C449)&gt;0,ROUND(G449*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B449,İndirimler!$B$2:$B$110,C449)),2),"")</f>
         <v>435.4</v>
       </c>
-      <c r="J449" s="12"/>
+      <c r="J449" s="12" t="s">
+        <v>744</v>
+      </c>
       <c r="K449" s="30"/>
     </row>
     <row r="450" spans="1:11" ht="21.95" customHeight="1">
@@ -17176,7 +17540,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B456,İndirimler!$B$2:$B$110,C456)&gt;0,ROUND(G456*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B456,İndirimler!$B$2:$B$110,C456)),2),"")</f>
         <v>348.6</v>
       </c>
-      <c r="J456" s="12"/>
+      <c r="J456" s="12" t="s">
+        <v>757</v>
+      </c>
       <c r="K456" s="30"/>
     </row>
     <row r="457" spans="1:11" ht="21.95" customHeight="1">
@@ -17329,7 +17695,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B461,İndirimler!$B$2:$B$110,C461)&gt;0,ROUND(G461*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B461,İndirimler!$B$2:$B$110,C461)),2),"")</f>
         <v>343</v>
       </c>
-      <c r="J461" s="12"/>
+      <c r="J461" s="12" t="s">
+        <v>758</v>
+      </c>
       <c r="K461" s="30"/>
     </row>
     <row r="462" spans="1:11" ht="21.95" customHeight="1">
@@ -17777,7 +18145,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B475,İndirimler!$B$2:$B$110,C475)&gt;0,ROUND(G475*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B475,İndirimler!$B$2:$B$110,C475)),2),"")</f>
         <v>236.6</v>
       </c>
-      <c r="J475" s="12"/>
+      <c r="J475" s="12" t="s">
+        <v>759</v>
+      </c>
       <c r="K475" s="30"/>
     </row>
     <row r="476" spans="1:11" ht="21.95" customHeight="1">
@@ -18206,10 +18576,30 @@
     <hyperlink ref="J470" r:id="rId27" xr:uid="{31A01E12-6AC8-4177-8B2D-7CFCD44E8417}"/>
     <hyperlink ref="J304" r:id="rId28" xr:uid="{A4AE380D-4B87-4437-BB89-4773F040D583}"/>
     <hyperlink ref="J458" r:id="rId29" xr:uid="{8A06FEE5-F34A-44C9-A3D0-3F22C02299CA}"/>
+    <hyperlink ref="J62" r:id="rId30" location="p=1" xr:uid="{5AFA6750-C6A3-4801-A187-4AFF6A65A642}"/>
+    <hyperlink ref="J70" r:id="rId31" location="p=1" xr:uid="{C444E026-2AC0-4B4D-9E03-89F36AB609BE}"/>
+    <hyperlink ref="J181" r:id="rId32" xr:uid="{BC1BF0B5-707B-4AED-9DED-A91BA7EE6A46}"/>
+    <hyperlink ref="J188" r:id="rId33" xr:uid="{A083CB39-20C7-4755-8E37-DA9E0890722B}"/>
+    <hyperlink ref="J259" r:id="rId34" xr:uid="{4E60A13C-D451-439B-862D-CD0FB3FA1BCA}"/>
+    <hyperlink ref="J332" r:id="rId35" xr:uid="{87016D08-C106-41E9-8FBC-3901062186E4}"/>
+    <hyperlink ref="J266" r:id="rId36" location="p=1" xr:uid="{E1B50F41-B56B-4F6A-86E3-6FBDCCEF25FF}"/>
+    <hyperlink ref="J20" r:id="rId37" xr:uid="{48AAB0A1-EF5B-4878-B30F-F9BD22070494}"/>
+    <hyperlink ref="J64" r:id="rId38" xr:uid="{C8D3FBF3-5BD4-4085-8AA4-172924CCF22B}"/>
+    <hyperlink ref="J76" r:id="rId39" xr:uid="{7FCF337B-5F2A-4C3A-AD58-9A6B2D9B1EE0}"/>
+    <hyperlink ref="J194" r:id="rId40" xr:uid="{C781D89B-CCB5-450E-9B2B-7702DC9AFD1D}"/>
+    <hyperlink ref="J262" r:id="rId41" xr:uid="{B42DFCBF-185F-48CB-8E4E-CC69D088BEEC}"/>
+    <hyperlink ref="J270" r:id="rId42" xr:uid="{9C1FF28D-FDCC-4354-AA33-DA9E98E53D89}"/>
+    <hyperlink ref="J329" r:id="rId43" xr:uid="{BE919999-0AE7-4CCA-A490-9239D982CEF8}"/>
+    <hyperlink ref="J338" r:id="rId44" xr:uid="{957D701F-57A3-4D43-A147-46466A8B3A52}"/>
+    <hyperlink ref="J429" r:id="rId45" xr:uid="{C2D953AE-9E6E-4E21-986C-11C0D105B1AE}"/>
+    <hyperlink ref="J129" r:id="rId46" xr:uid="{C08DB0CE-10D9-4C97-9D87-96735B9A0422}"/>
+    <hyperlink ref="J10" r:id="rId47" xr:uid="{8EF72808-1E62-4D82-8E8C-FB880ECC3C12}"/>
+    <hyperlink ref="J61" r:id="rId48" xr:uid="{486EDB62-EEE6-4F68-B002-F9128E3B5716}"/>
+    <hyperlink ref="J22" r:id="rId49" xr:uid="{CF8FDB49-BA5C-4157-BF0B-8C58DA4AB9FA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId30"/>
+    <tablePart r:id="rId50"/>
   </tableParts>
 </worksheet>
 </file>

--- a/output/Fiyat-Listesi-Yonetim.xlsx
+++ b/output/Fiyat-Listesi-Yonetim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALS\Documents\26-27 Fiyat Listeleri\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FEE42A-E80D-4B17-9C5B-4A72B7DD618D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572DA820-91F0-4E04-A441-9BC13CE22EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3079" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3139" uniqueCount="830">
   <si>
     <t>Barkod</t>
   </si>
@@ -2337,25 +2337,193 @@
     <t>https://biyotik.com.tr/view/img/pdf/11.pdf</t>
   </si>
   <si>
-    <t>https://capyayinlari.com/Kitap/9._Sinif_Kimya_Seti/B2E5693C613F48C7B83C7DEF86D4147D</t>
-  </si>
-  <si>
-    <t>https://capyayinlari.com/Kitap/9._Sinif_Biyoloji_Seti/FFC79E08ED0B4A30A4A4523AD4D359A8</t>
-  </si>
-  <si>
-    <t>https://capyayinlari.com/Kitap/9._Sinif_Tarih_Seti/B01E33FFEF7E4440B6F781C9A950305F</t>
-  </si>
-  <si>
-    <t>https://capyayinlari.com/Kitap/9._Sinif_Co%C4%9Frafya_Seti/51AAAD61DD8349F2BA61C6ED823808B8</t>
-  </si>
-  <si>
-    <t>https://capyayinlari.com/Kitap/9_TDE_Soru_Bankasi/AE0784D7574C4AC8A3127A26DC0A6898</t>
-  </si>
-  <si>
     <t>https://online.fliphtml5.com/chncu/mibj/</t>
   </si>
   <si>
     <t>https://online.fliphtml5.com/chncu/xxtv/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/zgpd/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/zjmx/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/bkiw/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/fljb/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/zjwx/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/ynai/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/xwmz/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/bref/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/jgqp/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/iosj/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/xycg/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/tucv/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/gytr/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/bysh/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/gsqk/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/zbnn/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/serp/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/zlro/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/ymyi/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/jbyq/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/bzor/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/cwos/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/unbs/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/naki/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/topp/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/xzrr/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/avcj/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/dhzq/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/prwq/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/lhfz/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/chncu/swka/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/ftqu/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/lark/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/qqfx/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/glnk/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/ewtq/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/lcil/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/qkos/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/aois/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/xjvc/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/wsau/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/qdll/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/qnmp/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/tioy/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/afjs/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/wlxl/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/engb/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/mdhg/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/veus/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/yxzb/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/etww/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/dssa/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/xruh/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/ofyh/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/wpto/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/tctd/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/hpbi/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/rwci/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/zgtb/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/zymh/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/udqwy/dydh/</t>
   </si>
 </sst>
 </file>
@@ -2632,6 +2800,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UrunlerTablosu" displayName="UrunlerTablosu" ref="A1:K488" totalsRowShown="0">
+  <autoFilter ref="A1:K488" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Barkod"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Yayın"/>
@@ -2965,7 +3134,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B3,İndirimler!$B$2:$B$110,C3)&gt;0,ROUND(G3*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B3,İndirimler!$B$2:$B$110,C3)),2),"")</f>
         <v>377.3</v>
       </c>
-      <c r="J3" s="12"/>
+      <c r="J3" s="12" t="s">
+        <v>819</v>
+      </c>
       <c r="K3" s="30"/>
     </row>
     <row r="4" spans="1:11" ht="21.95" customHeight="1">
@@ -3189,7 +3360,7 @@
         <v>395.5</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="K10" s="30"/>
     </row>
@@ -3487,7 +3658,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B19,İndirimler!$B$2:$B$110,C19)&gt;0,ROUND(G19*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B19,İndirimler!$B$2:$B$110,C19)),2),"")</f>
         <v>332.5</v>
       </c>
-      <c r="J19" s="12"/>
+      <c r="J19" s="12" t="s">
+        <v>800</v>
+      </c>
       <c r="K19" s="30"/>
     </row>
     <row r="20" spans="1:11" ht="21.95" customHeight="1">
@@ -3586,9 +3759,7 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B22,İndirimler!$B$2:$B$110,C22)&gt;0,ROUND(G22*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B22,İndirimler!$B$2:$B$110,C22)),2),"")</f>
         <v>363.3</v>
       </c>
-      <c r="J22" s="31" t="s">
-        <v>771</v>
-      </c>
+      <c r="J22" s="31"/>
       <c r="K22" s="30"/>
     </row>
     <row r="23" spans="1:11" ht="21.95" customHeight="1">
@@ -3714,7 +3885,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B26,İndirimler!$B$2:$B$110,C26)&gt;0,ROUND(G26*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B26,İndirimler!$B$2:$B$110,C26)),2),"")</f>
         <v>412.3</v>
       </c>
-      <c r="J26" s="12"/>
+      <c r="J26" s="12" t="s">
+        <v>777</v>
+      </c>
       <c r="K26" s="30"/>
     </row>
     <row r="27" spans="1:11" ht="21.95" customHeight="1">
@@ -3980,7 +4153,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B34,İndirimler!$B$2:$B$110,C34)&gt;0,ROUND(G34*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B34,İndirimler!$B$2:$B$110,C34)),2),"")</f>
         <v>283.5</v>
       </c>
-      <c r="J34" s="12"/>
+      <c r="J34" s="12" t="s">
+        <v>806</v>
+      </c>
       <c r="K34" s="30"/>
     </row>
     <row r="35" spans="1:11" ht="21.95" customHeight="1">
@@ -4389,7 +4564,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B47,İndirimler!$B$2:$B$110,C47)&gt;0,ROUND(G47*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B47,İndirimler!$B$2:$B$110,C47)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J47" s="12"/>
+      <c r="J47" s="12" t="s">
+        <v>812</v>
+      </c>
       <c r="K47" s="30"/>
     </row>
     <row r="48" spans="1:11" ht="21.95" customHeight="1">
@@ -4836,7 +5013,7 @@
         <v>629.29999999999995</v>
       </c>
       <c r="J61" s="31" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="K61" s="30"/>
     </row>
@@ -5305,7 +5482,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B75,İndirimler!$B$2:$B$110,C75)&gt;0,ROUND(G75*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B75,İndirimler!$B$2:$B$110,C75)),2),"")</f>
         <v>381.5</v>
       </c>
-      <c r="J75" s="12"/>
+      <c r="J75" s="12" t="s">
+        <v>801</v>
+      </c>
       <c r="K75" s="30"/>
     </row>
     <row r="76" spans="1:11" ht="21.95" customHeight="1">
@@ -5497,7 +5676,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B81,İndirimler!$B$2:$B$110,C81)&gt;0,ROUND(G81*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B81,İndirimler!$B$2:$B$110,C81)),2),"")</f>
         <v>350</v>
       </c>
-      <c r="J81" s="12"/>
+      <c r="J81" s="12" t="s">
+        <v>774</v>
+      </c>
       <c r="K81" s="30"/>
     </row>
     <row r="82" spans="1:11" ht="21.95" customHeight="1">
@@ -5753,7 +5934,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B89,İndirimler!$B$2:$B$110,C89)&gt;0,ROUND(G89*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B89,İndirimler!$B$2:$B$110,C89)),2),"")</f>
         <v>545.29999999999995</v>
       </c>
-      <c r="J89" s="12"/>
+      <c r="J89" s="12" t="s">
+        <v>778</v>
+      </c>
       <c r="K89" s="30"/>
     </row>
     <row r="90" spans="1:11" ht="21.95" customHeight="1">
@@ -6190,7 +6373,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B102,İndirimler!$B$2:$B$110,C102)&gt;0,ROUND(G102*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B102,İndirimler!$B$2:$B$110,C102)),2),"")</f>
         <v>398.3</v>
       </c>
-      <c r="J102" s="12"/>
+      <c r="J102" s="12" t="s">
+        <v>807</v>
+      </c>
       <c r="K102" s="30"/>
     </row>
     <row r="103" spans="1:11" ht="21.95" customHeight="1">
@@ -6384,7 +6569,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B108,İndirimler!$B$2:$B$110,C108)&gt;0,ROUND(G108*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B108,İndirimler!$B$2:$B$110,C108)),2),"")</f>
         <v>363.3</v>
       </c>
-      <c r="J108" s="12"/>
+      <c r="J108" s="12" t="s">
+        <v>784</v>
+      </c>
       <c r="K108" s="30"/>
     </row>
     <row r="109" spans="1:11" ht="21.95" customHeight="1">
@@ -7006,7 +7193,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B128,İndirimler!$B$2:$B$110,C128)&gt;0,ROUND(G128*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B128,İndirimler!$B$2:$B$110,C128)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J128" s="12"/>
+      <c r="J128" s="31" t="s">
+        <v>813</v>
+      </c>
       <c r="K128" s="30"/>
     </row>
     <row r="129" spans="1:11" ht="21.95" customHeight="1">
@@ -7382,7 +7571,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B140,İndirimler!$B$2:$B$110,C140)&gt;0,ROUND(G140*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B140,İndirimler!$B$2:$B$110,C140)),2),"")</f>
         <v>545.29999999999995</v>
       </c>
-      <c r="J140" s="12"/>
+      <c r="J140" s="12" t="s">
+        <v>792</v>
+      </c>
       <c r="K140" s="30"/>
     </row>
     <row r="141" spans="1:11" ht="21.95" customHeight="1">
@@ -7415,7 +7606,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B141,İndirimler!$B$2:$B$110,C141)&gt;0,ROUND(G141*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B141,İndirimler!$B$2:$B$110,C141)),2),"")</f>
         <v>629.29999999999995</v>
       </c>
-      <c r="J141" s="12"/>
+      <c r="J141" s="12" t="s">
+        <v>796</v>
+      </c>
       <c r="K141" s="30"/>
     </row>
     <row r="142" spans="1:11" ht="21.95" customHeight="1">
@@ -7708,7 +7901,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B150,İndirimler!$B$2:$B$110,C150)&gt;0,ROUND(G150*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B150,İndirimler!$B$2:$B$110,C150)),2),"")</f>
         <v>384.3</v>
       </c>
-      <c r="J150" s="12"/>
+      <c r="J150" s="12" t="s">
+        <v>820</v>
+      </c>
       <c r="K150" s="30"/>
     </row>
     <row r="151" spans="1:11" ht="21.95" customHeight="1">
@@ -8270,7 +8465,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B168,İndirimler!$B$2:$B$110,C168)&gt;0,ROUND(G168*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B168,İndirimler!$B$2:$B$110,C168)),2),"")</f>
         <v>300.3</v>
       </c>
-      <c r="J168" s="12"/>
+      <c r="J168" s="12" t="s">
+        <v>821</v>
+      </c>
       <c r="K168" s="30"/>
     </row>
     <row r="169" spans="1:11" ht="21.95" customHeight="1">
@@ -8648,7 +8845,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B180,İndirimler!$B$2:$B$110,C180)&gt;0,ROUND(G180*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B180,İndirimler!$B$2:$B$110,C180)),2),"")</f>
         <v>479.5</v>
       </c>
-      <c r="J180" s="31"/>
+      <c r="J180" s="31" t="s">
+        <v>769</v>
+      </c>
       <c r="K180" s="30"/>
     </row>
     <row r="181" spans="1:11" ht="21.95" customHeight="1">
@@ -9075,7 +9274,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B193,İndirimler!$B$2:$B$110,C193)&gt;0,ROUND(G193*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B193,İndirimler!$B$2:$B$110,C193)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J193" s="12"/>
+      <c r="J193" s="12" t="s">
+        <v>802</v>
+      </c>
       <c r="K193" s="30"/>
     </row>
     <row r="194" spans="1:11" ht="21.95" customHeight="1">
@@ -9174,7 +9375,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B196,İndirimler!$B$2:$B$110,C196)&gt;0,ROUND(G196*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B196,İndirimler!$B$2:$B$110,C196)),2),"")</f>
         <v>286.3</v>
       </c>
-      <c r="J196" s="12"/>
+      <c r="J196" s="12" t="s">
+        <v>775</v>
+      </c>
       <c r="K196" s="30"/>
     </row>
     <row r="197" spans="1:11" ht="21.95" customHeight="1">
@@ -9337,7 +9540,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B201,İndirimler!$B$2:$B$110,C201)&gt;0,ROUND(G201*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B201,İndirimler!$B$2:$B$110,C201)),2),"")</f>
         <v>577.5</v>
       </c>
-      <c r="J201" s="12"/>
+      <c r="J201" s="12" t="s">
+        <v>779</v>
+      </c>
       <c r="K201" s="30"/>
     </row>
     <row r="202" spans="1:11" ht="21.95" customHeight="1">
@@ -9795,7 +10000,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B215,İndirimler!$B$2:$B$110,C215)&gt;0,ROUND(G215*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B215,İndirimler!$B$2:$B$110,C215)),2),"")</f>
         <v>367.5</v>
       </c>
-      <c r="J215" s="12"/>
+      <c r="J215" s="12" t="s">
+        <v>808</v>
+      </c>
       <c r="K215" s="30"/>
     </row>
     <row r="216" spans="1:11" ht="21.95" customHeight="1">
@@ -9894,7 +10101,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B218,İndirimler!$B$2:$B$110,C218)&gt;0,ROUND(G218*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B218,İndirimler!$B$2:$B$110,C218)),2),"")</f>
         <v>353.5</v>
       </c>
-      <c r="J218" s="12"/>
+      <c r="J218" s="12" t="s">
+        <v>785</v>
+      </c>
       <c r="K218" s="30"/>
     </row>
     <row r="219" spans="1:11" ht="21.95" customHeight="1">
@@ -10355,7 +10564,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B233,İndirimler!$B$2:$B$110,C233)&gt;0,ROUND(G233*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B233,İndirimler!$B$2:$B$110,C233)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J233" s="12"/>
+      <c r="J233" s="12" t="s">
+        <v>814</v>
+      </c>
       <c r="K233" s="30"/>
     </row>
     <row r="234" spans="1:11" ht="21.95" customHeight="1">
@@ -10578,7 +10789,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B240,İndirimler!$B$2:$B$110,C240)&gt;0,ROUND(G240*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B240,İndirimler!$B$2:$B$110,C240)),2),"")</f>
         <v>479.5</v>
       </c>
-      <c r="J240" s="12"/>
+      <c r="J240" s="12" t="s">
+        <v>793</v>
+      </c>
       <c r="K240" s="30"/>
     </row>
     <row r="241" spans="1:11" ht="21.95" customHeight="1">
@@ -10611,7 +10824,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B241,İndirimler!$B$2:$B$110,C241)&gt;0,ROUND(G241*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B241,İndirimler!$B$2:$B$110,C241)),2),"")</f>
         <v>479.5</v>
       </c>
-      <c r="J241" s="12"/>
+      <c r="J241" s="12" t="s">
+        <v>797</v>
+      </c>
       <c r="K241" s="30"/>
     </row>
     <row r="242" spans="1:11" ht="21.95" customHeight="1">
@@ -10803,7 +11018,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B247,İndirimler!$B$2:$B$110,C247)&gt;0,ROUND(G247*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B247,İndirimler!$B$2:$B$110,C247)),2),"")</f>
         <v>349.3</v>
       </c>
-      <c r="J247" s="12"/>
+      <c r="J247" s="12" t="s">
+        <v>821</v>
+      </c>
       <c r="K247" s="30"/>
     </row>
     <row r="248" spans="1:11" ht="21.95" customHeight="1">
@@ -11080,7 +11297,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B256,İndirimler!$B$2:$B$110,C256)&gt;0,ROUND(G256*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B256,İndirimler!$B$2:$B$110,C256)),2),"")</f>
         <v>454.3</v>
       </c>
-      <c r="J256" s="12"/>
+      <c r="J256" s="12" t="s">
+        <v>826</v>
+      </c>
       <c r="K256" s="30"/>
     </row>
     <row r="257" spans="1:11" ht="21.95" customHeight="1">
@@ -11144,8 +11363,8 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B258,İndirimler!$B$2:$B$110,C258)&gt;0,ROUND(G258*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B258,İndirimler!$B$2:$B$110,C258)),2),"")</f>
         <v>430.5</v>
       </c>
-      <c r="J258" s="12" t="s">
-        <v>767</v>
+      <c r="J258" s="31" t="s">
+        <v>770</v>
       </c>
       <c r="K258" s="30"/>
     </row>
@@ -11509,7 +11728,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B269,İndirimler!$B$2:$B$110,C269)&gt;0,ROUND(G269*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B269,İndirimler!$B$2:$B$110,C269)),2),"")</f>
         <v>332.5</v>
       </c>
-      <c r="J269" s="12"/>
+      <c r="J269" s="12" t="s">
+        <v>803</v>
+      </c>
       <c r="K269" s="30"/>
     </row>
     <row r="270" spans="1:11" ht="21.95" customHeight="1">
@@ -11606,7 +11827,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B272,İndirimler!$B$2:$B$110,C272)&gt;0,ROUND(G272*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B272,İndirimler!$B$2:$B$110,C272)),2),"")</f>
         <v>314.3</v>
       </c>
-      <c r="J272" s="12"/>
+      <c r="J272" s="12" t="s">
+        <v>827</v>
+      </c>
       <c r="K272" s="30"/>
     </row>
     <row r="273" spans="1:11" ht="21.95" customHeight="1">
@@ -11639,7 +11862,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B273,İndirimler!$B$2:$B$110,C273)&gt;0,ROUND(G273*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B273,İndirimler!$B$2:$B$110,C273)),2),"")</f>
         <v>241.5</v>
       </c>
-      <c r="J273" s="12"/>
+      <c r="J273" s="12" t="s">
+        <v>776</v>
+      </c>
       <c r="K273" s="30"/>
     </row>
     <row r="274" spans="1:11" ht="21.95" customHeight="1">
@@ -11703,7 +11928,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B275,İndirimler!$B$2:$B$110,C275)&gt;0,ROUND(G275*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B275,İndirimler!$B$2:$B$110,C275)),2),"")</f>
         <v>437.5</v>
       </c>
-      <c r="J275" s="12"/>
+      <c r="J275" s="12" t="s">
+        <v>828</v>
+      </c>
       <c r="K275" s="30"/>
     </row>
     <row r="276" spans="1:11" ht="21.95" customHeight="1">
@@ -11767,7 +11994,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B277,İndirimler!$B$2:$B$110,C277)&gt;0,ROUND(G277*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B277,İndirimler!$B$2:$B$110,C277)),2),"")</f>
         <v>444.5</v>
       </c>
-      <c r="J277" s="12"/>
+      <c r="J277" s="12" t="s">
+        <v>780</v>
+      </c>
       <c r="K277" s="30"/>
     </row>
     <row r="278" spans="1:11" ht="21.95" customHeight="1">
@@ -12130,7 +12359,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B288,İndirimler!$B$2:$B$110,C288)&gt;0,ROUND(G288*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B288,İndirimler!$B$2:$B$110,C288)),2),"")</f>
         <v>332.5</v>
       </c>
-      <c r="J288" s="12"/>
+      <c r="J288" s="12" t="s">
+        <v>809</v>
+      </c>
       <c r="K288" s="30"/>
     </row>
     <row r="289" spans="1:11" ht="21.95" customHeight="1">
@@ -12227,7 +12458,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B291,İndirimler!$B$2:$B$110,C291)&gt;0,ROUND(G291*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B291,İndirimler!$B$2:$B$110,C291)),2),"")</f>
         <v>307.3</v>
       </c>
-      <c r="J291" s="12"/>
+      <c r="J291" s="12" t="s">
+        <v>829</v>
+      </c>
       <c r="K291" s="30"/>
     </row>
     <row r="292" spans="1:11" ht="21.95" customHeight="1">
@@ -12260,7 +12493,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B292,İndirimler!$B$2:$B$110,C292)&gt;0,ROUND(G292*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B292,İndirimler!$B$2:$B$110,C292)),2),"")</f>
         <v>241.5</v>
       </c>
-      <c r="J292" s="12"/>
+      <c r="J292" s="12" t="s">
+        <v>786</v>
+      </c>
       <c r="K292" s="30"/>
     </row>
     <row r="293" spans="1:11" ht="21.95" customHeight="1">
@@ -12665,7 +12900,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B305,İndirimler!$B$2:$B$110,C305)&gt;0,ROUND(G305*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B305,İndirimler!$B$2:$B$110,C305)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J305" s="12"/>
+      <c r="J305" s="12" t="s">
+        <v>815</v>
+      </c>
       <c r="K305" s="30"/>
     </row>
     <row r="306" spans="1:11" ht="21.95" customHeight="1">
@@ -12822,7 +13059,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B310,İndirimler!$B$2:$B$110,C310)&gt;0,ROUND(G310*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B310,İndirimler!$B$2:$B$110,C310)),2),"")</f>
         <v>430.5</v>
       </c>
-      <c r="J310" s="12"/>
+      <c r="J310" s="12" t="s">
+        <v>794</v>
+      </c>
       <c r="K310" s="30"/>
     </row>
     <row r="311" spans="1:11" ht="21.95" customHeight="1">
@@ -12855,7 +13094,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B311,İndirimler!$B$2:$B$110,C311)&gt;0,ROUND(G311*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B311,İndirimler!$B$2:$B$110,C311)),2),"")</f>
         <v>430.5</v>
       </c>
-      <c r="J311" s="12"/>
+      <c r="J311" s="12" t="s">
+        <v>798</v>
+      </c>
       <c r="K311" s="30"/>
     </row>
     <row r="312" spans="1:11" ht="21.95" customHeight="1">
@@ -13082,7 +13323,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B318,İndirimler!$B$2:$B$110,C318)&gt;0,ROUND(G318*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B318,İndirimler!$B$2:$B$110,C318)),2),"")</f>
         <v>335.3</v>
       </c>
-      <c r="J318" s="12"/>
+      <c r="J318" s="12" t="s">
+        <v>822</v>
+      </c>
       <c r="K318" s="30"/>
     </row>
     <row r="319" spans="1:11" ht="21.95" customHeight="1">
@@ -13302,7 +13545,7 @@
         <v>528.5</v>
       </c>
       <c r="J325" s="12" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="K325" s="30"/>
     </row>
@@ -13711,7 +13954,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B337,İndirimler!$B$2:$B$110,C337)&gt;0,ROUND(G337*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B337,İndirimler!$B$2:$B$110,C337)),2),"")</f>
         <v>314.3</v>
       </c>
-      <c r="J337" s="12"/>
+      <c r="J337" s="12" t="s">
+        <v>804</v>
+      </c>
       <c r="K337" s="30"/>
     </row>
     <row r="338" spans="1:11" ht="21.95" customHeight="1">
@@ -13841,7 +14086,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B341,İndirimler!$B$2:$B$110,C341)&gt;0,ROUND(G341*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B341,İndirimler!$B$2:$B$110,C341)),2),"")</f>
         <v>251.3</v>
       </c>
-      <c r="J341" s="12"/>
+      <c r="J341" s="12" t="s">
+        <v>787</v>
+      </c>
       <c r="K341" s="30"/>
     </row>
     <row r="342" spans="1:11" ht="21.95" customHeight="1">
@@ -13936,7 +14183,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B344,İndirimler!$B$2:$B$110,C344)&gt;0,ROUND(G344*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B344,İndirimler!$B$2:$B$110,C344)),2),"")</f>
         <v>510.3</v>
       </c>
-      <c r="J344" s="12"/>
+      <c r="J344" s="12" t="s">
+        <v>781</v>
+      </c>
       <c r="K344" s="30"/>
     </row>
     <row r="345" spans="1:11" ht="21.95" customHeight="1">
@@ -14344,7 +14593,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B356,İndirimler!$B$2:$B$110,C356)&gt;0,ROUND(G356*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B356,İndirimler!$B$2:$B$110,C356)),2),"")</f>
         <v>314.3</v>
       </c>
-      <c r="J356" s="12"/>
+      <c r="J356" s="12" t="s">
+        <v>809</v>
+      </c>
       <c r="K356" s="30"/>
     </row>
     <row r="357" spans="1:11" ht="21.95" customHeight="1">
@@ -14474,7 +14725,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B360,İndirimler!$B$2:$B$110,C360)&gt;0,ROUND(G360*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B360,İndirimler!$B$2:$B$110,C360)),2),"")</f>
         <v>188.3</v>
       </c>
-      <c r="J360" s="12"/>
+      <c r="J360" s="12" t="s">
+        <v>787</v>
+      </c>
       <c r="K360" s="30"/>
     </row>
     <row r="361" spans="1:11" ht="21.95" customHeight="1">
@@ -14817,7 +15070,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B371,İndirimler!$B$2:$B$110,C371)&gt;0,ROUND(G371*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B371,İndirimler!$B$2:$B$110,C371)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J371" s="12"/>
+      <c r="J371" s="12" t="s">
+        <v>816</v>
+      </c>
       <c r="K371" s="30"/>
     </row>
     <row r="372" spans="1:11" ht="21.95" customHeight="1">
@@ -15003,7 +15258,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B377,İndirimler!$B$2:$B$110,C377)&gt;0,ROUND(G377*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B377,İndirimler!$B$2:$B$110,C377)),2),"")</f>
         <v>412.3</v>
       </c>
-      <c r="J377" s="12"/>
+      <c r="J377" s="12" t="s">
+        <v>795</v>
+      </c>
       <c r="K377" s="30"/>
     </row>
     <row r="378" spans="1:11" ht="21.95" customHeight="1">
@@ -15036,7 +15293,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B378,İndirimler!$B$2:$B$110,C378)&gt;0,ROUND(G378*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B378,İndirimler!$B$2:$B$110,C378)),2),"")</f>
         <v>412.3</v>
       </c>
-      <c r="J378" s="12"/>
+      <c r="J378" s="12" t="s">
+        <v>799</v>
+      </c>
       <c r="K378" s="30"/>
     </row>
     <row r="379" spans="1:11" ht="21.95" customHeight="1">
@@ -15162,7 +15421,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B382,İndirimler!$B$2:$B$110,C382)&gt;0,ROUND(G382*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B382,İndirimler!$B$2:$B$110,C382)),2),"")</f>
         <v>335.3</v>
       </c>
-      <c r="J382" s="12"/>
+      <c r="J382" s="12" t="s">
+        <v>823</v>
+      </c>
       <c r="K382" s="30"/>
     </row>
     <row r="383" spans="1:11" ht="21.95" customHeight="1">
@@ -15353,7 +15614,7 @@
         <v>377.3</v>
       </c>
       <c r="J388" s="12" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="K388" s="30"/>
     </row>
@@ -15587,7 +15848,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B395,İndirimler!$B$2:$B$110,C395)&gt;0,ROUND(G395*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B395,İndirimler!$B$2:$B$110,C395)),2),"")</f>
         <v>300.3</v>
       </c>
-      <c r="J395" s="12"/>
+      <c r="J395" s="12" t="s">
+        <v>805</v>
+      </c>
       <c r="K395" s="30"/>
     </row>
     <row r="396" spans="1:11" ht="21.95" customHeight="1">
@@ -15748,7 +16011,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B400,İndirimler!$B$2:$B$110,C400)&gt;0,ROUND(G400*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B400,İndirimler!$B$2:$B$110,C400)),2),"")</f>
         <v>545.29999999999995</v>
       </c>
-      <c r="J400" s="12"/>
+      <c r="J400" s="12" t="s">
+        <v>782</v>
+      </c>
       <c r="K400" s="30"/>
     </row>
     <row r="401" spans="1:11" ht="21.95" customHeight="1">
@@ -15981,7 +16246,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B407,İndirimler!$B$2:$B$110,C407)&gt;0,ROUND(G407*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B407,İndirimler!$B$2:$B$110,C407)),2),"")</f>
         <v>300.3</v>
       </c>
-      <c r="J407" s="12"/>
+      <c r="J407" s="12" t="s">
+        <v>810</v>
+      </c>
       <c r="K407" s="30"/>
     </row>
     <row r="408" spans="1:11" ht="21.95" customHeight="1">
@@ -16080,7 +16347,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B410,İndirimler!$B$2:$B$110,C410)&gt;0,ROUND(G410*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B410,İndirimler!$B$2:$B$110,C410)),2),"")</f>
         <v>206.5</v>
       </c>
-      <c r="J410" s="12"/>
+      <c r="J410" s="12" t="s">
+        <v>789</v>
+      </c>
       <c r="K410" s="30"/>
     </row>
     <row r="411" spans="1:11" ht="21.95" customHeight="1">
@@ -16324,7 +16593,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B418,İndirimler!$B$2:$B$110,C418)&gt;0,ROUND(G418*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B418,İndirimler!$B$2:$B$110,C418)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J418" s="12"/>
+      <c r="J418" s="12" t="s">
+        <v>817</v>
+      </c>
       <c r="K418" s="30"/>
     </row>
     <row r="419" spans="1:11" ht="21.95" customHeight="1">
@@ -16479,7 +16750,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B423,İndirimler!$B$2:$B$110,C423)&gt;0,ROUND(G423*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B423,İndirimler!$B$2:$B$110,C423)),2),"")</f>
         <v>300.3</v>
       </c>
-      <c r="J423" s="12"/>
+      <c r="J423" s="12" t="s">
+        <v>824</v>
+      </c>
       <c r="K423" s="30"/>
     </row>
     <row r="424" spans="1:11" ht="21.95" customHeight="1">
@@ -16573,7 +16846,7 @@
         <v>461.3</v>
       </c>
       <c r="J426" s="12" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="K426" s="30"/>
     </row>
@@ -16836,7 +17109,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B434,İndirimler!$B$2:$B$110,C434)&gt;0,ROUND(G434*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B434,İndirimler!$B$2:$B$110,C434)),2),"")</f>
         <v>314.3</v>
       </c>
-      <c r="J434" s="12"/>
+      <c r="J434" s="12" t="s">
+        <v>806</v>
+      </c>
       <c r="K434" s="30"/>
     </row>
     <row r="435" spans="1:11" ht="21.95" customHeight="1">
@@ -16935,7 +17210,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B437,İndirimler!$B$2:$B$110,C437)&gt;0,ROUND(G437*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B437,İndirimler!$B$2:$B$110,C437)),2),"")</f>
         <v>269.5</v>
       </c>
-      <c r="J437" s="12"/>
+      <c r="J437" s="12" t="s">
+        <v>788</v>
+      </c>
       <c r="K437" s="30"/>
     </row>
     <row r="438" spans="1:11" ht="21.95" customHeight="1">
@@ -17030,7 +17307,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B440,İndirimler!$B$2:$B$110,C440)&gt;0,ROUND(G440*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B440,İndirimler!$B$2:$B$110,C440)),2),"")</f>
         <v>412.3</v>
       </c>
-      <c r="J440" s="12"/>
+      <c r="J440" s="12" t="s">
+        <v>783</v>
+      </c>
       <c r="K440" s="30"/>
     </row>
     <row r="441" spans="1:11" ht="21.95" customHeight="1">
@@ -17290,7 +17569,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B448,İndirimler!$B$2:$B$110,C448)&gt;0,ROUND(G448*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B448,İndirimler!$B$2:$B$110,C448)),2),"")</f>
         <v>283.5</v>
       </c>
-      <c r="J448" s="12"/>
+      <c r="J448" s="12" t="s">
+        <v>811</v>
+      </c>
       <c r="K448" s="30"/>
     </row>
     <row r="449" spans="1:11" ht="21.95" customHeight="1">
@@ -17389,7 +17670,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B451,İndirimler!$B$2:$B$110,C451)&gt;0,ROUND(G451*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B451,İndirimler!$B$2:$B$110,C451)),2),"")</f>
         <v>286.3</v>
       </c>
-      <c r="J451" s="12"/>
+      <c r="J451" s="12" t="s">
+        <v>790</v>
+      </c>
       <c r="K451" s="30"/>
     </row>
     <row r="452" spans="1:11" ht="21.95" customHeight="1">
@@ -17664,7 +17947,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B460,İndirimler!$B$2:$B$110,C460)&gt;0,ROUND(G460*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B460,İndirimler!$B$2:$B$110,C460)),2),"")</f>
         <v>0</v>
       </c>
-      <c r="J460" s="12"/>
+      <c r="J460" s="12" t="s">
+        <v>818</v>
+      </c>
       <c r="K460" s="30"/>
     </row>
     <row r="461" spans="1:11" ht="21.95" customHeight="1">
@@ -17819,7 +18104,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B465,İndirimler!$B$2:$B$110,C465)&gt;0,ROUND(G465*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B465,İndirimler!$B$2:$B$110,C465)),2),"")</f>
         <v>321.3</v>
       </c>
-      <c r="J465" s="12"/>
+      <c r="J465" s="12" t="s">
+        <v>825</v>
+      </c>
       <c r="K465" s="30"/>
     </row>
     <row r="466" spans="1:11" ht="21.95" customHeight="1">
@@ -18083,7 +18370,9 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B473,İndirimler!$B$2:$B$110,C473)&gt;0,ROUND(G473*(1-SUMIFS(İndirimler!$D$2:$D$110,İndirimler!$A$2:$A$110,B473,İndirimler!$B$2:$B$110,C473)),2),"")</f>
         <v>241.5</v>
       </c>
-      <c r="J473" s="12"/>
+      <c r="J473" s="12" t="s">
+        <v>791</v>
+      </c>
       <c r="K473" s="30"/>
     </row>
     <row r="474" spans="1:11" ht="21.95" customHeight="1">
@@ -18595,11 +18884,12 @@
     <hyperlink ref="J129" r:id="rId46" xr:uid="{C08DB0CE-10D9-4C97-9D87-96735B9A0422}"/>
     <hyperlink ref="J10" r:id="rId47" xr:uid="{8EF72808-1E62-4D82-8E8C-FB880ECC3C12}"/>
     <hyperlink ref="J61" r:id="rId48" xr:uid="{486EDB62-EEE6-4F68-B002-F9128E3B5716}"/>
-    <hyperlink ref="J22" r:id="rId49" xr:uid="{CF8FDB49-BA5C-4157-BF0B-8C58DA4AB9FA}"/>
+    <hyperlink ref="J258" r:id="rId49" xr:uid="{C3EA6963-9AC1-47E9-9743-6490E4B9CF95}"/>
+    <hyperlink ref="J128" r:id="rId50" xr:uid="{B50B0463-738F-491E-A419-2E4B8423833B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId50"/>
+    <tablePart r:id="rId51"/>
   </tableParts>
 </worksheet>
 </file>

--- a/output/Fiyat-Listesi-Yonetim.xlsx
+++ b/output/Fiyat-Listesi-Yonetim.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ürünler" sheetId="1" r:id="R6c26f4d4d941499b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İndirimler" sheetId="2" r:id="Re89dfb461f60467a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasarım" sheetId="3" r:id="R82ab493ee7674199"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kullanım" sheetId="4" r:id="R8c6d36d35a44428f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ayarlar" sheetId="5" r:id="R31c0457105754066"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayfa Ayarları" sheetId="6" r:id="Ra0d52624b3754b38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İletişim" sheetId="7" r:id="R51e3681850e84c35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ürünler" sheetId="1" r:id="Rb9dd5a23b66a45b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İndirimler" sheetId="2" r:id="R9262368db7854836"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasarım" sheetId="3" r:id="R775ad0901e7e4d08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kullanım" sheetId="4" r:id="Rebb04810d08b444c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ayarlar" sheetId="5" r:id="Rab84dffcb1dc4beb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayfa Ayarları" sheetId="6" r:id="Re1d4f43611cc4a01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İletişim" sheetId="7" r:id="Rcb48a92fe6cc48f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2557,46 +2557,22 @@
     <x:t xml:space="preserve">Lise</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Sayfa Başlığı</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Açıklama</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Aktif</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ana Sayfa Sırası</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ortaokul kitapları ve güncel fiyat listesi</x:t>
+    <x:t xml:space="preserve">Ad Soyad</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Telefon</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WhatsApp</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Aytaç Arslan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">5345556747</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lise kitapları ve güncel fiyat listesi</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">#234E52</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">#F6C453</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ad Soyad</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Telefon</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WhatsApp</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Aytaç Arslan</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">5345556747</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Emre Arslan</x:t>
@@ -19084,60 +19060,60 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="R29b43ebe052745d2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="Rce941e6778a9467d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="R434631329d3e40ea"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="R941eebf69eef4319"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="Ra3636c17f23740fc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="R3e9ff2687d4f4651"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="R66e749e6d04e4849"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="R5792659ae8374280"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="R73e107d3306a4137"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="R94ab8d1270704ba3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="Ra6590a2d5f384eb2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="R3735bb2edd2e4e54"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="Rbaec0ddafff94432"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="R945b5ba11b4642f2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="R94859d1e88904e5f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="Rd11d6b7dae2e4382"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="Rbe63e1953aea401f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="R075e0017a1ca4994"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="Rf4896688a5c84152"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="R8ffd5e5d023041e1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="Ra2b7955c0e5a4110"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="R814a12013b17433f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="Rd59cfbf801c3478f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="Rb606f8c93ff24db3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="R747c4a1f73a449cf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="R87c09f0e72f14793"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="R4554d143576c451f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="R233a0caa61ae4c9d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="R3ed457c032fc4c78"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="R6eb62273335e4f62"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="R2e7e50ec035f42d3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="R9056acfba8074204"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="R2ad59aac3586417f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="R5002df22e17f4134"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J324" r:id="R349d95464f714e0e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="R39c1d10c26dd4066"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="R0e03bc3c0dbf4abf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="R58f8624d55b2423d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="R5802bd2f69fc4d06"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="R24d6fcc6d60c456a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="R63b95b1ab25443d3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="Ra2ffa85f14664ddd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="Rb3c762798ec54f5c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="R7b2e27aeb1284c88"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="R81283a263c154956"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="R8b9fb2a12f004c2c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="Rcfb71255122a4aac"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J439" r:id="Rfcbe50564eeb4b5c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="R981b66426ff44c54"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="Rd8a5e4c956df4678"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="Rf5868dd89b114609"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="R139e728302704965"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="R9d436fde78d847ef"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="Rd8980e6915fa48fe"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="R19ede4a5d10448b3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="Rd496114d2bd24d9a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="Reb1880f43a694ce6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="R9defe46981424341"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="R9f75206da06e41a3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="R77e803aa1f114c17"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="R9aaa654bcb524a1b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="R80e6cf0c9705469a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="R479e1e1130b64201"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="R606d0612f771420f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="Rf74ddffd193e43e0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="R37a87eba675940d3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="Rb76e57d610fe4af8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="Rddce47f265e24177"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="R535827b203c74fc6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="Rfe8781b183484799"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="R87c26f48771b475a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="Rd28f55383f4c43b5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="R37766e3ab8be4e0b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="R338ae189e6ce4ebd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="R05f3bb55c9d645f4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="R220e00d5b2fd4343"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="Rcc7ba72105774d5d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="Rb92eaffb5fd84575"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="R3737a0c6bc204ab3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="R251931cf7b114d91"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="R1dada3a02c224bf4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="R4fe669b275564fc2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="R7af2151606ea480c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="R5b8c448ed9ed4f68"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J324" r:id="R50796819c2ab4943"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="Rce65394aec5b4d3f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="Rd06211eecaef4aba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="R6376df39372c43ff"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="R958d641523014cc4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="R850011debe614713"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="Rcc41b3dc65ff492f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="Rb50101c11e5c498e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="R674d6173b8b04fe2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="R7137ee80738b43e2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="Rb2d1fbbffb694e88"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="R677bf6eb7b3549a6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="R56a3c8d98b3d49d9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J439" r:id="R15dac2b878e247b3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="R1b6983c0ad7044df"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="Rb21da75fbbcf427e"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf223b26615684644"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb561f65cb6f64d04"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20701,7 +20677,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb30064ad0ab4075"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4d258532f4b4aec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21266,8 +21242,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec52639d419446b2"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra48182bd9c384cec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4389774e21894828"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a07e837b7ed414a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21286,133 +21262,141 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="39" t="s">
-        <x:v>834</x:v>
-      </x:c>
-      <x:c r="B1" s="39" t="s">
-        <x:v>833</x:v>
-      </x:c>
-      <x:c r="C1" s="39" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="D1" s="39" t="s">
-        <x:v>848</x:v>
-      </x:c>
-      <x:c r="E1" s="39" t="s">
-        <x:v>812</x:v>
-      </x:c>
-      <x:c r="F1" s="39" t="s">
-        <x:v>814</x:v>
-      </x:c>
-      <x:c r="G1" s="39" t="s">
-        <x:v>849</x:v>
-      </x:c>
-      <x:c r="H1" s="39" t="s">
-        <x:v>850</x:v>
+      <x:c r="A1" s="39" t="str">
+        <x:v>Kitabevi Kodu</x:v>
+      </x:c>
+      <x:c r="B1" s="39" t="str">
+        <x:v>Kademe</x:v>
+      </x:c>
+      <x:c r="C1" s="39" t="str">
+        <x:v>Sayfa Başlığı</x:v>
+      </x:c>
+      <x:c r="D1" s="39" t="str">
+        <x:v>Açıklama</x:v>
+      </x:c>
+      <x:c r="E1" s="39" t="str">
+        <x:v>Ana Renk</x:v>
+      </x:c>
+      <x:c r="F1" s="39" t="str">
+        <x:v>Vurgu Rengi</x:v>
+      </x:c>
+      <x:c r="G1" s="39" t="str">
+        <x:v>Aktif</x:v>
+      </x:c>
+      <x:c r="H1" s="39" t="str">
+        <x:v>Ana Sayfa Sırası</x:v>
       </x:c>
       <x:c r="I1" s="57" t="str">
         <x:v>Logo Linki</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="40" t="s">
-        <x:v>839</x:v>
-      </x:c>
-      <x:c r="B2" s="40" t="s">
-        <x:v>838</x:v>
+      <x:c r="A2" s="40" t="str">
+        <x:v>kitabevi-1</x:v>
+      </x:c>
+      <x:c r="B2" s="40" t="str">
+        <x:v>Ortaokul</x:v>
       </x:c>
       <x:c r="C2" s="40"/>
-      <x:c r="D2" s="40" t="s">
-        <x:v>851</x:v>
-      </x:c>
-      <x:c r="E2" s="40" t="s">
-        <x:v>813</x:v>
-      </x:c>
-      <x:c r="F2" s="40" t="s">
-        <x:v>815</x:v>
-      </x:c>
-      <x:c r="G2" s="40" t="s">
-        <x:v>852</x:v>
-      </x:c>
-      <x:c r="H2" s="40">
+      <x:c r="D2" s="40" t="str">
+        <x:v>Ortaokul kitapları ve güncel fiyat listesi</x:v>
+      </x:c>
+      <x:c r="E2" s="40" t="str">
+        <x:v>#173F5F</x:v>
+      </x:c>
+      <x:c r="F2" s="40" t="str">
+        <x:v>#F2B134</x:v>
+      </x:c>
+      <x:c r="G2" s="40" t="str">
+        <x:v>Evet</x:v>
+      </x:c>
+      <x:c r="H2" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I2" s="60"/>
+      <x:c r="I2" s="60" t="str">
+        <x:v>assets/logos/isler-kitabevi.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="41" t="s">
-        <x:v>839</x:v>
-      </x:c>
-      <x:c r="B3" s="41" t="s">
-        <x:v>846</x:v>
+      <x:c r="A3" s="41" t="str">
+        <x:v>kitabevi-1</x:v>
+      </x:c>
+      <x:c r="B3" s="41" t="str">
+        <x:v>Lise</x:v>
       </x:c>
       <x:c r="C3" s="41"/>
-      <x:c r="D3" s="41" t="s">
-        <x:v>853</x:v>
-      </x:c>
-      <x:c r="E3" s="41" t="s">
-        <x:v>813</x:v>
-      </x:c>
-      <x:c r="F3" s="41" t="s">
-        <x:v>815</x:v>
-      </x:c>
-      <x:c r="G3" s="41" t="s">
-        <x:v>852</x:v>
-      </x:c>
-      <x:c r="H3" s="41">
+      <x:c r="D3" s="41" t="str">
+        <x:v>Lise kitapları ve güncel fiyat listesi</x:v>
+      </x:c>
+      <x:c r="E3" s="41" t="str">
+        <x:v>#173F5F</x:v>
+      </x:c>
+      <x:c r="F3" s="41" t="str">
+        <x:v>#F2B134</x:v>
+      </x:c>
+      <x:c r="G3" s="41" t="str">
+        <x:v>Evet</x:v>
+      </x:c>
+      <x:c r="H3" s="41" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I3" s="60"/>
+      <x:c r="I3" s="60" t="str">
+        <x:v>assets/logos/isler-kitabevi.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="41" t="s">
-        <x:v>842</x:v>
-      </x:c>
-      <x:c r="B4" s="41" t="s">
-        <x:v>838</x:v>
+      <x:c r="A4" s="41" t="str">
+        <x:v>kitabevi-2</x:v>
+      </x:c>
+      <x:c r="B4" s="41" t="str">
+        <x:v>Ortaokul</x:v>
       </x:c>
       <x:c r="C4" s="41"/>
-      <x:c r="D4" s="41" t="s">
-        <x:v>851</x:v>
-      </x:c>
-      <x:c r="E4" s="41" t="s">
-        <x:v>854</x:v>
-      </x:c>
-      <x:c r="F4" s="41" t="s">
-        <x:v>855</x:v>
-      </x:c>
-      <x:c r="G4" s="41" t="s">
-        <x:v>852</x:v>
-      </x:c>
-      <x:c r="H4" s="41">
+      <x:c r="D4" s="41" t="str">
+        <x:v>Ortaokul kitapları ve güncel fiyat listesi</x:v>
+      </x:c>
+      <x:c r="E4" s="41" t="str">
+        <x:v>#234E52</x:v>
+      </x:c>
+      <x:c r="F4" s="41" t="str">
+        <x:v>#F6C453</x:v>
+      </x:c>
+      <x:c r="G4" s="41" t="str">
+        <x:v>Evet</x:v>
+      </x:c>
+      <x:c r="H4" s="41" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I4" s="60"/>
+      <x:c r="I4" s="60" t="str">
+        <x:v>assets/logos/mega-kitabevi.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="41" t="s">
-        <x:v>842</x:v>
-      </x:c>
-      <x:c r="B5" s="41" t="s">
-        <x:v>846</x:v>
+      <x:c r="A5" s="41" t="str">
+        <x:v>kitabevi-2</x:v>
+      </x:c>
+      <x:c r="B5" s="41" t="str">
+        <x:v>Lise</x:v>
       </x:c>
       <x:c r="C5" s="41"/>
-      <x:c r="D5" s="41" t="s">
-        <x:v>853</x:v>
-      </x:c>
-      <x:c r="E5" s="41" t="s">
-        <x:v>854</x:v>
-      </x:c>
-      <x:c r="F5" s="41" t="s">
-        <x:v>855</x:v>
-      </x:c>
-      <x:c r="G5" s="41" t="s">
-        <x:v>852</x:v>
-      </x:c>
-      <x:c r="H5" s="41">
+      <x:c r="D5" s="41" t="str">
+        <x:v>Lise kitapları ve güncel fiyat listesi</x:v>
+      </x:c>
+      <x:c r="E5" s="41" t="str">
+        <x:v>#234E52</x:v>
+      </x:c>
+      <x:c r="F5" s="41" t="str">
+        <x:v>#F6C453</x:v>
+      </x:c>
+      <x:c r="G5" s="41" t="str">
+        <x:v>Evet</x:v>
+      </x:c>
+      <x:c r="H5" s="41" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I5" s="60"/>
+      <x:c r="I5" s="60" t="str">
+        <x:v>assets/logos/mega-kitabevi.png</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="27.950000762939453" customHeight="1">
       <x:c r="A6" s="41"/>
@@ -21575,7 +21559,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd506bcee5bb43ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf46de4659a614dd4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21599,13 +21583,13 @@
         <x:v>833</x:v>
       </x:c>
       <x:c r="C1" s="43" t="s">
-        <x:v>856</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="D1" s="43" t="s">
-        <x:v>857</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="E1" s="43" t="s">
-        <x:v>858</x:v>
+        <x:v>849</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26.100000381469727" customHeight="1">
@@ -21616,10 +21600,10 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="C2" s="40" t="s">
-        <x:v>859</x:v>
+        <x:v>850</x:v>
       </x:c>
       <x:c r="D2" s="44" t="s">
-        <x:v>860</x:v>
+        <x:v>851</x:v>
       </x:c>
       <x:c r="E2" s="40" t="s">
         <x:v>852</x:v>
@@ -21633,10 +21617,10 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="C3" s="41" t="s">
-        <x:v>861</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="D3" s="45" t="s">
-        <x:v>862</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="E3" s="41" t="s">
         <x:v>852</x:v>
@@ -21650,10 +21634,10 @@
         <x:v>846</x:v>
       </x:c>
       <x:c r="C4" s="40" t="s">
-        <x:v>859</x:v>
+        <x:v>850</x:v>
       </x:c>
       <x:c r="D4" s="44" t="s">
-        <x:v>860</x:v>
+        <x:v>851</x:v>
       </x:c>
       <x:c r="E4" s="41" t="s">
         <x:v>852</x:v>
@@ -21667,10 +21651,10 @@
         <x:v>846</x:v>
       </x:c>
       <x:c r="C5" s="41" t="s">
-        <x:v>861</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="D5" s="45" t="s">
-        <x:v>862</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="E5" s="41" t="s">
         <x:v>852</x:v>
@@ -21684,10 +21668,10 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="C6" s="41" t="s">
-        <x:v>863</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="D6" s="45" t="s">
-        <x:v>864</x:v>
+        <x:v>856</x:v>
       </x:c>
       <x:c r="E6" s="41" t="s">
         <x:v>852</x:v>
@@ -21714,10 +21698,10 @@
         <x:v>846</x:v>
       </x:c>
       <x:c r="C8" s="41" t="s">
-        <x:v>863</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="D8" s="45" t="s">
-        <x:v>864</x:v>
+        <x:v>856</x:v>
       </x:c>
       <x:c r="E8" s="41" t="s">
         <x:v>852</x:v>
@@ -21964,7 +21948,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58c8c73c88b34ddf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33d900a4f3514b2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/Fiyat-Listesi-Yonetim.xlsx
+++ b/output/Fiyat-Listesi-Yonetim.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ürünler" sheetId="1" r:id="Rb9dd5a23b66a45b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İndirimler" sheetId="2" r:id="R9262368db7854836"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasarım" sheetId="3" r:id="R775ad0901e7e4d08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kullanım" sheetId="4" r:id="Rebb04810d08b444c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ayarlar" sheetId="5" r:id="Rab84dffcb1dc4beb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayfa Ayarları" sheetId="6" r:id="Re1d4f43611cc4a01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İletişim" sheetId="7" r:id="Rcb48a92fe6cc48f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ürünler" sheetId="1" r:id="Rdbd497cab81f4766"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İndirimler" sheetId="2" r:id="Rdeca6853128843f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasarım" sheetId="3" r:id="Ra0511d50af9c4f94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kullanım" sheetId="4" r:id="R996a66dfab0c4b67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ayarlar" sheetId="5" r:id="R42e02c8ff9e94a68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayfa Ayarları" sheetId="6" r:id="R666c7c55ba99497f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İletişim" sheetId="7" r:id="Raf168619436e4b31"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2506,79 +2506,58 @@
     <x:t xml:space="preserve">Dosya GitHub'a yüklendiğinde web programı ve PDF otomatik yenilenir.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Sınıf Ayarları</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Kitabevi Listesi</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Yayınevi - Kitabevi Eşleştirmesi</x:t>
+    <x:t xml:space="preserve">7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yeni bir yayınevi ekleyip Güncelle düğmesine bastığınızda Ayarlar listesine otomatik eklenir. Karşısındaki Kitabevi Kodu'nu seçin.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Logo göstermek için Sayfa Ayarları sayfasındaki Logo Linki alanına doğrudan görsel bağlantısını yapıştırın.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kitabevi Kodu</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Kademe</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Kitabevi Kodu</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Kitabevi Adı</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Yayınevi</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">5. Sınıf</x:t>
+    <x:t xml:space="preserve">Ad Soyad</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Telefon</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">WhatsApp</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">kitabevi-1</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Ortaokul</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">kitabevi-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">İşer Kitabevi</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">6. Sınıf</x:t>
+    <x:t xml:space="preserve">Aytaç Arslan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">5345556747</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Evet</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Emre Arslan</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">5466779329</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lise</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">kitabevi-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Mega Kitabevi</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">7. Sınıf</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">8. Sınıf</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Lise</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ad Soyad</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Telefon</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WhatsApp</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Aytaç Arslan</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">5345556747</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Evet</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Emre Arslan</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">5466779329</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Furkan ÖZKAN</x:t>
@@ -2646,7 +2625,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="16">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -2701,11 +2680,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF2B134"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF4CC"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -2797,7 +2771,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="66">
+  <x:cellXfs count="55">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2920,13 +2894,16 @@
     <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2937,34 +2914,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -19060,60 +19009,60 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="Rf5868dd89b114609"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="R139e728302704965"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="R9d436fde78d847ef"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="Rd8980e6915fa48fe"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="R19ede4a5d10448b3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="Rd496114d2bd24d9a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="Reb1880f43a694ce6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="R9defe46981424341"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="R9f75206da06e41a3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="R77e803aa1f114c17"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="R9aaa654bcb524a1b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="R80e6cf0c9705469a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="R479e1e1130b64201"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="R606d0612f771420f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="Rf74ddffd193e43e0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="R37a87eba675940d3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="Rb76e57d610fe4af8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="Rddce47f265e24177"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="R535827b203c74fc6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="Rfe8781b183484799"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="R87c26f48771b475a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="Rd28f55383f4c43b5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="R37766e3ab8be4e0b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="R338ae189e6ce4ebd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="R05f3bb55c9d645f4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="R220e00d5b2fd4343"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="Rcc7ba72105774d5d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="Rb92eaffb5fd84575"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="R3737a0c6bc204ab3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="R251931cf7b114d91"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="R1dada3a02c224bf4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="R4fe669b275564fc2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="R7af2151606ea480c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="R5b8c448ed9ed4f68"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J324" r:id="R50796819c2ab4943"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="Rce65394aec5b4d3f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="Rd06211eecaef4aba"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="R6376df39372c43ff"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="R958d641523014cc4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="R850011debe614713"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="Rcc41b3dc65ff492f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="Rb50101c11e5c498e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="R674d6173b8b04fe2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="R7137ee80738b43e2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="Rb2d1fbbffb694e88"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="R677bf6eb7b3549a6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="R56a3c8d98b3d49d9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J439" r:id="R15dac2b878e247b3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="R1b6983c0ad7044df"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="Rb21da75fbbcf427e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="R9c25b7fc9ba04b8b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="Rc35f41db43904b65"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="R15121bc8272e4445"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="R0c4aa081762a4840"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="R5825bf036bd644b7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="R35c1d17b51554f63"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="R5fb3e2c7e3b74b4b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="Rd64f6c6552ff4c10"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="Rd1f517dbd2244ffb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="R261f4722a7264218"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="R32fb441d8b7f4376"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="R4e596ae772da4897"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="Re67af15ef7aa4095"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="R112e8a82d4824799"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="R0c272d30add241ee"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="R273e02cb07274204"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="R778b73da12864683"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="R0fcad0137ab9416c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="R4a866e3d62de4129"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="R558cc9c3211d441d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="Rc3ded1653a17486b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="R785663d842604955"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="R6c79ac8360fd487d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="Rdd8e9707cebe4cf9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="R163051eca9f54356"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="R2d94d485b14f439a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="R410697465a0e4e64"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="Rd9088c8f37f748a4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="R9203f6c6d0b046d5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="Rfa3b8b79ec9a4b75"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="Rdeac31759a884340"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="Rf154bf395ca94dc1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="R6b62c2d289004d2e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="Rce60f66630004022"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J324" r:id="R91f1a572b9ab4139"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="R44371b6fd936426f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="Re45cc429d0744e83"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="R3509699e1b0d4f34"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="R0682b8e219104b05"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="Rb66d5e8f78b44cd9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="R4b546eb8f610442c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="Ra42efcc00050457b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="Rd79703fe22b042d6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="R7a465e84a8b44926"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="R80ea31a41eb0494d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="Rae3473b411e94a88"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="R5d81b9c3355b4725"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J439" r:id="Rd0399517eaa24661"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="R20fcd5911be74c3c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="R957a40037e7f41aa"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb561f65cb6f64d04"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ca0f94852084e6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20677,7 +20626,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4d258532f4b4aec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ec948967a424468"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20739,19 +20688,19 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="82" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" customWidth="1"/>
+    <x:col min="2" max="2" width="82" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="51" t="s">
+      <x:c r="A1" s="52" t="s">
         <x:v>816</x:v>
       </x:c>
-      <x:c r="B1" s="51"/>
-      <x:c r="C1" s="51"/>
-      <x:c r="D1" s="51"/>
-      <x:c r="E1" s="51"/>
-      <x:c r="F1" s="51"/>
+      <x:c r="B1" s="52"/>
+      <x:c r="C1" s="52"/>
+      <x:c r="D1" s="52"/>
+      <x:c r="E1" s="52"/>
+      <x:c r="F1" s="52"/>
     </x:row>
     <x:row r="3" ht="33.95000076293945" customHeight="1">
       <x:c r="A3" s="26" t="s">
@@ -20807,20 +20756,20 @@
         <x:v>829</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="40" customHeight="1">
-      <x:c r="A10" s="27" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B10" s="27" t="str">
-        <x:v>Yeni bir yayınevi ekleyip Güncelle düğmesine bastığınızda Ayarlar listesine otomatik eklenir. Karşısındaki Kitabevi Kodu'nu seçin.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="40" customHeight="1">
-      <x:c r="A11" s="27" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B11" s="27" t="str">
-        <x:v>Logo göstermek için Sayfa Ayarları sayfasındaki Logo Linki alanına doğrudan görsel bağlantısını yapıştırın.</x:v>
+    <x:row r="10" ht="39.95000076293945" customHeight="1">
+      <x:c r="A10" s="27" t="s">
+        <x:v>830</x:v>
+      </x:c>
+      <x:c r="B10" s="27" t="s">
+        <x:v>831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="39.95000076293945" customHeight="1">
+      <x:c r="A11" s="27" t="s">
+        <x:v>832</x:v>
+      </x:c>
+      <x:c r="B11" s="27" t="s">
+        <x:v>833</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -20843,389 +20792,542 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32.099998474121094" customHeight="1">
-      <x:c r="A1" s="52" t="s">
-        <x:v>830</x:v>
-      </x:c>
-      <x:c r="B1" s="52"/>
-      <x:c r="D1" s="52" t="s">
-        <x:v>831</x:v>
-      </x:c>
-      <x:c r="E1" s="52"/>
-      <x:c r="G1" s="53" t="s">
-        <x:v>832</x:v>
-      </x:c>
-      <x:c r="H1" s="53"/>
-    </x:row>
-    <x:row r="2" ht="24" customHeight="1"/>
+      <x:c r="A1" s="53" t="str">
+        <x:v>Sınıf Ayarları</x:v>
+      </x:c>
+      <x:c r="B1" s="53"/>
+      <x:c r="C1"/>
+      <x:c r="D1" s="53" t="str">
+        <x:v>Kitabevi Listesi</x:v>
+      </x:c>
+      <x:c r="E1" s="53"/>
+      <x:c r="F1"/>
+      <x:c r="G1" s="54" t="str">
+        <x:v>Yayınevi - Kitabevi Eşleştirmesi</x:v>
+      </x:c>
+      <x:c r="H1" s="54"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+    </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="32" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="32" t="s">
-        <x:v>833</x:v>
-      </x:c>
-      <x:c r="D3" s="32" t="s">
-        <x:v>834</x:v>
-      </x:c>
-      <x:c r="E3" s="32" t="s">
-        <x:v>835</x:v>
-      </x:c>
-      <x:c r="G3" s="47" t="s">
-        <x:v>836</x:v>
-      </x:c>
-      <x:c r="H3" s="47" t="s">
-        <x:v>834</x:v>
+      <x:c r="A3" s="32" t="str">
+        <x:v>Sınıf</x:v>
+      </x:c>
+      <x:c r="B3" s="32" t="str">
+        <x:v>Kademe</x:v>
+      </x:c>
+      <x:c r="C3"/>
+      <x:c r="D3" s="32" t="str">
+        <x:v>Kitabevi Kodu</x:v>
+      </x:c>
+      <x:c r="E3" s="32" t="str">
+        <x:v>Kitabevi Adı</x:v>
+      </x:c>
+      <x:c r="F3"/>
+      <x:c r="G3" s="47" t="str">
+        <x:v>Yayınevi</x:v>
+      </x:c>
+      <x:c r="H3" s="47" t="str">
+        <x:v>Kitabevi Kodu</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="33" t="s">
-        <x:v>837</x:v>
-      </x:c>
-      <x:c r="B4" s="33" t="s">
-        <x:v>838</x:v>
-      </x:c>
-      <x:c r="D4" s="36" t="s">
-        <x:v>839</x:v>
-      </x:c>
-      <x:c r="E4" s="36" t="s">
-        <x:v>840</x:v>
-      </x:c>
+      <x:c r="A4" s="33" t="str">
+        <x:v>5. Sınıf</x:v>
+      </x:c>
+      <x:c r="B4" s="33" t="str">
+        <x:v>Ortaokul</x:v>
+      </x:c>
+      <x:c r="C4"/>
+      <x:c r="D4" s="36" t="str">
+        <x:v>kitabevi-1</x:v>
+      </x:c>
+      <x:c r="E4" s="36" t="str">
+        <x:v>İşler Kitabevi</x:v>
+      </x:c>
+      <x:c r="F4"/>
       <x:c r="G4" s="3" t="str">
         <x:v>4K</x:v>
       </x:c>
-      <x:c r="H4" s="64" t="str">
+      <x:c r="H4" s="50" t="str">
         <x:v>kitabevi-2</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="34" t="s">
-        <x:v>841</x:v>
-      </x:c>
-      <x:c r="B5" s="34" t="s">
-        <x:v>838</x:v>
-      </x:c>
-      <x:c r="D5" s="37" t="s">
-        <x:v>842</x:v>
-      </x:c>
-      <x:c r="E5" s="37" t="s">
-        <x:v>843</x:v>
-      </x:c>
+      <x:c r="A5" s="34" t="str">
+        <x:v>6. Sınıf</x:v>
+      </x:c>
+      <x:c r="B5" s="34" t="str">
+        <x:v>Ortaokul</x:v>
+      </x:c>
+      <x:c r="C5"/>
+      <x:c r="D5" s="37" t="str">
+        <x:v>kitabevi-2</x:v>
+      </x:c>
+      <x:c r="E5" s="37" t="str">
+        <x:v>Mega Kitabevi</x:v>
+      </x:c>
+      <x:c r="F5"/>
       <x:c r="G5" s="4" t="str">
         <x:v>Acil Yayınları</x:v>
       </x:c>
-      <x:c r="H5" s="65" t="str">
+      <x:c r="H5" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="34" t="s">
-        <x:v>844</x:v>
-      </x:c>
-      <x:c r="B6" s="34" t="s">
-        <x:v>838</x:v>
-      </x:c>
+      <x:c r="A6" s="34" t="str">
+        <x:v>7. Sınıf</x:v>
+      </x:c>
+      <x:c r="B6" s="34" t="str">
+        <x:v>Ortaokul</x:v>
+      </x:c>
+      <x:c r="C6"/>
       <x:c r="D6" s="37"/>
       <x:c r="E6" s="37"/>
+      <x:c r="F6"/>
       <x:c r="G6" s="4" t="str">
         <x:v>Aktif Öğrenme Yayınları</x:v>
       </x:c>
-      <x:c r="H6" s="65" t="str">
+      <x:c r="H6" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="34" t="s">
-        <x:v>845</x:v>
-      </x:c>
-      <x:c r="B7" s="34" t="s">
-        <x:v>838</x:v>
-      </x:c>
+      <x:c r="A7" s="34" t="str">
+        <x:v>8. Sınıf</x:v>
+      </x:c>
+      <x:c r="B7" s="34" t="str">
+        <x:v>Ortaokul</x:v>
+      </x:c>
+      <x:c r="C7"/>
       <x:c r="D7" s="37"/>
       <x:c r="E7" s="37"/>
+      <x:c r="F7"/>
       <x:c r="G7" s="4" t="str">
         <x:v>Alan Yayınları</x:v>
       </x:c>
-      <x:c r="H7" s="65" t="str">
+      <x:c r="H7" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
-      <x:c r="A8" s="34" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B8" s="34" t="s">
-        <x:v>846</x:v>
-      </x:c>
+      <x:c r="A8" s="34" t="str">
+        <x:v>9. Sınıf</x:v>
+      </x:c>
+      <x:c r="B8" s="34" t="str">
+        <x:v>Lise</x:v>
+      </x:c>
+      <x:c r="C8"/>
       <x:c r="D8" s="37"/>
       <x:c r="E8" s="37"/>
+      <x:c r="F8"/>
       <x:c r="G8" s="4" t="str">
         <x:v>Apotemi Yayınları</x:v>
       </x:c>
-      <x:c r="H8" s="65" t="str">
+      <x:c r="H8" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
-      <x:c r="A9" s="34" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B9" s="34" t="s">
-        <x:v>846</x:v>
-      </x:c>
+      <x:c r="A9" s="34" t="str">
+        <x:v>10. Sınıf</x:v>
+      </x:c>
+      <x:c r="B9" s="34" t="str">
+        <x:v>Lise</x:v>
+      </x:c>
+      <x:c r="C9"/>
       <x:c r="D9" s="37"/>
       <x:c r="E9" s="37"/>
+      <x:c r="F9"/>
       <x:c r="G9" s="4" t="str">
         <x:v>Aydın</x:v>
       </x:c>
-      <x:c r="H9" s="65" t="str">
+      <x:c r="H9" s="51" t="str">
         <x:v>kitabevi-2</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="34" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B10" s="34" t="s">
-        <x:v>846</x:v>
-      </x:c>
+      <x:c r="A10" s="34" t="str">
+        <x:v>11. Sınıf</x:v>
+      </x:c>
+      <x:c r="B10" s="34" t="str">
+        <x:v>Lise</x:v>
+      </x:c>
+      <x:c r="C10"/>
       <x:c r="D10" s="37"/>
       <x:c r="E10" s="37"/>
+      <x:c r="F10"/>
       <x:c r="G10" s="4" t="str">
         <x:v>Bilgi Arşivi Yayınları</x:v>
       </x:c>
-      <x:c r="H10" s="65" t="str">
+      <x:c r="H10" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="34" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="B11" s="34" t="s">
-        <x:v>846</x:v>
-      </x:c>
+      <x:c r="A11" s="34" t="str">
+        <x:v>12. Sınıf</x:v>
+      </x:c>
+      <x:c r="B11" s="34" t="str">
+        <x:v>Lise</x:v>
+      </x:c>
+      <x:c r="C11"/>
       <x:c r="D11" s="37"/>
       <x:c r="E11" s="37"/>
+      <x:c r="F11"/>
       <x:c r="G11" s="4" t="str">
         <x:v>Bilgi Sarmal Yayınları</x:v>
       </x:c>
-      <x:c r="H11" s="65" t="str">
+      <x:c r="H11" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="35" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B12" s="35" t="s">
-        <x:v>846</x:v>
-      </x:c>
+      <x:c r="A12" s="35" t="str">
+        <x:v>Maarif TYT</x:v>
+      </x:c>
+      <x:c r="B12" s="35" t="str">
+        <x:v>Lise</x:v>
+      </x:c>
+      <x:c r="C12"/>
       <x:c r="D12" s="37"/>
       <x:c r="E12" s="37"/>
+      <x:c r="F12"/>
       <x:c r="G12" s="4" t="str">
         <x:v>Biyotik Yayınları</x:v>
       </x:c>
-      <x:c r="H12" s="65" t="str">
+      <x:c r="H12" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
       <x:c r="D13" s="37"/>
       <x:c r="E13" s="37"/>
+      <x:c r="F13"/>
       <x:c r="G13" s="4" t="str">
         <x:v>Coğrafya Gurmesi Yayınları</x:v>
       </x:c>
-      <x:c r="H13" s="65" t="str">
+      <x:c r="H13" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
       <x:c r="D14" s="37"/>
       <x:c r="E14" s="37"/>
+      <x:c r="F14"/>
       <x:c r="G14" s="4" t="str">
         <x:v>Çap Yayınları</x:v>
       </x:c>
-      <x:c r="H14" s="65" t="str">
+      <x:c r="H14" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
       <x:c r="D15" s="37"/>
       <x:c r="E15" s="37"/>
+      <x:c r="F15"/>
       <x:c r="G15" s="4" t="str">
         <x:v>Edebiyat Sokağı Yayınları</x:v>
       </x:c>
-      <x:c r="H15" s="65" t="str">
+      <x:c r="H15" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
       <x:c r="D16" s="37"/>
       <x:c r="E16" s="37"/>
+      <x:c r="F16"/>
       <x:c r="G16" s="4" t="str">
         <x:v>Egzersiz Yayınları</x:v>
       </x:c>
-      <x:c r="H16" s="65" t="str">
+      <x:c r="H16" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
       <x:c r="D17" s="37"/>
       <x:c r="E17" s="37"/>
+      <x:c r="F17"/>
       <x:c r="G17" s="4" t="str">
         <x:v>Eğitim Vadisi</x:v>
       </x:c>
-      <x:c r="H17" s="65" t="str">
+      <x:c r="H17" s="51" t="str">
         <x:v>kitabevi-2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
       <x:c r="D18" s="37"/>
       <x:c r="E18" s="37"/>
+      <x:c r="F18"/>
       <x:c r="G18" s="4" t="str">
         <x:v>ENS Yayınları</x:v>
       </x:c>
-      <x:c r="H18" s="65" t="str">
+      <x:c r="H18" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
       <x:c r="D19" s="37"/>
       <x:c r="E19" s="37"/>
+      <x:c r="F19"/>
       <x:c r="G19" s="4" t="str">
         <x:v>Etkili Matematik Yayınları</x:v>
       </x:c>
-      <x:c r="H19" s="65" t="str">
+      <x:c r="H19" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
       <x:c r="D20" s="38"/>
       <x:c r="E20" s="38"/>
+      <x:c r="F20"/>
       <x:c r="G20" s="4" t="str">
         <x:v>Fizik Pedia Yayınları</x:v>
       </x:c>
-      <x:c r="H20" s="65" t="str">
+      <x:c r="H20" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
       <x:c r="G21" s="4" t="str">
         <x:v>Full Matematik Yayınları</x:v>
       </x:c>
-      <x:c r="H21" s="65" t="str">
+      <x:c r="H21" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
       <x:c r="G22" s="4" t="str">
         <x:v>Hız ve Renk Yayınları</x:v>
       </x:c>
-      <x:c r="H22" s="65" t="str">
+      <x:c r="H22" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
       <x:c r="G23" s="4" t="str">
         <x:v>Limit</x:v>
       </x:c>
-      <x:c r="H23" s="65" t="str">
+      <x:c r="H23" s="51" t="str">
         <x:v>kitabevi-2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
       <x:c r="G24" s="4" t="str">
         <x:v>Mikro Orijinal Yayınları</x:v>
       </x:c>
-      <x:c r="H24" s="65" t="str">
+      <x:c r="H24" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
       <x:c r="G25" s="4" t="str">
         <x:v>Miray</x:v>
       </x:c>
-      <x:c r="H25" s="65" t="str">
+      <x:c r="H25" s="51" t="str">
         <x:v>kitabevi-2</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
       <x:c r="G26" s="4" t="str">
         <x:v>Oktet Yayınları</x:v>
       </x:c>
-      <x:c r="H26" s="65" t="str">
+      <x:c r="H26" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
       <x:c r="G27" s="4" t="str">
         <x:v>Orbital Yayınları</x:v>
       </x:c>
-      <x:c r="H27" s="65" t="str">
+      <x:c r="H27" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
       <x:c r="G28" s="4" t="str">
         <x:v>Orijinal Matematik Yayınları</x:v>
       </x:c>
-      <x:c r="H28" s="65" t="str">
+      <x:c r="H28" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
       <x:c r="G29" s="4" t="str">
         <x:v>Profizik</x:v>
       </x:c>
-      <x:c r="H29" s="65" t="str">
+      <x:c r="H29" s="51" t="str">
         <x:v>kitabevi-2</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
       <x:c r="G30" s="4" t="str">
         <x:v>Rehber Matematik Yayınları</x:v>
       </x:c>
-      <x:c r="H30" s="65" t="str">
+      <x:c r="H30" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
       <x:c r="G31" s="4" t="str">
         <x:v>Ritim Biyoloji Yayınları</x:v>
       </x:c>
-      <x:c r="H31" s="65" t="str">
+      <x:c r="H31" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
       <x:c r="G32" s="4" t="str">
         <x:v>Süre Yayınları</x:v>
       </x:c>
-      <x:c r="H32" s="65" t="str">
+      <x:c r="H32" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
       <x:c r="G33" s="4" t="str">
         <x:v>Ulti Yayınları</x:v>
       </x:c>
-      <x:c r="H33" s="65" t="str">
+      <x:c r="H33" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
       <x:c r="G34" s="4" t="str">
         <x:v>Viral Yayınları</x:v>
       </x:c>
-      <x:c r="H34" s="65" t="str">
+      <x:c r="H34" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
       <x:c r="G35" s="4" t="str">
         <x:v>Yarıçap Yayınları</x:v>
       </x:c>
-      <x:c r="H35" s="65" t="str">
+      <x:c r="H35" s="51" t="str">
         <x:v>kitabevi-1</x:v>
       </x:c>
     </x:row>
@@ -21242,8 +21344,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4389774e21894828"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a07e837b7ed414a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R781cc4c197b74aa3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15d5d0827bc0428c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21258,7 +21360,7 @@
     <x:col min="4" max="4" width="52" customWidth="1"/>
     <x:col min="5" max="6" width="16" customWidth="1"/>
     <x:col min="7" max="8" width="17" customWidth="1"/>
-    <x:col min="9" max="9" width="46" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="46" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -21286,7 +21388,7 @@
       <x:c r="H1" s="39" t="str">
         <x:v>Ana Sayfa Sırası</x:v>
       </x:c>
-      <x:c r="I1" s="57" t="str">
+      <x:c r="I1" s="48" t="str">
         <x:v>Logo Linki</x:v>
       </x:c>
     </x:row>
@@ -21302,7 +21404,7 @@
         <x:v>Ortaokul kitapları ve güncel fiyat listesi</x:v>
       </x:c>
       <x:c r="E2" s="40" t="str">
-        <x:v>#173F5F</x:v>
+        <x:v>#8B1E2D</x:v>
       </x:c>
       <x:c r="F2" s="40" t="str">
         <x:v>#F2B134</x:v>
@@ -21313,7 +21415,7 @@
       <x:c r="H2" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I2" s="60" t="str">
+      <x:c r="I2" s="49" t="str">
         <x:v>assets/logos/isler-kitabevi.png</x:v>
       </x:c>
     </x:row>
@@ -21329,7 +21431,7 @@
         <x:v>Lise kitapları ve güncel fiyat listesi</x:v>
       </x:c>
       <x:c r="E3" s="41" t="str">
-        <x:v>#173F5F</x:v>
+        <x:v>#8B1E2D</x:v>
       </x:c>
       <x:c r="F3" s="41" t="str">
         <x:v>#F2B134</x:v>
@@ -21340,7 +21442,7 @@
       <x:c r="H3" s="41" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I3" s="60" t="str">
+      <x:c r="I3" s="49" t="str">
         <x:v>assets/logos/isler-kitabevi.png</x:v>
       </x:c>
     </x:row>
@@ -21367,7 +21469,7 @@
       <x:c r="H4" s="41" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I4" s="60" t="str">
+      <x:c r="I4" s="49" t="str">
         <x:v>assets/logos/mega-kitabevi.png</x:v>
       </x:c>
     </x:row>
@@ -21394,7 +21496,7 @@
       <x:c r="H5" s="41" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I5" s="60" t="str">
+      <x:c r="I5" s="49" t="str">
         <x:v>assets/logos/mega-kitabevi.png</x:v>
       </x:c>
     </x:row>
@@ -21559,7 +21661,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf46de4659a614dd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R295d7b50697848cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21580,16 +21682,16 @@
         <x:v>834</x:v>
       </x:c>
       <x:c r="B1" s="43" t="s">
-        <x:v>833</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C1" s="43" t="s">
-        <x:v>847</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="D1" s="43" t="s">
-        <x:v>848</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="E1" s="43" t="s">
-        <x:v>849</x:v>
+        <x:v>838</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="26.100000381469727" customHeight="1">
@@ -21597,16 +21699,16 @@
         <x:v>839</x:v>
       </x:c>
       <x:c r="B2" s="40" t="s">
-        <x:v>838</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="C2" s="40" t="s">
-        <x:v>850</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="D2" s="44" t="s">
-        <x:v>851</x:v>
+        <x:v>842</x:v>
       </x:c>
       <x:c r="E2" s="40" t="s">
-        <x:v>852</x:v>
+        <x:v>843</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="26.100000381469727" customHeight="1">
@@ -21614,16 +21716,16 @@
         <x:v>839</x:v>
       </x:c>
       <x:c r="B3" s="41" t="s">
-        <x:v>838</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="C3" s="41" t="s">
-        <x:v>853</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="D3" s="45" t="s">
-        <x:v>854</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="E3" s="41" t="s">
-        <x:v>852</x:v>
+        <x:v>843</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26.100000381469727" customHeight="1">
@@ -21634,13 +21736,13 @@
         <x:v>846</x:v>
       </x:c>
       <x:c r="C4" s="40" t="s">
-        <x:v>850</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="D4" s="44" t="s">
-        <x:v>851</x:v>
+        <x:v>842</x:v>
       </x:c>
       <x:c r="E4" s="41" t="s">
-        <x:v>852</x:v>
+        <x:v>843</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="26.100000381469727" customHeight="1">
@@ -21651,65 +21753,65 @@
         <x:v>846</x:v>
       </x:c>
       <x:c r="C5" s="41" t="s">
-        <x:v>853</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="D5" s="45" t="s">
-        <x:v>854</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="E5" s="41" t="s">
-        <x:v>852</x:v>
+        <x:v>843</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.100000381469727" customHeight="1">
       <x:c r="A6" s="41" t="s">
-        <x:v>842</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="B6" s="41" t="s">
-        <x:v>838</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="C6" s="41" t="s">
-        <x:v>855</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="D6" s="45" t="s">
-        <x:v>856</x:v>
+        <x:v>849</x:v>
       </x:c>
       <x:c r="E6" s="41" t="s">
-        <x:v>852</x:v>
+        <x:v>843</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.100000381469727" customHeight="1">
       <x:c r="A7" s="41" t="s">
-        <x:v>842</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="B7" s="41" t="s">
-        <x:v>838</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="C7" s="41"/>
       <x:c r="D7" s="45"/>
       <x:c r="E7" s="41" t="s">
-        <x:v>852</x:v>
+        <x:v>843</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="26.100000381469727" customHeight="1">
       <x:c r="A8" s="41" t="s">
-        <x:v>842</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="B8" s="41" t="s">
         <x:v>846</x:v>
       </x:c>
       <x:c r="C8" s="41" t="s">
-        <x:v>855</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="D8" s="45" t="s">
-        <x:v>856</x:v>
+        <x:v>849</x:v>
       </x:c>
       <x:c r="E8" s="41" t="s">
-        <x:v>852</x:v>
+        <x:v>843</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26.100000381469727" customHeight="1">
       <x:c r="A9" s="41" t="s">
-        <x:v>842</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="B9" s="41" t="s">
         <x:v>846</x:v>
@@ -21717,7 +21819,7 @@
       <x:c r="C9" s="41"/>
       <x:c r="D9" s="45"/>
       <x:c r="E9" s="41" t="s">
-        <x:v>852</x:v>
+        <x:v>843</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="26.100000381469727" customHeight="1">
@@ -21948,7 +22050,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33d900a4f3514b2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebb88dbe0dbf4696"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/Fiyat-Listesi-Yonetim.xlsx
+++ b/output/Fiyat-Listesi-Yonetim.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ürünler" sheetId="1" r:id="Rdbd497cab81f4766"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İndirimler" sheetId="2" r:id="Rdeca6853128843f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasarım" sheetId="3" r:id="Ra0511d50af9c4f94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kullanım" sheetId="4" r:id="R996a66dfab0c4b67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ayarlar" sheetId="5" r:id="R42e02c8ff9e94a68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayfa Ayarları" sheetId="6" r:id="R666c7c55ba99497f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İletişim" sheetId="7" r:id="Raf168619436e4b31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ürünler" sheetId="1" r:id="R3ae31ddbde894f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İndirimler" sheetId="2" r:id="R320adc1706574c7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasarım" sheetId="3" r:id="R7663e8f2e5cf4a94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kullanım" sheetId="4" r:id="R2bc3fb719c954739"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ayarlar" sheetId="5" r:id="R71fc2aea5c764a63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayfa Ayarları" sheetId="6" r:id="R9ea8b890059247f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İletişim" sheetId="7" r:id="Rd9b6d26d5dd740c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19009,60 +19009,60 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="R9c25b7fc9ba04b8b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="Rc35f41db43904b65"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="R15121bc8272e4445"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="R0c4aa081762a4840"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="R5825bf036bd644b7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="R35c1d17b51554f63"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="R5fb3e2c7e3b74b4b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="Rd64f6c6552ff4c10"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="Rd1f517dbd2244ffb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="R261f4722a7264218"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="R32fb441d8b7f4376"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="R4e596ae772da4897"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="Re67af15ef7aa4095"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="R112e8a82d4824799"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="R0c272d30add241ee"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="R273e02cb07274204"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="R778b73da12864683"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="R0fcad0137ab9416c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="R4a866e3d62de4129"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="R558cc9c3211d441d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="Rc3ded1653a17486b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="R785663d842604955"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="R6c79ac8360fd487d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="Rdd8e9707cebe4cf9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="R163051eca9f54356"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="R2d94d485b14f439a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="R410697465a0e4e64"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="Rd9088c8f37f748a4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="R9203f6c6d0b046d5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="Rfa3b8b79ec9a4b75"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="Rdeac31759a884340"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="Rf154bf395ca94dc1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="R6b62c2d289004d2e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="Rce60f66630004022"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J324" r:id="R91f1a572b9ab4139"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="R44371b6fd936426f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="Re45cc429d0744e83"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="R3509699e1b0d4f34"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="R0682b8e219104b05"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="Rb66d5e8f78b44cd9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="R4b546eb8f610442c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="Ra42efcc00050457b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="Rd79703fe22b042d6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="R7a465e84a8b44926"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="R80ea31a41eb0494d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="Rae3473b411e94a88"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="R5d81b9c3355b4725"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J439" r:id="Rd0399517eaa24661"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="R20fcd5911be74c3c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="R957a40037e7f41aa"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="Rd8fc043c275f4faa"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="R2561cc4ee1594b65"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="Rb2aceca866fa4fe8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="Rce6e3fe5f05b43dd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="Rff7660c4bd644334"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="Rcb7ee03f6a3c413e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="Rff010bb958ac47c4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="R25104c90ea1f428a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="R67ccf0d21d77419c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="Rfa9ff748d62e4404"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="Rb3d05134ff0c41d0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="R7cd52b9a4e404342"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="Re1e257ef89f947c8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="R088731e22c7d4c12"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="Ra0316cd905e4447c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="R9697e3ad6c6d401b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="R238159b02fe84cd6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="R7e0c49203b244d64"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="R936e89cb65e24a3c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="R1e715b7fd5614bc5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="Rb34ce3853f214e21"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="Rfed8911ecd0a4a90"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="Ra6825685fab64d3a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="R3e9d6edc76da4e5c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="R36aa12ff38ee4b52"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="R2a4c1e0ac032479f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="R30bba635fc6145ca"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="Rfe5dd124df124fc7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="R0549a48388254140"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="Re3d0d94a50e34078"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="R1e49bcd5f91544b5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="R0329512bb9544b59"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="R95ef9c7fa454440b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="R925cb52d62b64aad"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J324" r:id="R065d3c25985b4c3b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="Rc1b79a89a4b0488d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="R4c1bb36bfb6e4dd2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="Reabce9a2992c4025"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="R4c08202f34934bef"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="R9f835619f0674099"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="Rb6dd3e4394c544c0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="R0a8534a3af414a65"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="R06909328d0074b01"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="Rfc8ae3dae2e44a10"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="R16949d0edaaf4d8c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="R5ff4137e468243e6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="R7989af1fc5bf4e95"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J439" r:id="R3941217fbba64707"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="R340e7b7de94e409a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="R0f2c4c02059b40f8"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ca0f94852084e6a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra64380c6a9834c43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20626,7 +20626,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ec948967a424468"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b87a4137a1b4dcc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21344,8 +21344,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R781cc4c197b74aa3"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15d5d0827bc0428c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf18931f488434aef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R058eb3f5690348f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21458,10 +21458,10 @@
         <x:v>Ortaokul kitapları ve güncel fiyat listesi</x:v>
       </x:c>
       <x:c r="E4" s="41" t="str">
-        <x:v>#234E52</x:v>
+        <x:v>#211F20</x:v>
       </x:c>
       <x:c r="F4" s="41" t="str">
-        <x:v>#F6C453</x:v>
+        <x:v>#F6B500</x:v>
       </x:c>
       <x:c r="G4" s="41" t="str">
         <x:v>Evet</x:v>
@@ -21485,10 +21485,10 @@
         <x:v>Lise kitapları ve güncel fiyat listesi</x:v>
       </x:c>
       <x:c r="E5" s="41" t="str">
-        <x:v>#234E52</x:v>
+        <x:v>#211F20</x:v>
       </x:c>
       <x:c r="F5" s="41" t="str">
-        <x:v>#F6C453</x:v>
+        <x:v>#F6B500</x:v>
       </x:c>
       <x:c r="G5" s="41" t="str">
         <x:v>Evet</x:v>
@@ -21661,7 +21661,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R295d7b50697848cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d1b5c0df7cf42ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22050,7 +22050,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebb88dbe0dbf4696"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fc827c749ae4f5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/Fiyat-Listesi-Yonetim.xlsx
+++ b/output/Fiyat-Listesi-Yonetim.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ürünler" sheetId="1" r:id="R3ae31ddbde894f24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İndirimler" sheetId="2" r:id="R320adc1706574c7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasarım" sheetId="3" r:id="R7663e8f2e5cf4a94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kullanım" sheetId="4" r:id="R2bc3fb719c954739"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ayarlar" sheetId="5" r:id="R71fc2aea5c764a63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayfa Ayarları" sheetId="6" r:id="R9ea8b890059247f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İletişim" sheetId="7" r:id="Rd9b6d26d5dd740c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ürünler" sheetId="1" r:id="R5da03a1f94064d93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İndirimler" sheetId="2" r:id="R280de119b2ef4dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasarım" sheetId="3" r:id="Re076a537326a4e13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kullanım" sheetId="4" r:id="Ra9b9c9a01a124e4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ayarlar" sheetId="5" r:id="R5e2293e460704ad2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayfa Ayarları" sheetId="6" r:id="Rea7644fd068e40de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İletişim" sheetId="7" r:id="Ra3cbeeadadf34d3a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2625,7 +2625,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -2690,6 +2690,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF4CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF173F5F"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -2771,7 +2781,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="55">
+  <x:cellXfs count="61">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2915,6 +2925,18 @@
     <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Köprü" xfId="1"/>
@@ -19009,60 +19031,60 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="Rd8fc043c275f4faa"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="R2561cc4ee1594b65"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="Rb2aceca866fa4fe8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="Rce6e3fe5f05b43dd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="Rff7660c4bd644334"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="Rcb7ee03f6a3c413e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="Rff010bb958ac47c4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="R25104c90ea1f428a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="R67ccf0d21d77419c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="Rfa9ff748d62e4404"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="Rb3d05134ff0c41d0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="R7cd52b9a4e404342"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="Re1e257ef89f947c8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="R088731e22c7d4c12"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="Ra0316cd905e4447c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="R9697e3ad6c6d401b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="R238159b02fe84cd6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="R7e0c49203b244d64"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="R936e89cb65e24a3c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="R1e715b7fd5614bc5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="Rb34ce3853f214e21"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="Rfed8911ecd0a4a90"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="Ra6825685fab64d3a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="R3e9d6edc76da4e5c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="R36aa12ff38ee4b52"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="R2a4c1e0ac032479f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="R30bba635fc6145ca"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="Rfe5dd124df124fc7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="R0549a48388254140"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="Re3d0d94a50e34078"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="R1e49bcd5f91544b5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="R0329512bb9544b59"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="R95ef9c7fa454440b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="R925cb52d62b64aad"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J324" r:id="R065d3c25985b4c3b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="Rc1b79a89a4b0488d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="R4c1bb36bfb6e4dd2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="Reabce9a2992c4025"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="R4c08202f34934bef"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="R9f835619f0674099"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="Rb6dd3e4394c544c0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="R0a8534a3af414a65"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="R06909328d0074b01"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="Rfc8ae3dae2e44a10"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="R16949d0edaaf4d8c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="R5ff4137e468243e6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="R7989af1fc5bf4e95"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J439" r:id="R3941217fbba64707"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="R340e7b7de94e409a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="R0f2c4c02059b40f8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="Ra8b67e8a81354fd7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="R8c5cf00ff194490e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="R725be37277c543f3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="Ra593d1ddc2fc4882"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="R6509f43898a04599"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="R215bf2246fd841bd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="R4c04e84133a94f8b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="Rbb2734d666d543df"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="R9e50211ab0cb4730"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="R2e678d0f34bb4a1b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="R8c76c90be3034c77"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="Ra2a6a84574f343f0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="R24153d84382a41c0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="R635ae4f039c9487f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="Redb89279cd0e485c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="Rdbb00d72b4c84839"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="Re83fc8638c124ce1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="Rd1ccfb348218407e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="Re0a6ea2c8e54482e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="Rf313729fe30e4795"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="R46ebd285693e4d75"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="Rba62afe623364400"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="R626d8dbed8eb40c1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="R87d62b242cdc486e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="R4e548c3690be4ebc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="R6a04c76cbbc941e2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="R3c7123c9e44144bc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="Rf73cd085d5ba43fd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="R8386705a60ca4889"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="R5e74deb9eea44f86"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="R9537430d9bca428d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="R8151916a3e244916"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="R0b2e0e1d5f104d82"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="R5c6601b0895b41e5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J324" r:id="Rb8a8df9a658947c8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="Reb6a853e1e4742ef"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="R4d4bf19c2c5b4ca3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="R120c72a0715446ad"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="R204f8e6cf97a46c5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="R689aae3ee0324e46"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="Re74a224ed1624358"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="R2f45e80e886d442b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="Rd28b7aede8f64e8c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="Rc56d741c5c964a2f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="Rd14db475bb504c0d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="R1550de81fb724024"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="R993139d7d9184734"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J439" r:id="Re611f794205c4f87"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="R749489d8afa04074"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="Rc72dc4c170b94d2a"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra64380c6a9834c43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb2340301db948f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20626,7 +20648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b87a4137a1b4dcc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd100b30ec8fc4ed8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21344,8 +21366,8 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf18931f488434aef"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R058eb3f5690348f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43b3f84bf12d4d25"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa22a70df890427e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21361,6 +21383,7 @@
     <x:col min="5" max="6" width="16" customWidth="1"/>
     <x:col min="7" max="8" width="17" customWidth="1"/>
     <x:col min="9" max="9" width="46" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -21391,6 +21414,9 @@
       <x:c r="I1" s="48" t="str">
         <x:v>Logo Linki</x:v>
       </x:c>
+      <x:c r="J1" s="59" t="str">
+        <x:v>Gösterilecek Diğer Liste</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="40" t="str">
@@ -21418,6 +21444,9 @@
       <x:c r="I2" s="49" t="str">
         <x:v>assets/logos/isler-kitabevi.png</x:v>
       </x:c>
+      <x:c r="J2" s="60" t="str">
+        <x:v>kitabevi-2 | Ortaokul</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="41" t="str">
@@ -21445,6 +21474,9 @@
       <x:c r="I3" s="49" t="str">
         <x:v>assets/logos/isler-kitabevi.png</x:v>
       </x:c>
+      <x:c r="J3" s="60" t="str">
+        <x:v>kitabevi-2 | Lise</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="41" t="str">
@@ -21472,6 +21504,9 @@
       <x:c r="I4" s="49" t="str">
         <x:v>assets/logos/mega-kitabevi.png</x:v>
       </x:c>
+      <x:c r="J4" s="60" t="str">
+        <x:v>kitabevi-1 | Ortaokul</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="41" t="str">
@@ -21498,6 +21533,9 @@
       </x:c>
       <x:c r="I5" s="49" t="str">
         <x:v>assets/logos/mega-kitabevi.png</x:v>
+      </x:c>
+      <x:c r="J5" s="60" t="str">
+        <x:v>kitabevi-1 | Lise</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="27.950000762939453" customHeight="1">
@@ -21651,17 +21689,20 @@
       <x:c r="H20" s="42"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="G2:G20">
       <x:formula1>"Evet,Hayır"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="B2:B20">
       <x:formula1>"Ortaokul,Lise"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="J2:J100">
+      <x:formula1>"Yok,kitabevi-1 | Ortaokul,kitabevi-1 | Lise,kitabevi-2 | Ortaokul,kitabevi-2 | Lise"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d1b5c0df7cf42ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8753ffe177cc4b7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22050,7 +22091,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fc827c749ae4f5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b37a75beed14015"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/output/Fiyat-Listesi-Yonetim.xlsx
+++ b/output/Fiyat-Listesi-Yonetim.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALS\Documents\26-27 Fiyat Listeleri\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB075AB-39F7-42A0-B46C-B11FBEED8EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A55C0B1-086E-4883-B476-59E9C1800E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ürünler" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3605" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3619" uniqueCount="886">
   <si>
     <t>Barkod</t>
   </si>
@@ -2653,6 +2653,48 @@
   </si>
   <si>
     <t>SİVAS MERKEZ</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/cktz/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/luxj/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/rwbh/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/pijg/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/lraw/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/ppbg/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/qqya/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/nbqo/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/rryj/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/izmi/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/axqm/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/xzgg/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/eqxu/</t>
+  </si>
+  <si>
+    <t>https://online.fliphtml5.com/nnalh/ogfs/</t>
   </si>
 </sst>
 </file>
@@ -2909,7 +2951,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3048,6 +3090,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3057,10 +3103,7 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Köprü" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3081,6 +3124,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UrunlerTablosu" displayName="UrunlerTablosu" ref="A1:K988" totalsRowShown="0">
+  <autoFilter ref="A1:K988" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Barkod"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Yayın"/>
@@ -19150,7 +19194,7 @@
       <c r="K488" s="31"/>
     </row>
     <row r="489" spans="1:11">
-      <c r="A489" s="57">
+      <c r="A489" s="54">
         <v>9786255984661</v>
       </c>
       <c r="B489" t="s">
@@ -19178,7 +19222,7 @@
       </c>
     </row>
     <row r="490" spans="1:11">
-      <c r="A490" s="57">
+      <c r="A490" s="54">
         <v>9786255984685</v>
       </c>
       <c r="B490" t="s">
@@ -19206,7 +19250,7 @@
       </c>
     </row>
     <row r="491" spans="1:11">
-      <c r="A491" s="57">
+      <c r="A491" s="54">
         <v>9786255984654</v>
       </c>
       <c r="B491" t="s">
@@ -19234,7 +19278,7 @@
       </c>
     </row>
     <row r="492" spans="1:11">
-      <c r="A492" s="57">
+      <c r="A492" s="54">
         <v>9786255984708</v>
       </c>
       <c r="B492" t="s">
@@ -19262,7 +19306,7 @@
       </c>
     </row>
     <row r="493" spans="1:11">
-      <c r="A493" s="57">
+      <c r="A493" s="54">
         <v>9786255984678</v>
       </c>
       <c r="B493" t="s">
@@ -19290,7 +19334,7 @@
       </c>
     </row>
     <row r="494" spans="1:11">
-      <c r="A494" s="57">
+      <c r="A494" s="54">
         <v>9786255984746</v>
       </c>
       <c r="B494" t="s">
@@ -19318,7 +19362,7 @@
       </c>
     </row>
     <row r="495" spans="1:11">
-      <c r="A495" s="57">
+      <c r="A495" s="54">
         <v>9786255984845</v>
       </c>
       <c r="B495" t="s">
@@ -19346,7 +19390,7 @@
       </c>
     </row>
     <row r="496" spans="1:11">
-      <c r="A496" s="57">
+      <c r="A496" s="54">
         <v>9786255984890</v>
       </c>
       <c r="B496" t="s">
@@ -19374,7 +19418,7 @@
       </c>
     </row>
     <row r="497" spans="1:9">
-      <c r="A497" s="57">
+      <c r="A497" s="54">
         <v>9786255676047</v>
       </c>
       <c r="B497" t="s">
@@ -19402,7 +19446,7 @@
       </c>
     </row>
     <row r="498" spans="1:9">
-      <c r="A498" s="57">
+      <c r="A498" s="54">
         <v>9786255984937</v>
       </c>
       <c r="B498" t="s">
@@ -19430,7 +19474,7 @@
       </c>
     </row>
     <row r="499" spans="1:9">
-      <c r="A499" s="57">
+      <c r="A499" s="54">
         <v>9786255676115</v>
       </c>
       <c r="B499" t="s">
@@ -19458,7 +19502,7 @@
       </c>
     </row>
     <row r="500" spans="1:9">
-      <c r="A500" s="57">
+      <c r="A500" s="54">
         <v>9786255676221</v>
       </c>
       <c r="B500" t="s">
@@ -19486,7 +19530,7 @@
       </c>
     </row>
     <row r="501" spans="1:9">
-      <c r="A501" s="57">
+      <c r="A501" s="54">
         <v>9786255676061</v>
       </c>
       <c r="B501" t="s">
@@ -19514,7 +19558,7 @@
       </c>
     </row>
     <row r="502" spans="1:9">
-      <c r="A502" s="57">
+      <c r="A502" s="54">
         <v>9786255676276</v>
       </c>
       <c r="B502" t="s">
@@ -19542,7 +19586,7 @@
       </c>
     </row>
     <row r="503" spans="1:9">
-      <c r="A503" s="57">
+      <c r="A503" s="54">
         <v>9786255676214</v>
       </c>
       <c r="B503" t="s">
@@ -19570,7 +19614,7 @@
       </c>
     </row>
     <row r="504" spans="1:9">
-      <c r="A504" s="57">
+      <c r="A504" s="54">
         <v>9786255676467</v>
       </c>
       <c r="B504" t="s">
@@ -19598,7 +19642,7 @@
       </c>
     </row>
     <row r="505" spans="1:9">
-      <c r="A505" s="57">
+      <c r="A505" s="54">
         <v>9786255676566</v>
       </c>
       <c r="B505" t="s">
@@ -19626,7 +19670,7 @@
       </c>
     </row>
     <row r="506" spans="1:9">
-      <c r="A506" s="57">
+      <c r="A506" s="54">
         <v>9786255676511</v>
       </c>
       <c r="B506" t="s">
@@ -19654,7 +19698,7 @@
       </c>
     </row>
     <row r="507" spans="1:9">
-      <c r="A507" s="57">
+      <c r="A507" s="54">
         <v>9786255676610</v>
       </c>
       <c r="B507" t="s">
@@ -19682,7 +19726,7 @@
       </c>
     </row>
     <row r="508" spans="1:9">
-      <c r="A508" s="57">
+      <c r="A508" s="54">
         <v>9786255676405</v>
       </c>
       <c r="B508" t="s">
@@ -19710,7 +19754,7 @@
       </c>
     </row>
     <row r="509" spans="1:9">
-      <c r="A509" s="57">
+      <c r="A509" s="54">
         <v>9786255676795</v>
       </c>
       <c r="B509" t="s">
@@ -19738,7 +19782,7 @@
       </c>
     </row>
     <row r="510" spans="1:9">
-      <c r="A510" s="57">
+      <c r="A510" s="54">
         <v>9786255676788</v>
       </c>
       <c r="B510" t="s">
@@ -19766,7 +19810,7 @@
       </c>
     </row>
     <row r="511" spans="1:9">
-      <c r="A511" s="57">
+      <c r="A511" s="54">
         <v>9786255676801</v>
       </c>
       <c r="B511" t="s">
@@ -19794,7 +19838,7 @@
       </c>
     </row>
     <row r="512" spans="1:9">
-      <c r="A512" s="57">
+      <c r="A512" s="54">
         <v>9786255676818</v>
       </c>
       <c r="B512" t="s">
@@ -19822,7 +19866,7 @@
       </c>
     </row>
     <row r="513" spans="1:9">
-      <c r="A513" s="57" t="s">
+      <c r="A513" s="54" t="s">
         <v>866</v>
       </c>
       <c r="B513" t="s">
@@ -19850,7 +19894,7 @@
       </c>
     </row>
     <row r="514" spans="1:9">
-      <c r="A514" s="57">
+      <c r="A514" s="54">
         <v>9786255676696</v>
       </c>
       <c r="B514" t="s">
@@ -19878,7 +19922,7 @@
       </c>
     </row>
     <row r="515" spans="1:9">
-      <c r="A515" s="57">
+      <c r="A515" s="54">
         <v>9786255676757</v>
       </c>
       <c r="B515" t="s">
@@ -19906,7 +19950,7 @@
       </c>
     </row>
     <row r="516" spans="1:9">
-      <c r="A516" s="57">
+      <c r="A516" s="54">
         <v>9786255676726</v>
       </c>
       <c r="B516" t="s">
@@ -19934,7 +19978,7 @@
       </c>
     </row>
     <row r="517" spans="1:9">
-      <c r="A517" s="57">
+      <c r="A517" s="54">
         <v>9786255676665</v>
       </c>
       <c r="B517" t="s">
@@ -19962,7 +20006,7 @@
       </c>
     </row>
     <row r="518" spans="1:9">
-      <c r="A518" s="57" t="s">
+      <c r="A518" s="54" t="s">
         <v>866</v>
       </c>
       <c r="B518" t="s">
@@ -19990,7 +20034,7 @@
       </c>
     </row>
     <row r="519" spans="1:9">
-      <c r="A519" s="57">
+      <c r="A519" s="54">
         <v>9786255984456</v>
       </c>
       <c r="B519" t="s">
@@ -20018,7 +20062,7 @@
       </c>
     </row>
     <row r="520" spans="1:9">
-      <c r="A520" s="57">
+      <c r="A520" s="54">
         <v>9786255984487</v>
       </c>
       <c r="B520" t="s">
@@ -20046,7 +20090,7 @@
       </c>
     </row>
     <row r="521" spans="1:9">
-      <c r="A521" s="57">
+      <c r="A521" s="54">
         <v>9786255984494</v>
       </c>
       <c r="B521" t="s">
@@ -20074,7 +20118,7 @@
       </c>
     </row>
     <row r="522" spans="1:9">
-      <c r="A522" s="57">
+      <c r="A522" s="54">
         <v>9786255984449</v>
       </c>
       <c r="B522" t="s">
@@ -20102,7 +20146,7 @@
       </c>
     </row>
     <row r="523" spans="1:9">
-      <c r="A523" s="57">
+      <c r="A523" s="54">
         <v>9786255984463</v>
       </c>
       <c r="B523" t="s">
@@ -20130,7 +20174,7 @@
       </c>
     </row>
     <row r="524" spans="1:9">
-      <c r="A524" s="57">
+      <c r="A524" s="54">
         <v>9786255984470</v>
       </c>
       <c r="B524" t="s">
@@ -20158,7 +20202,7 @@
       </c>
     </row>
     <row r="525" spans="1:9">
-      <c r="A525" s="57">
+      <c r="A525" s="54">
         <v>9786259783246</v>
       </c>
       <c r="B525" t="s">
@@ -20186,7 +20230,7 @@
       </c>
     </row>
     <row r="526" spans="1:9">
-      <c r="A526" s="57">
+      <c r="A526" s="54">
         <v>9786259783222</v>
       </c>
       <c r="B526" t="s">
@@ -20214,7 +20258,7 @@
       </c>
     </row>
     <row r="527" spans="1:9">
-      <c r="A527" s="57">
+      <c r="A527" s="54">
         <v>9786259783277</v>
       </c>
       <c r="B527" t="s">
@@ -20242,7 +20286,7 @@
       </c>
     </row>
     <row r="528" spans="1:9">
-      <c r="A528" s="57">
+      <c r="A528" s="54">
         <v>9786259783260</v>
       </c>
       <c r="B528" t="s">
@@ -20269,8 +20313,8 @@
         <v>302.39999999999998</v>
       </c>
     </row>
-    <row r="529" spans="1:9">
-      <c r="A529" s="57">
+    <row r="529" spans="1:10">
+      <c r="A529" s="54">
         <v>9786259783239</v>
       </c>
       <c r="B529" t="s">
@@ -20297,8 +20341,8 @@
         <v>310.8</v>
       </c>
     </row>
-    <row r="530" spans="1:9">
-      <c r="A530" s="57">
+    <row r="530" spans="1:10">
+      <c r="A530" s="54">
         <v>9786259783253</v>
       </c>
       <c r="B530" t="s">
@@ -20325,8 +20369,8 @@
         <v>277.2</v>
       </c>
     </row>
-    <row r="531" spans="1:9">
-      <c r="A531" s="57">
+    <row r="531" spans="1:10">
+      <c r="A531" s="54">
         <v>9786259783215</v>
       </c>
       <c r="B531" t="s">
@@ -20355,9 +20399,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B531,İndirimler!$B$2:$B$210,C531)&gt;0,ROUND(G531*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B531,İndirimler!$B$2:$B$210,C531)),2),"")</f>
         <v>223.3</v>
       </c>
-    </row>
-    <row r="532" spans="1:9">
-      <c r="A532" s="57">
+      <c r="J531" s="59" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="532" spans="1:10">
+      <c r="A532" s="54">
         <v>9786259483597</v>
       </c>
       <c r="B532" t="s">
@@ -20386,9 +20433,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B532,İndirimler!$B$2:$B$210,C532)&gt;0,ROUND(G532*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B532,İndirimler!$B$2:$B$210,C532)),2),"")</f>
         <v>200.2</v>
       </c>
-    </row>
-    <row r="533" spans="1:9">
-      <c r="A533" s="57">
+      <c r="J532" s="59" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="533" spans="1:10">
+      <c r="A533" s="54">
         <v>9786259483573</v>
       </c>
       <c r="B533" t="s">
@@ -20417,9 +20467,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B533,İndirimler!$B$2:$B$210,C533)&gt;0,ROUND(G533*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B533,İndirimler!$B$2:$B$210,C533)),2),"")</f>
         <v>215.6</v>
       </c>
-    </row>
-    <row r="534" spans="1:9">
-      <c r="A534" s="57">
+      <c r="J533" s="59" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="534" spans="1:10">
+      <c r="A534" s="54">
         <v>9786259483566</v>
       </c>
       <c r="B534" t="s">
@@ -20448,9 +20501,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B534,İndirimler!$B$2:$B$210,C534)&gt;0,ROUND(G534*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B534,İndirimler!$B$2:$B$210,C534)),2),"")</f>
         <v>238.7</v>
       </c>
-    </row>
-    <row r="535" spans="1:9">
-      <c r="A535" s="57">
+      <c r="J534" s="59" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="535" spans="1:10">
+      <c r="A535" s="54">
         <v>9786259483559</v>
       </c>
       <c r="B535" t="s">
@@ -20479,9 +20535,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B535,İndirimler!$B$2:$B$210,C535)&gt;0,ROUND(G535*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B535,İndirimler!$B$2:$B$210,C535)),2),"")</f>
         <v>246.4</v>
       </c>
-    </row>
-    <row r="536" spans="1:9">
-      <c r="A536" s="57">
+      <c r="J535" s="59" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="536" spans="1:10">
+      <c r="A536" s="54">
         <v>9786259483580</v>
       </c>
       <c r="B536" t="s">
@@ -20510,9 +20569,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B536,İndirimler!$B$2:$B$210,C536)&gt;0,ROUND(G536*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B536,İndirimler!$B$2:$B$210,C536)),2),"")</f>
         <v>200.2</v>
       </c>
-    </row>
-    <row r="537" spans="1:9">
-      <c r="A537" s="57">
+      <c r="J536" s="59" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="537" spans="1:10">
+      <c r="A537" s="54">
         <v>9786259783208</v>
       </c>
       <c r="B537" t="s">
@@ -20541,9 +20603,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B537,İndirimler!$B$2:$B$210,C537)&gt;0,ROUND(G537*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B537,İndirimler!$B$2:$B$210,C537)),2),"")</f>
         <v>261.8</v>
       </c>
-    </row>
-    <row r="538" spans="1:9">
-      <c r="A538" s="57">
+      <c r="J537" s="59" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="538" spans="1:10">
+      <c r="A538" s="54">
         <v>9786259483511</v>
       </c>
       <c r="B538" t="s">
@@ -20572,9 +20637,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B538,İndirimler!$B$2:$B$210,C538)&gt;0,ROUND(G538*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B538,İndirimler!$B$2:$B$210,C538)),2),"")</f>
         <v>300.3</v>
       </c>
-    </row>
-    <row r="539" spans="1:9">
-      <c r="A539" s="57">
+      <c r="J538" s="59" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="539" spans="1:10">
+      <c r="A539" s="54">
         <v>9786259825380</v>
       </c>
       <c r="B539" t="s">
@@ -20603,9 +20671,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B539,İndirimler!$B$2:$B$210,C539)&gt;0,ROUND(G539*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B539,İndirimler!$B$2:$B$210,C539)),2),"")</f>
         <v>246.4</v>
       </c>
-    </row>
-    <row r="540" spans="1:9">
-      <c r="A540" s="57">
+      <c r="J539" s="59" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="540" spans="1:10">
+      <c r="A540" s="54">
         <v>9786259825397</v>
       </c>
       <c r="B540" t="s">
@@ -20634,9 +20705,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B540,İndirimler!$B$2:$B$210,C540)&gt;0,ROUND(G540*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B540,İndirimler!$B$2:$B$210,C540)),2),"")</f>
         <v>277.2</v>
       </c>
-    </row>
-    <row r="541" spans="1:9">
-      <c r="A541" s="57">
+      <c r="J540" s="59" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="541" spans="1:10">
+      <c r="A541" s="54">
         <v>9786259483504</v>
       </c>
       <c r="B541" t="s">
@@ -20665,9 +20739,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B541,İndirimler!$B$2:$B$210,C541)&gt;0,ROUND(G541*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B541,İndirimler!$B$2:$B$210,C541)),2),"")</f>
         <v>261.8</v>
       </c>
-    </row>
-    <row r="542" spans="1:9">
-      <c r="A542" s="57">
+      <c r="J541" s="59" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="542" spans="1:10">
+      <c r="A542" s="54">
         <v>9786259483535</v>
       </c>
       <c r="B542" t="s">
@@ -20696,9 +20773,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B542,İndirimler!$B$2:$B$210,C542)&gt;0,ROUND(G542*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B542,İndirimler!$B$2:$B$210,C542)),2),"")</f>
         <v>261.8</v>
       </c>
-    </row>
-    <row r="543" spans="1:9">
-      <c r="A543" s="57">
+      <c r="J542" s="59" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="543" spans="1:10">
+      <c r="A543" s="54">
         <v>9786259483528</v>
       </c>
       <c r="B543" t="s">
@@ -20727,9 +20807,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B543,İndirimler!$B$2:$B$210,C543)&gt;0,ROUND(G543*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B543,İndirimler!$B$2:$B$210,C543)),2),"")</f>
         <v>231</v>
       </c>
-    </row>
-    <row r="544" spans="1:9">
-      <c r="A544" s="57">
+      <c r="J543" s="59" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="544" spans="1:10">
+      <c r="A544" s="54">
         <v>9786259483542</v>
       </c>
       <c r="B544" t="s">
@@ -20758,9 +20841,12 @@
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B544,İndirimler!$B$2:$B$210,C544)&gt;0,ROUND(G544*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B544,İndirimler!$B$2:$B$210,C544)),2),"")</f>
         <v>261.8</v>
       </c>
+      <c r="J544" s="59" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="545" spans="1:9">
-      <c r="A545" s="57">
+      <c r="A545" s="54">
         <v>9786259825328</v>
       </c>
       <c r="B545" t="s">
@@ -20791,7 +20877,7 @@
       </c>
     </row>
     <row r="546" spans="1:9">
-      <c r="A546" s="57">
+      <c r="A546" s="54">
         <v>9786259825311</v>
       </c>
       <c r="B546" t="s">
@@ -20822,7 +20908,7 @@
       </c>
     </row>
     <row r="547" spans="1:9">
-      <c r="A547" s="57">
+      <c r="A547" s="54">
         <v>9786259825366</v>
       </c>
       <c r="B547" t="s">
@@ -20853,7 +20939,7 @@
       </c>
     </row>
     <row r="548" spans="1:9">
-      <c r="A548" s="57">
+      <c r="A548" s="54">
         <v>9786259825335</v>
       </c>
       <c r="B548" t="s">
@@ -20884,7 +20970,7 @@
       </c>
     </row>
     <row r="549" spans="1:9">
-      <c r="A549" s="57">
+      <c r="A549" s="54">
         <v>9786259825373</v>
       </c>
       <c r="B549" t="s">
@@ -20915,7 +21001,7 @@
       </c>
     </row>
     <row r="550" spans="1:9">
-      <c r="A550" s="57">
+      <c r="A550" s="54">
         <v>9786259825359</v>
       </c>
       <c r="B550" t="s">
@@ -20946,7 +21032,7 @@
       </c>
     </row>
     <row r="551" spans="1:9">
-      <c r="A551" s="57">
+      <c r="A551" s="54">
         <v>9786259825342</v>
       </c>
       <c r="B551" t="s">
@@ -25397,10 +25483,24 @@
     <hyperlink ref="J439" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
     <hyperlink ref="J458" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
     <hyperlink ref="J470" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="J537" r:id="rId50" xr:uid="{09889307-60F5-4747-A45C-D7F760721F1A}"/>
+    <hyperlink ref="J536" r:id="rId51" xr:uid="{E7839B6F-D21F-4320-870A-EBE38918564E}"/>
+    <hyperlink ref="J534" r:id="rId52" xr:uid="{DE9BB287-A5F7-44C0-87B0-629EFE81C65C}"/>
+    <hyperlink ref="J535" r:id="rId53" xr:uid="{3E2FFE86-2EB3-422A-A224-689AD22D251C}"/>
+    <hyperlink ref="J533" r:id="rId54" xr:uid="{A5A40469-9630-4494-AA3D-3995AD445FB4}"/>
+    <hyperlink ref="J532" r:id="rId55" xr:uid="{423186BC-072B-4B79-910E-95C9D57A9D22}"/>
+    <hyperlink ref="J531" r:id="rId56" xr:uid="{C4F0FC62-E67D-4227-B6EC-FCE4D2AF2E29}"/>
+    <hyperlink ref="J538" r:id="rId57" xr:uid="{CC18A69F-3019-4377-9524-7BCCBEE01288}"/>
+    <hyperlink ref="J539" r:id="rId58" xr:uid="{5772DA47-A421-4AC1-85B3-EEB7346A8F45}"/>
+    <hyperlink ref="J540" r:id="rId59" xr:uid="{1C1B8E51-75AE-40A9-9270-709FC26C193D}"/>
+    <hyperlink ref="J542" r:id="rId60" xr:uid="{E7458058-C40B-4C83-A630-617AA5E851F5}"/>
+    <hyperlink ref="J541" r:id="rId61" xr:uid="{6DD5B95A-1C32-428D-9F22-F5BD62A7BE9A}"/>
+    <hyperlink ref="J543" r:id="rId62" xr:uid="{FF7A0BCD-4670-42FB-A725-4B0A26D9B4D8}"/>
+    <hyperlink ref="J544" r:id="rId63" xr:uid="{B62B9AB9-E582-4FDC-A04D-D7D86EE675A0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId50"/>
+    <tablePart r:id="rId64"/>
   </tableParts>
 </worksheet>
 </file>
@@ -27133,14 +27233,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="42" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="56" t="s">
         <v>802</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
     </row>
     <row r="3" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A3" s="26" t="s">
@@ -27233,18 +27333,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="32.1" customHeight="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="57" t="s">
         <v>820</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="D1" s="55" t="s">
+      <c r="B1" s="57"/>
+      <c r="D1" s="57" t="s">
         <v>821</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="G1" s="56" t="s">
+      <c r="E1" s="57"/>
+      <c r="G1" s="58" t="s">
         <v>822</v>
       </c>
-      <c r="H1" s="56"/>
+      <c r="H1" s="58"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1"/>
     <row r="3" spans="1:8" ht="24" customHeight="1">
@@ -27620,7 +27720,7 @@
       </c>
     </row>
     <row r="36" spans="7:8">
-      <c r="G36" s="58" t="s">
+      <c r="G36" s="55" t="s">
         <v>863</v>
       </c>
       <c r="H36" s="51" t="s">

--- a/output/Fiyat-Listesi-Yonetim.xlsx
+++ b/output/Fiyat-Listesi-Yonetim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALS\Documents\26-27 Fiyat Listeleri\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E4F17C-277E-4A9E-B78C-11491B190565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E3F67E-F5A4-4B49-B8CA-6B52457B3E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3645" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3644" uniqueCount="900">
   <si>
     <t>Barkod</t>
   </si>
@@ -21168,8 +21168,8 @@
       </c>
     </row>
     <row r="553" spans="1:10">
-      <c r="A553" s="50" t="s">
-        <v>262</v>
+      <c r="A553" s="50">
+        <v>9786258188158</v>
       </c>
       <c r="B553" t="s">
         <v>123</v>
@@ -21186,13 +21186,16 @@
       <c r="F553" t="s">
         <v>16</v>
       </c>
+      <c r="G553">
+        <v>499</v>
+      </c>
       <c r="H553">
         <f>IF(SUMIFS(İndirimler!$C$2:$C$210,İndirimler!$A$2:$A$210,B553,İndirimler!$B$2:$B$210,C553)&gt;0,ROUND(G553*(1-SUMIFS(İndirimler!$C$2:$C$210,İndirimler!$A$2:$A$210,B553,İndirimler!$B$2:$B$210,C553)),2),"")</f>
-        <v>0</v>
+        <v>424.15</v>
       </c>
       <c r="I553">
         <f>IF(SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B553,İndirimler!$B$2:$B$210,C553)&gt;0,ROUND(G553*(1-SUMIFS(İndirimler!$D$2:$D$210,İndirimler!$A$2:$A$210,B553,İndirimler!$B$2:$B$210,C553)),2),"")</f>
-        <v>0</v>
+        <v>349.3</v>
       </c>
       <c r="J553" s="52" t="s">
         <v>888</v>
